--- a/llm/evaluation/annotation/calibration/annotator1.xlsx
+++ b/llm/evaluation/annotation/calibration/annotator1.xlsx
@@ -428,17 +428,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,20 +471,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>annotator_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>abstain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hallucinated</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>wrong_claims</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>faithfulness_level</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>approach_match</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>domain_familiarity</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -577,10 +619,21 @@
 By following this approach, you will have a clear and reusable way to convert strings into `RenderFragment` while maintaining performance and security in your Blazor applications.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -613,10 +666,60 @@
 If your project requires something more specific beyond these aspects, it might be useful to consult existing forums or communities focused on Windows Mobile development for tailored advice or recommendations on suitable libraries.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+'t done automatically by the UI library), and intercept events.&lt;/li&gt;
+&lt;li&gt;potential for a large, easy-to-contribute standard library.&lt;/li&gt;
+&lt;li&gt;documentation, though if the library was well designed and generated enough interest, this would be a given.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;In my experience, html is so much easier to get something good-looking up than UI libraries.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;edit&lt;/strong&gt; - after working with PyQt 4 for a while, it gets the job done for simple UI's. I'm currently not developing for end users, so looks don't matter. The QTextBrowser is very useful for displaying basic HTML tables and generating HTML links.&lt;/p&gt;
+[K2]
+Q: asp.net mobile web applications
+A: &lt;p&gt;Are you using the Mobile controls in ASP.NET, or just the regular ones? There is a separate set that are intended to support and adjust to various mobile devices somewhat better.&lt;/p&gt;
+&lt;p&gt;For a first-effort mobile site, I would look either at a well-established mobile framework (to be honest, I've never extensively used the ASP.NET Mobile Webforms controls), or to do something where I'm building my own HTML much more directly, to be sure to keep things mobile-safe.&lt;/p&gt;
+&lt;p&gt;That's one of the reasons I use ASP.NET MVC more myself, now... but that is a bit of a leap to make, and especially if it would just be for mobile use.&lt;/p&gt;
+&lt;hr&gt;
+&lt;p&gt;So anyway, if you are already using the ASP.NET Mobile controls, my answer is irrelevant!&lt;/p&gt;
+[K3]
+Q: Business web-app in .NET - which technology to pick?
+A: &lt;p&gt;if you're planning to support iphone/android/non-win, then say goodbye to silverlight. then again if you're planning to support smartphones, you'd need to do separate designs for small vs large form factor devices. dockable interfaces are too cluttered for small devices.&lt;/p&gt;
+&lt;p&gt;Technology? HTML5 would be nice but only recent browsers support it, and even then only support bits &amp;amp; pieces of the standard.&lt;/p&gt;
+&lt;p&gt;MVC vs webforms? doesn't really matter. both just a way of spitting out HTML.&lt;/p&gt;
+&lt;p&gt;You'll need to do some "screwing around with Javascript or non-server technologies". Telerik offer a lot of the components you mentioned for webforms, though they do tend to bloat. &lt;/p&gt;
+&lt;p&gt;Based lightly on what your requirements are:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;list views: native in webforms/mvc&lt;/li&gt;
+&lt;li&gt;tree views: telerik, or a jQuery plugin&lt;/li&gt;
+&lt;li&gt;grids: native html tables work best IMO, or you can do do a databound something in asp.net or telerik&lt;/li&gt;
+&lt;li&gt;charts: free plugin, telerik, dundas, or something like SSRS if you have something of a reporting nature&lt;/li&gt;
+&lt;li&gt;docking ui: reconsider your need for this. If you're still keen asp.net has webparts built in or you can get a package from jQuery UI&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;overall you may be looking for a "quick" way to web-enable your app, but they are two different beasts and will perform as such. if you do a straight conversion using every plugin available, it will take you a lot of time to learn each component, a lot of page bloat, a lot of bugs, and it will never feel right. my suggestion is to invest the same time learning
+[K4]
+Q: Text editors with built-in terminal?
+A: &lt;p&gt;Emacs, of course.  Can't say if it works on every platform, but Windows, linux and most unixes support it.&lt;/p&gt;
+[K5]
+Q: Reinventing the wheel -a WYSIWYG Editor
+A: &lt;p&gt;Don't reinvent the wheel! If you decide that you need to support designmode iframes as well as contenteditable, &lt;a href="http://closure-library.googlecode.com/svn/docs/class_goog_editor_Field.html" rel="nofollow noreferrer"&gt;Google Closure Editor&lt;/a&gt; has a very performant implementation of multiple editing surfaces that only creates one iframe at a time. &lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -676,13 +779,52 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific method or best practice for converting a string to a RenderFragment in Blazor. They do not provide any information on the topic or clarify whether the approach you are using (`RenderFragment fragm = @&amp;lt;text&amp;gt;@myString&amp;lt;/text&amp;gt;;`) is the best way to achieve this. Therefore, I cannot provide guidance based on the provided context.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific method or best practice for converting a string to a RenderFragment in Blazor. They do not provide any information on the topic or clarify whether the approach you are using (`RenderFragment fragm = @&amp;lt;text&amp;gt;@myString&amp;lt;/text&amp;gt;;`) is the best way to achieve this. Therefore, I cannot provide guidance.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+.toString());
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+ dynamically in the code.&lt;/p&gt;
+&lt;p&gt;After all, it doesn't need to be specified in the C# source code -- can it be done?&lt;/p&gt;
+&lt;p&gt;Cheers,&lt;/p&gt;
+[K3]
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Will get you :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;string 'I. NEED. ISOLATION' (length=18)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Note the only thing I changed compared to your proposed code is the regex delimiter ;-)&lt;/p&gt;
+&lt;br&gt;
+And, using a character that's not present in the HTML string, I don't have anything to escape -- especially, I don't have to escape all the `/`s -- which means the regex is far more easy to both write, read, and understand.
+[K4]
+ e.g. &lt;code&gt;coalesce(1)&lt;/code&gt; &lt;em&gt;(OK, 1 is a bit caricatural, but you see the point)&lt;/em&gt;.&lt;/p&gt;
+[K5]
+Q: Java - converting string to a List
+A: &lt;p&gt;With the additional servlet/JSP context you provided, it seems that the &lt;em&gt;real&lt;/em&gt; mistake in your code is the use of &lt;code&gt;request.getParameter&lt;/code&gt; in the JSP page: that method indeed returns a &lt;code&gt;String&lt;/code&gt;, and you can't &lt;em&gt;convert&lt;/em&gt; a &lt;code&gt;String&lt;/code&gt; in a &lt;code&gt;List&lt;/code&gt;, not with a cast, not even with any other operation allowed by the language or the data structures. You may &lt;em&gt;insert&lt;/em&gt; a &lt;code&gt;String&lt;/code&gt; into a &lt;code&gt;List&lt;/code&gt;, using one of the methods already suggested (or &lt;em&gt;transform&lt;/em&gt; a &lt;code&gt;List&lt;/code&gt; into a &lt;code&gt;String&lt;/code&gt; using other methods), but judging from the code that's not what you need.&lt;/p&gt;
+&lt;p&gt;In the servlet code, you set the &lt;code&gt;styles&lt;/code&gt; &lt;em&gt;attribute&lt;/em&gt; to the &lt;code&gt;List&lt;/code&gt; containing the beer brands. So, to get that &lt;code&gt;List&lt;/code&gt; back, you need to invoke &lt;code&gt;request.getAttribute&lt;/code&gt; instead of &lt;code&gt;getParameter&lt;/code&gt;. The &lt;code&gt;getAttribute&lt;/code&gt; methods returns an &lt;code&gt;Object&lt;/code&gt;, which really is a &lt;code&gt;List&lt;/code&gt;, and you know that because you have set it to be as such, so in this case a cast is exactly the operation that is needed to get back the value with its original type. In code, this means&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;List styles = (List) request.getAttribute("styles");
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;in your JSP, in place of the line that got you troubles.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -736,10 +878,21 @@
 Integrating a fully-fledged WYSIWYG HTML editor in a Windows Mobile app is challenging due to platform limitations. Consider the above suggestions and determine what aligns best with your requirements and user needs. If developing from scratch, start simple, and you can always iterate and add features based on user feedback.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -861,10 +1014,21 @@
 By following these steps, you should be able to pre-index your JSON files and provide efficient search functionality in your ASP.NET Core application using Lucene.Net without relying on an external search engine.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -934,10 +1098,123 @@
 This solution aligns with the concept of manipulating individual elements in jQuery, ensuring that each field gets the correct class based on its individual content.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: jquery giving TypeError getting elements from wrapped set
+A: &lt;p&gt;&lt;code&gt;addClass&lt;/code&gt; is a jQuery method. It can only be called on jQuery objects. When you call &lt;code&gt;[0]&lt;/code&gt; or &lt;code&gt;.get(0)&lt;/code&gt; on your jQuery object, you are fetching the underlying DOM element. That object doesn't support the jQuery methods.&lt;/p&gt;
+&lt;p&gt;You should call &lt;code&gt;addClass&lt;/code&gt; on the jQuery object itself:&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;img[alt].addClass('my-new-class');&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;If you only want to add a class to the first image with an &lt;code&gt;alt&lt;/code&gt; attribute, you could change the jQuery selector to &lt;code&gt;$('img[alt]:first')&lt;/code&gt;.&lt;/p&gt;
+[K2]
+Q: Jquery check if i tag has a class and replace it
+A: &lt;p&gt;First of all, make sure your class names do NOT have spaces. Spaces in &lt;code&gt;class="a b"&lt;/code&gt; actually means 2 separate classes, a and b, not a class "a b". Also as others have mentioned, IDs should be unique. So with code:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;ul class="list-inline recommended-logo"&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-1" class="first_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;First class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-2" class="second_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Second class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-3" class="third_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Third, class&amp;lt;/span&amp;lt;/li&amp;gt;
+   &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-4" class="fourth_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Four class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You can select by class (with a .) and replace easily:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$('.first_class').removeClass('first_class').addClass('fifth_class')
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;will take everything with the class "first_class" and replace it with "fifth_class".&lt;/p&gt;
+&lt;p&gt;I stand by my original code as listed above. But looking at the edits to the question, the problem is apparently using jQuery to select on ID when IDs are repeated - the first  So &lt;strong&gt;ignore&lt;/
+[K3]
+Q: Jquery Burger Menu wont apply class correctly
+A: &lt;p&gt;The problem is in the css rule ,&lt;/p&gt;
+&lt;p&gt;Instead of &lt;strong&gt;&lt;code&gt;header nav ul .open&lt;/code&gt;&lt;/strong&gt; set it to  &lt;strong&gt;&lt;code&gt;header nav ul.open&lt;/code&gt;&lt;/strong&gt; (remove space between &lt;code&gt;ul&lt;/code&gt; and &lt;code&gt;.space&lt;/code&gt; class) , the first  search for element insude the ul that has .open class , the second the ul that has .open class , that's the difference &lt;/p&gt;
+&lt;p&gt;See below snippet &lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="true" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code snippet-currently-hidden"&gt;
+&lt;pre class="snippet-code-js lang-js prettyprint-override"&gt;&lt;code&gt;$(document).ready(function() {
+  $(".burger-nav").on("click", function() {
+      $("header nav ul").toggleClass("open");
+  });
+});&lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;@media screen and (max-width: 680px) {
+  .burger-nav {
+    display: block;
+    height: 30px;
+    width:40px;
+    background: url(https://cdn.css-tricks.com/wp-content/uploads/2012/10/threelines.png) no-repeat 98% center;
+    background-color: blue;
+    background-size: 50px;
+    cursor:pointer;
+  }
+  header .navwrap{
+    padding:0;
+    width:100%;
+  }
+  header nav ul {
+    overflow:hidden;
+    background: #505050;
+    height: 0 ;
+  }
+  header nav ul.open {
+    height: auto;
+  }
+  header nav ul li {
+    float: none;
+    text-align: left;
+    width: 100%;
+    margin: 
+[K4]
+Q: Use of a class inside another class
+A: &lt;p&gt;Use the class which you have given to the span itself.&lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="false" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code"&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;.description p span {
+  font-style: italic;
+}
+.description .cor {
+  font-style: normal;
+  color: red;
+} &lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-html lang-html prettyprint-override"&gt;&lt;code&gt;&amp;lt;div class="description"&amp;gt;
+  &amp;lt;p&amp;gt;This recipe is from one of my &amp;lt;span class="cor"&amp;gt;favorite&amp;lt;/span&amp;gt; cakes out there, really &amp;lt;span&amp;gt;delicious&amp;lt;/span&amp;gt;...check it out below&amp;lt;/p&amp;gt;
+&amp;lt;/div&amp;gt;&lt;/code&gt;&lt;/pre&gt;
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/p&gt;
+[K5]
+Q: nested jquery $.each repeating iteration issue
+A: &lt;p&gt;You could return the newly created &lt;code&gt;.table-list&lt;/code&gt; using &lt;code&gt;.appendTo&lt;/code&gt; (rather than &lt;code&gt;.append&lt;/code&gt;) so that it can be appended to:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;function getList() {
+ $.getJSON(&amp;quot;src/list.json&amp;quot;, function(data) {
+  $.each(data, function( key, fax ) {
+      const faxItem = this;
+      displayOnDom.append(`&amp;lt;div id=faxPlan-${faxItem.id} class=&amp;quot;pricing-table flex-item ${faxItem.recommended ? 'recommended' : ''}&amp;quot;&amp;gt;
+        &amp;lt;h3 class=&amp;quot;pricing-title&amp;quot;&amp;gt;${faxItem.title}&amp;lt;/h3&amp;gt;
+        &amp;lt;div class=&amp;quot;price&amp;quot;&amp;gt;${faxItem.price_per_month}&amp;lt;sup&amp;gt;/ month&amp;lt;/sup&amp;gt;&amp;lt;/div&amp;gt;
+        ${faxItem.button ? `&amp;lt;p class=&amp;quot;rounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;` : `&amp;lt;p class=&amp;quot;norounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;`}
+        `);
+      var tablelist = $('&amp;lt;div class=&amp;quot;table-list&amp;quot;&amp;gt;&amp;lt;/div&amp;gt;').appendTo(displayOnDom);
+      $.each(fax.features, function( key, list ) {
+        tablelist.append(`&amp;lt;p&amp;gt;${list.title}&amp;lt;span&amp;gt;${list.list}&amp;lt;/span&amp;gt;&amp;lt;/p&amp;gt;`)
+      })
+   })   
+ });
+}
+&lt;/code&gt;&lt;/pre&gt;
+</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -994,10 +1271,21 @@
 Continued discussion in the community and between tooling developers and language designers can facilitate better solutions and implementations going forward.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1128,10 +1416,21 @@
 This modification should properly validate the form before allowing the user to switch tabs using the "Next" and "Previous" links.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1185,14 +1484,64 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specifics of how to design your Oracle APEX application to handle family contributions, including how to specifically address the handling of the `CONTRIBUTORS`. It discusses some general database design patterns for creating hierarchical relationships and polymorphism in object-oriented data structures, but does not directly apply to the structure you provided for handling family contributions based on the criteria you laid out.
+          <t>[catatan: informasi tidak tersedia] the specifics of how to design your Oracle APEX application to handle family contributions, including how to specifically address the handling of the `CONTRIBUTORS`. It discusses some general database design patterns for creating hierarchical relationships and polymorphism in object-oriented data structures, but does not directly apply to the structure you provided for handling family contributions based on the criteria you laid out.
 For more specialized advice on this scenario, additional context or resources regarding APEX-specific features, handling many-to-many relationships, or conditionally assigning contributions in Oracle databases would be essential.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: How do I design a chart of accounts for an accounting system using PHP
+A: &lt;p&gt;You may use a hierarchical data model like a nested set or a closure table. In this approach, each node in the tree is represented as a row in a database table, and the relationship between nodes is encoded using additional columns in the table. This approach allows for efficient querying of the tree structure and is suitable for handling a large number of nodes. Or you may use a recursive data model, where each node in the tree is represented as an object that contains a list of its child nodes. This approach is simpler and more intuitive to work with, but may be less efficient for large trees.
+You may also want to have a look at some APIs like Java Tree API and their documentation to get some more insight about the idea.&lt;/p&gt;
+[K2]
+Q: How to visualize the relationship of tables in an Oracle database
+A: &lt;p&gt;There is no inbuilt tool, but you can use some free ware, or even buy some of these if you really like them.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool"&gt;https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/433071/good-tool-to-visualise-database-schema"&gt;Good tool to visualise database schema?&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;My personal favorite is &lt;a href="http://www.embarcadero.com/products/er-studio" rel="nofollow noreferrer"&gt;ER/Studio&lt;/a&gt;&lt;/p&gt;
+[K3]
+ a table that is at the end child point and its data is not so important.&lt;/p&gt;
+[K4]
+Q: Polymorphism in databases
+A: &lt;p&gt;&lt;strong&gt;The OO structure of your data&lt;/strong&gt; &lt;/p&gt;
+&lt;p&gt;You have identified several classes in your &lt;code&gt;Character&lt;/code&gt; population, that are derived from the abstract role , namely &lt;code&gt;Attack&lt;/code&gt;, &lt;code&gt;Defense&lt;/code&gt; and &lt;code&gt;Support&lt;/code&gt;. Each kind of role has different attributes depending on the class.  &lt;/p&gt;
+&lt;p&gt;So you have clearly an OOP design in your mind and want to implement it in a database.  Several design patterns could be used :   &lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;The easiest seems to be the &lt;a href="http://www.martinfowler.com/eaaCatalog/singleTableInheritance.html" rel="noreferrer"&gt;single table inheritance&lt;/a&gt; puts all the fields in a single table.  These are used/interpreted depending on the concrete role.  &lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://martinfowler.com/eaaCatalog/classTableInheritance.html" rel="noreferrer"&gt;class table inheritance&lt;/a&gt; puts the data related to each role (and the character itself) in a distinct table. This requires a 1:1 relation between the derived class' table (e.g. &lt;code&gt;Defense&lt;/code&gt;) and the parent class table (here &lt;code&gt;Character&lt;/code&gt;).  This seems an overkill here&lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://www.martinfowler.com/eaaCatalog/concreteTableInheritance.html" rel="noreferrer"&gt;concrete table inheritance&lt;/a&gt; merges the parent classes with the most derived classes, so you'd end up with a table per role, each having its own &lt;code&gt;name&lt;/code&gt; field.  Again, this seems an overkill here. &lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Classes or relations ?&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is another additional model that you could consider.
+[K5]
+Q: How to optimize long query that displays thousands of data
+A: &lt;p&gt;Several of your tables need this 'composite' index:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;INDEX(allotment_code, category_name, ntp_number, activity)  -- in any order
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;payroll_transaction&lt;/code&gt; needs &lt;code&gt;INDEX(contractor_name)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;payroll_billed_units&lt;/code&gt; needs &lt;code&gt;INDEX(billing_date)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;For further discussion, please provide &lt;code&gt;SHOW CREATE TABLE&lt;/code&gt; for each table and &lt;code&gt;EXPLAIN SELECT ...&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;Use simply &lt;code&gt;COUNT(*)&lt;/code&gt; instead of &lt;code&gt;COUNT(foo)&lt;/code&gt;.  The latter checks the column for being not-NULL before including it.  This is usually not needed.  The reader is confused by thinking that there might be NULLs.&lt;/p&gt;
+&lt;p&gt;Your &lt;code&gt;GROUP BY&lt;/code&gt; is improper because it is missing &lt;code&gt;ntp_number&lt;/code&gt;.  Read about the &lt;code&gt;sql_mode&lt;/code&gt; of &lt;code&gt;ONLY_FULL_GROUP_BY&lt;/code&gt;.  I bring this up because you can almost get rid of some of those subqueries.&lt;/p&gt;
+&lt;p&gt;Another issue...  Because of the "inflate-deflate" nature of &lt;code&gt;JOIN&lt;/code&gt; with &lt;code&gt;GROUP BY&lt;/code&gt;, the numbers may be inflated.  I recommend you manually check the values of the &lt;code&gt;COUNTs&lt;/code&gt;.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1264,10 +1613,21 @@
 Make sure to test thoroughly after the upgrade to ensure all functionality works correctly with the new framework version.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1329,10 +1689,21 @@
 With this approach, you should be able to get the filename correctly and save the audio file as needed.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1403,13 +1774,126 @@
 &lt;div class="field-name-field-rating2 rating-5"&gt;
 &lt;div class="field-name-field-rating2 rating-8"&gt;
 ```
-The retrieved sources do not cover any additional aspects beyond this solution.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+[catatan: informasi tidak tersedia] any additional aspects beyond this solution.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: jquery giving TypeError getting elements from wrapped set
+A: &lt;p&gt;&lt;code&gt;addClass&lt;/code&gt; is a jQuery method. It can only be called on jQuery objects. When you call &lt;code&gt;[0]&lt;/code&gt; or &lt;code&gt;.get(0)&lt;/code&gt; on your jQuery object, you are fetching the underlying DOM element. That object doesn't support the jQuery methods.&lt;/p&gt;
+&lt;p&gt;You should call &lt;code&gt;addClass&lt;/code&gt; on the jQuery object itself:&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;img[alt].addClass('my-new-class');&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;If you only want to add a class to the first image with an &lt;code&gt;alt&lt;/code&gt; attribute, you could change the jQuery selector to &lt;code&gt;$('img[alt]:first')&lt;/code&gt;.&lt;/p&gt;
+[K2]
+Q: Jquery check if i tag has a class and replace it
+A: &lt;p&gt;First of all, make sure your class names do NOT have spaces. Spaces in &lt;code&gt;class="a b"&lt;/code&gt; actually means 2 separate classes, a and b, not a class "a b". Also as others have mentioned, IDs should be unique. So with code:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;ul class="list-inline recommended-logo"&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-1" class="first_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;First class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-2" class="second_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Second class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-3" class="third_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Third, class&amp;lt;/span&amp;lt;/li&amp;gt;
+   &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-4" class="fourth_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Four class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You can select by class (with a .) and replace easily:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$('.first_class').removeClass('first_class').addClass('fifth_class')
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;will take everything with the class "first_class" and replace it with "fifth_class".&lt;/p&gt;
+&lt;p&gt;I stand by my original code as listed above. But looking at the edits to the question, the problem is apparently using jQuery to select on ID when IDs are repeated - the first  So &lt;strong&gt;ignore&lt;/
+[K3]
+Q: Jquery Burger Menu wont apply class correctly
+A: &lt;p&gt;The problem is in the css rule ,&lt;/p&gt;
+&lt;p&gt;Instead of &lt;strong&gt;&lt;code&gt;header nav ul .open&lt;/code&gt;&lt;/strong&gt; set it to  &lt;strong&gt;&lt;code&gt;header nav ul.open&lt;/code&gt;&lt;/strong&gt; (remove space between &lt;code&gt;ul&lt;/code&gt; and &lt;code&gt;.space&lt;/code&gt; class) , the first  search for element insude the ul that has .open class , the second the ul that has .open class , that's the difference &lt;/p&gt;
+&lt;p&gt;See below snippet &lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="true" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code snippet-currently-hidden"&gt;
+&lt;pre class="snippet-code-js lang-js prettyprint-override"&gt;&lt;code&gt;$(document).ready(function() {
+  $(".burger-nav").on("click", function() {
+      $("header nav ul").toggleClass("open");
+  });
+});&lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;@media screen and (max-width: 680px) {
+  .burger-nav {
+    display: block;
+    height: 30px;
+    width:40px;
+    background: url(https://cdn.css-tricks.com/wp-content/uploads/2012/10/threelines.png) no-repeat 98% center;
+    background-color: blue;
+    background-size: 50px;
+    cursor:pointer;
+  }
+  header .navwrap{
+    padding:0;
+    width:100%;
+  }
+  header nav ul {
+    overflow:hidden;
+    background: #505050;
+    height: 0 ;
+  }
+  header nav ul.open {
+    height: auto;
+  }
+  header nav ul li {
+    float: none;
+    text-align: left;
+    width: 100%;
+    margin: 
+[K4]
+Q: Use of a class inside another class
+A: &lt;p&gt;Use the class which you have given to the span itself.&lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="false" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code"&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;.description p span {
+  font-style: italic;
+}
+.description .cor {
+  font-style: normal;
+  color: red;
+} &lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-html lang-html prettyprint-override"&gt;&lt;code&gt;&amp;lt;div class="description"&amp;gt;
+  &amp;lt;p&amp;gt;This recipe is from one of my &amp;lt;span class="cor"&amp;gt;favorite&amp;lt;/span&amp;gt; cakes out there, really &amp;lt;span&amp;gt;delicious&amp;lt;/span&amp;gt;...check it out below&amp;lt;/p&amp;gt;
+&amp;lt;/div&amp;gt;&lt;/code&gt;&lt;/pre&gt;
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/p&gt;
+[K5]
+Q: nested jquery $.each repeating iteration issue
+A: &lt;p&gt;You could return the newly created &lt;code&gt;.table-list&lt;/code&gt; using &lt;code&gt;.appendTo&lt;/code&gt; (rather than &lt;code&gt;.append&lt;/code&gt;) so that it can be appended to:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;function getList() {
+ $.getJSON(&amp;quot;src/list.json&amp;quot;, function(data) {
+  $.each(data, function( key, fax ) {
+      const faxItem = this;
+      displayOnDom.append(`&amp;lt;div id=faxPlan-${faxItem.id} class=&amp;quot;pricing-table flex-item ${faxItem.recommended ? 'recommended' : ''}&amp;quot;&amp;gt;
+        &amp;lt;h3 class=&amp;quot;pricing-title&amp;quot;&amp;gt;${faxItem.title}&amp;lt;/h3&amp;gt;
+        &amp;lt;div class=&amp;quot;price&amp;quot;&amp;gt;${faxItem.price_per_month}&amp;lt;sup&amp;gt;/ month&amp;lt;/sup&amp;gt;&amp;lt;/div&amp;gt;
+        ${faxItem.button ? `&amp;lt;p class=&amp;quot;rounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;` : `&amp;lt;p class=&amp;quot;norounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;`}
+        `);
+      var tablelist = $('&amp;lt;div class=&amp;quot;table-list&amp;quot;&amp;gt;&amp;lt;/div&amp;gt;').appendTo(displayOnDom);
+      $.each(fax.features, function( key, list ) {
+        tablelist.append(`&amp;lt;p&amp;gt;${list.title}&amp;lt;span&amp;gt;${list.list}&amp;lt;/span&amp;gt;&amp;lt;/p&amp;gt;`)
+      })
+   })   
+ });
+}
+&lt;/code&gt;&lt;/pre&gt;
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1506,10 +1990,60 @@
 This design will help maintain clarity and ensure that all contributions can be flexibly assigned based on your stated criteria.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: How do I design a chart of accounts for an accounting system using PHP
+A: &lt;p&gt;You may use a hierarchical data model like a nested set or a closure table. In this approach, each node in the tree is represented as a row in a database table, and the relationship between nodes is encoded using additional columns in the table. This approach allows for efficient querying of the tree structure and is suitable for handling a large number of nodes. Or you may use a recursive data model, where each node in the tree is represented as an object that contains a list of its child nodes. This approach is simpler and more intuitive to work with, but may be less efficient for large trees.
+You may also want to have a look at some APIs like Java Tree API and their documentation to get some more insight about the idea.&lt;/p&gt;
+[K2]
+Q: How to visualize the relationship of tables in an Oracle database
+A: &lt;p&gt;There is no inbuilt tool, but you can use some free ware, or even buy some of these if you really like them.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool"&gt;https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/433071/good-tool-to-visualise-database-schema"&gt;Good tool to visualise database schema?&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;My personal favorite is &lt;a href="http://www.embarcadero.com/products/er-studio" rel="nofollow noreferrer"&gt;ER/Studio&lt;/a&gt;&lt;/p&gt;
+[K3]
+ a table that is at the end child point and its data is not so important.&lt;/p&gt;
+[K4]
+Q: Polymorphism in databases
+A: &lt;p&gt;&lt;strong&gt;The OO structure of your data&lt;/strong&gt; &lt;/p&gt;
+&lt;p&gt;You have identified several classes in your &lt;code&gt;Character&lt;/code&gt; population, that are derived from the abstract role , namely &lt;code&gt;Attack&lt;/code&gt;, &lt;code&gt;Defense&lt;/code&gt; and &lt;code&gt;Support&lt;/code&gt;. Each kind of role has different attributes depending on the class.  &lt;/p&gt;
+&lt;p&gt;So you have clearly an OOP design in your mind and want to implement it in a database.  Several design patterns could be used :   &lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;The easiest seems to be the &lt;a href="http://www.martinfowler.com/eaaCatalog/singleTableInheritance.html" rel="noreferrer"&gt;single table inheritance&lt;/a&gt; puts all the fields in a single table.  These are used/interpreted depending on the concrete role.  &lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://martinfowler.com/eaaCatalog/classTableInheritance.html" rel="noreferrer"&gt;class table inheritance&lt;/a&gt; puts the data related to each role (and the character itself) in a distinct table. This requires a 1:1 relation between the derived class' table (e.g. &lt;code&gt;Defense&lt;/code&gt;) and the parent class table (here &lt;code&gt;Character&lt;/code&gt;).  This seems an overkill here&lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://www.martinfowler.com/eaaCatalog/concreteTableInheritance.html" rel="noreferrer"&gt;concrete table inheritance&lt;/a&gt; merges the parent classes with the most derived classes, so you'd end up with a table per role, each having its own &lt;code&gt;name&lt;/code&gt; field.  Again, this seems an overkill here. &lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Classes or relations ?&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is another additional model that you could consider.
+[K5]
+Q: How to optimize long query that displays thousands of data
+A: &lt;p&gt;Several of your tables need this 'composite' index:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;INDEX(allotment_code, category_name, ntp_number, activity)  -- in any order
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;payroll_transaction&lt;/code&gt; needs &lt;code&gt;INDEX(contractor_name)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;payroll_billed_units&lt;/code&gt; needs &lt;code&gt;INDEX(billing_date)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;For further discussion, please provide &lt;code&gt;SHOW CREATE TABLE&lt;/code&gt; for each table and &lt;code&gt;EXPLAIN SELECT ...&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;Use simply &lt;code&gt;COUNT(*)&lt;/code&gt; instead of &lt;code&gt;COUNT(foo)&lt;/code&gt;.  The latter checks the column for being not-NULL before including it.  This is usually not needed.  The reader is confused by thinking that there might be NULLs.&lt;/p&gt;
+&lt;p&gt;Your &lt;code&gt;GROUP BY&lt;/code&gt; is improper because it is missing &lt;code&gt;ntp_number&lt;/code&gt;.  Read about the &lt;code&gt;sql_mode&lt;/code&gt; of &lt;code&gt;ONLY_FULL_GROUP_BY&lt;/code&gt;.  I bring this up because you can almost get rid of some of those subqueries.&lt;/p&gt;
+&lt;p&gt;Another issue...  Because of the "inflate-deflate" nature of &lt;code&gt;JOIN&lt;/code&gt; with &lt;code&gt;GROUP BY&lt;/code&gt;, the numbers may be inflated.  I recommend you manually check the values of the &lt;code&gt;COUNTs&lt;/code&gt;.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1585,10 +2119,65 @@
 In summary, your proposed strategy using a `SET` to track keys for deletion is sound, especially given the limitations of bulk operations in Redis. This will provide you better control and efficiency regarding your cache management without incurring the risk of timeouts associated with the wildcard key deletion methods. Your awareness of performance considerations based on community feedback, such as efforts posted by Marc Gravell and other recommendations from StackExchange, illustrates a proactive approach to address common pitfalls in Redis key management .</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Memcached with Windows and .NET
+A: &lt;p&gt;I'm suprised no one here has yet to mention &lt;a href="http://code.google.com/p/redis/" rel="noreferrer"&gt;Redis&lt;/a&gt; - it is one of the most feature-rich and fastest (110,000 SET's per second on an entry level linux box) key-value data stores with rich data-structure support for strings, sets, lists, sorted sets and hashes.  &lt;/p&gt;
+&lt;p&gt;Although windows is not an officially supported platform, it runs perfectly under windows with all tests passing. I have windows builds (using Cygwin) available here:
+&lt;a href="https://github.com/ServiceStack/ServiceStack.Redis#redis-server-builds-for-windows" rel="noreferrer"&gt;https://github.com/ServiceStack/ServiceStack.Redis#redis-server-builds-for-windows&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;It also has client bindings for nearly every programming language in use today. I maintain a rich Open Source C# Redis client with native API support for any C# POCO type, transaction support and Thread-safe client managers that are ready to be dropped into any IOC at:
+&lt;a href="https://github.com/ServiceStack/ServiceStack.Redis" rel="noreferrer"&gt;https://github.com/ServiceStack/ServiceStack.Redis&lt;/a&gt;&lt;/p&gt;
+[K2]
+Q: more that 1mb data in memcahed nodejs
+A: &lt;p&gt;Options available :&lt;/p&gt;
+&lt;p&gt;1/ Make sure you are using compression while storing them in memcached, your nodejs memcached driver would be supporting gzip compression.&lt;/p&gt;
+&lt;p&gt;2/ Split the data into multiple keys&lt;/p&gt;
+&lt;p&gt;3/ Increase max object size to more than 1 MB ( but that may increase fragmentation,decrease performance based on your cache usage ) &lt;/p&gt;
+&lt;p&gt;4/ Use redis as cache instead of memcached if your object sizes are usually large. Redis string datatype supports objects upto 512 MB in size, that would be easily available as direct get,set interface in any standard nodejs-redis cache driver&lt;/p&gt;
+[K3]
+ have an RDB snapshot from time to time is a great idea for doing database backups, for faster restarts, and in the event of bugs in the AOF engine.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note: for all these reasons we'll likely end up unifying AOF and RDB into a single persistence model in the future (long term plan).&lt;/strong&gt;
+Refer &lt;a href="https://redis.io/topics/persistence" rel="nofollow noreferrer"&gt;Redis Persistence&lt;/a&gt;&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;Does this mean that we could host different caches for different purposes, for eg. one cache to host user information and another cache to host order information. Or is it so that one redis instance would be master and the others could be slaves for read operations but both would serve the same cache for eg. user_information. &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Both will work.It depends on your configuration, if you want to configure both master and slave in &lt;a href="http://blog.awareshop.com/2015/01/11/redis-master-slave-setup-on-single-machine/" rel="nofollow noreferrer"&gt;same machine&lt;/a&gt; for serving for single cache you can do that or else you want &lt;a href="https://stackoverflow.com/questions/39352899/running-multiple-instance-of-redis-on-centos"&gt;different instances of redis&lt;/a&gt; for serving different caches you can also do that.&lt;/p&gt;
+[K4]
+Q: How does Redis run on multi-core cpus
+A: &lt;blockquote&gt;
+  &lt;p&gt;It is recommended that you can run multiple redis instances to use multi-core CPUs?&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;First of all, redis is not designed for multi-core CPU.However, you can run multiple instances of redis in multi-core CPU.But it does not provide such guarantee.&lt;/p&gt;
+&lt;p&gt;For example, if you launch six instances on hexa-core, there will be 6 different processes that the OS will have to get scheduled on the six cores. It is up to the OS to perform this load balancing, optimizing the performance of the system.If you want to enforce the process to be execute in specific cores you can go with modern OS.But it will seriously impact the performance of redis.&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;If Redis supports persistence why would anyone use NoSQL Databases like DynamoDB etc.?&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Redis isn't the best fit for persistent storage as it's mainly performance focused.The major difference between redis and NOSQL databases is the way of writing data.Redis usually commits data in the periodic basis where NOSQL database like DynamoDB commits data for every transaction this makes DynamoDB to be slower than redis. &lt;/p&gt;
+&lt;p&gt;However you can also make redis to commit for each query by changing their configuration.It will also decreases the performance of the redis.If you want &lt;code&gt;DynamoDB like Persistence&lt;/code&gt; What they are saying.,&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;The general indication is that you should use both persistence methods if you want a degree of data safety comparable to what PostgreSQL can provide you.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;If you care a lot about your data, but still can live with a few minutes of data loss in case of disasters, you can simply use RDB alone.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;There are many users using AOF alone, but we discourage it since to
+[K5]
+ some specialized for cache DB like Memcached or Redis. Also instead of a threshold in a form of length of &lt;code&gt;colors&lt;/code&gt; you may use some specialized cache library that support a LRU cache or &lt;a href="https://en.wikipedia.org/wiki/Cache_replacement_policies" rel="nofollow noreferrer"&gt;some other replacement police&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Finally if your logic is that the result for given set of colors is just a union of the results for each color, you may try to cover those rare big combinations of colors on the client side by caching results for each color alone and then if the color combination is not in cache directly, compute it by merging the items in the cached results for each color.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1853,10 +2442,21 @@
 By implementing these adjustments, you should achieve the desired behavior where all input fields and the button are visible when one of the EditText fields is focused, improving the user experience when logging in.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1963,10 +2563,125 @@
 By following these guidance points, you should be able to resolve the errors related to your Firebase and Android Support library dependencies effectively.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: "com.android.support:appcompat-v7:28.0.0" Error
+A: &lt;pre&gt;&lt;code&gt;implementation 'com.android.support:support-media-compat:28.0.0'
+implementation 'com.android.support:support-v4:28.0.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;add to dependencies and change &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:16.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;to &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:9.0.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This is working for me&lt;/p&gt;
+[K2]
+0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CONFIG_VERSION&amp;quot;: &amp;quot;21.2.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_VERSION&amp;quot;: &amp;quot;20.3.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_AUTH_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FIRESTORE_VERSION&amp;quot;: &amp;quot;24.4.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FUNCTIONS_VERSION&amp;quot;: &amp;quot;20.2.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_IID_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_INSTALLATIONS_VERSION&amp;quot;: &amp;quot;17.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_NDK_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_GSON_VERSION&amp;quot;: &amp;quot;2.9.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_GRADLE_PLUGIN_VERSION&amp;quot;: &amp;quot;1.4.2&amp;quot;,
+        &amp;quot;ANDROID_GRPC_OKHTTP&amp;quot;: &amp;quot;1.46.0&amp;quot;,
+        &amp;quot;IOS_USE_PRECOMPILED_FIRESTORE_POD&amp;quot;: &amp;quot;false&amp;quot;
+      },
+      &amp;quot;cordova-plugin-androidx-adapter&amp;quot;: {}
+    },
+    &amp;quot;platforms&amp;quot;: [
+      &amp;quot;browser&amp;quot;,
+      &amp;quot;ios&amp;quot;,
+      &amp;quot;android&amp;quot;
+    ]
+  }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;References:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://developer.apple.com
+[K3]
+Q: I keep receiving a gradle sync error when trying to add Firebase UI 2.3.0
+A: &lt;p&gt;Since you are using &lt;code&gt;com.android.support:customtabs:26.0.1&lt;/code&gt; you have to add in the &lt;code&gt;repositories&lt;/code&gt; the "&lt;a href="https://maven.google.com" rel="nofollow noreferrer"&gt;https://maven.google.com&lt;/a&gt;" endpoint.&lt;br&gt;
+All the support libraries since 25.4.0 are in the google maven repo as &lt;a href="https://developer.android.com/topic/libraries/support-library/revisions.html#25-4-0" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;In your case something like;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;allprojects {
+    repositories {
+        jcenter()
+        maven { url 'https://maven.fabric.io/public' }  // &amp;lt;= ADD THIS
+        maven {
+            url "https://maven.google.com"
+        }
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Also if you want to add the latest &lt;strong&gt;Firebase libraries v. 11.2.0&lt;/strong&gt; you have to add the same repo as &lt;a href="https://developers.google.com/android/guides/releases#august_2017_-_version_1120" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+[K4]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Error:Execution failed for task ':app:processDebugManifest'. &gt; Manifest merger failed
+A: &lt;p&gt;There are some mistakes:&lt;/p&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of Firebase and Google Play Services&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;Change:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:10.0.1'
+compile 'com.google.android.gms:play-services:10.0.1'
+compile 'com.google.firebase:firebase-storage:10.0.1'
+compile 'com.google.firebase:firebase-auth:11.0.1'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;using the latest version:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:11.4.2'
+compile 'com.google.android.gms:play-services:11.4.2'
+compile 'com.google.firebase:firebase-storage:11.4.2'
+compile 'com.google.firebase:firebase-auth:11.4.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of support libraries&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:appcompat-v7:26.1.0'
+compile 'com.android.support:support-v4:26.1.0'
+compile 'com.android.support:support-compat:26.1.0'
+compile 'com.android.support:cardview-v7:26.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FirebaseUI has dependency on a fixed version of firebase libraries.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Check &lt;a href="https://github.com/firebase/FirebaseUI-Android" rel="nofollow noreferrer"&gt;the table&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;For convenience, here are some examples:&lt;/p&gt;
+&lt;pre&gt;&lt;code</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2098,10 +2813,21 @@
 By following the above steps, you should be able to resolve the dependency issues and successfully build your project. If problems persist, please provide any additional error messages or logs that may help in diagnosing the problem further.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2238,10 +2964,21 @@
 If you're always going to have a large, non-scrollable form, you may not need a `CoordinatorLayout`. Conversely, if you anticipate future enhancements involving scrollable content or more complex interactions, keeping it makes sense.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2271,14 +3008,130 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover how to replace the V8 version in Google Chrome with a debug version that supports the "--print-code" option. They do not provide information on changing V8 builds within Chrome or specific instructions related to the assembly and bytecode generation in that context. 
+          <t>[catatan: informasi tidak tersedia] how to replace the V8 version in Google Chrome with a debug version that supports the "--print-code" option. They do not provide information on changing V8 builds within Chrome or specific instructions related to the assembly and bytecode generation in that context. 
 If you need assistance on any other related topics or general issues, please feel free to ask!</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: How to simulate JavaScript yield?
+A: &lt;p&gt;For a non-trivial generator function, you will want to use some sort of tool to translate your code to an ES3 equivalent so that it can run in any modern browser. I recommend trying out &lt;a href="http://traceur-compiler.googlecode.com/" rel="noreferrer"&gt;Traceur&lt;/a&gt;, which can roughly be described as an ES6-to-ES3 source translator. Because generators are a language feature destined for ES6, Traceur will be able to translate them for you.&lt;/p&gt;
+&lt;p&gt;Traceur provides a &lt;a href="http://traceur-compiler.googlecode.com/git/demo/repl.html" rel="noreferrer"&gt;demo page&lt;/a&gt; where you can type ES6 code and see the ES3 generated on the fly. If you enter something as simple as:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;// Note that this declaration includes an asterisk, as specified by current ES6
+// proposals. As of version 16, Firefox's built-in support for generator
+// functions does not allow the asterisk.
+function* foo() {
+  var n = 0;
+  if (n &amp;lt; 10) {
+    n++;
+    yield n;
+  }
+}
+for (var n of foo()) {
+  console.log(n); 
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;you will see that the equivalent ES3 code is non-trivial, and it requires &lt;code&gt;traceur.runtime&lt;/code&gt; to be included so that the code runs correctly in a browser. The runtime is defined in &lt;a href="http://traceur-compiler.googlecode.com/git/src/runtime/runtime.js" rel="noreferrer"&gt;http://traceur-compiler.googlecode.com/git/src/runtime/runtime.js&lt;/a&gt;, which is currently 14K (unminified). This is a non-trivial amount of code, though likely much of it can be optimized away using the Closure Compiler.&lt;/p&gt;
+&lt;p&gt;Note
+[K2]
+.prototype.entries.prototype&lt;/code&gt; as &lt;code&gt;true&lt;/code&gt;. This was tested on Edge versions 40, 41, 42, 44 using either BrowserStack.com or a VM Win10 machine.&lt;/p&gt;
+&lt;p&gt;Most other browsers execute the test as &lt;code&gt;false&lt;/code&gt;. Here is the list of browsers that execute false to this test:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Chrome v42&lt;/li&gt;
+&lt;li&gt;Chrome v79&lt;/li&gt;
+&lt;li&gt;FF v44&lt;/li&gt;
+&lt;li&gt;FF v73&lt;/li&gt;
+&lt;li&gt;Safari v10.1&lt;/li&gt;
+&lt;li&gt;Safari v13.0&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Back to the GitHub post from &lt;em&gt;dgraham&lt;/em&gt;. Some browsers do have native code for &lt;code&gt;fetch&lt;/code&gt; and &lt;code&gt;Headers&lt;/code&gt;, yet test false for &lt;code&gt;!!self.Headers.prototype.entries&lt;/code&gt;. Thus &lt;em&gt;dgraham&lt;/em&gt; is correct that we need to test for this. The list of browsers that I found tested &lt;code&gt;false&lt;/code&gt; when &lt;code&gt;!!self.Headers.prototype.entries&lt;/code&gt; is executed is:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Edge v40 (EdgeHTML 15.15063)&lt;/li&gt;
+&lt;li&gt;FF v40&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Sorry to be so long-winded. Here is the code that I wrapped the &lt;code&gt;fetch&lt;/code&gt; polyfill within:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;var loadPoly = false
+if(!self.fetch){loadPoly = true}
+if(!loadPoly &amp;amp;&amp;amp; !self.Headers.prototype.entries){loadPoly = true}
+if(!loadPoly &amp;amp;&amp;amp; !!self.Headers.prototype.entries.prototype){loadPoly = true}
+if(!!loadPoly){...
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+String.prototype.replaceAll&lt;/code&gt;.&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;The full config would thus be:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;{
+  &amp;quot;compilerOptions&amp;quot;: {
+    &amp;quot;allowSyntheticDefaultImports&amp;quot;: true,
+    &amp;quot;lib&amp;quot;: [&amp;quot;ES2022&amp;quot;],
+    &amp;quot;module&amp;quot;: &amp;quot;ES2022&amp;quot;,
+    &amp;quot;moduleResolution&amp;quot;: &amp;quot;node&amp;quot;,
+    &amp;quot;target&amp;quot;: &amp;quot;ES2022&amp;quot;
+  }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;In addition to this, we also need to tell Node.js to treat &lt;code&gt;.js&lt;/code&gt; files in this project as ES Modules. The reason for this is that Node.js had to maintain backwards compatibility with code written for older Node.js versions. This can be done by adding &lt;code&gt;&amp;quot;type&amp;quot;: &amp;quot;module&amp;quot;&lt;/code&gt; to your &lt;code&gt;package.json&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;{
+  &amp;quot;type&amp;quot;: &amp;quot;module&amp;quot;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Another change if you are coming from an earlier version of Node.js is that &lt;a href="https://nodejs.org/dist/latest-v18.x/docs/api/esm.html#esm_mandatory_file_extensions" rel="noreferrer"&gt;the file extensions when importing files are now mandatory&lt;/a&gt;. This means that you must write out &lt;code&gt;.js&lt;/code&gt; at the end of your local imports. Note that this is &lt;code&gt;.js&lt;/code&gt; even though you are importing a TypeScript file that actually has the file extension &lt;code&gt;.ts&lt;/code&gt;. This might seem a bit confusing but &lt;a href="https://github.com/microsoft/TypeScript/issues/35589#issuecomment-564644320" rel="noreferrer"&gt;this comment from one of the TS contributors explains why that
+[K4]
+Q: Why it is an error to ignore a rejected promise on Chrome?
+A: &lt;p&gt;Rejecting a promise basically means something bad happened, and that you should be handling it with a call to &lt;code&gt;catch&lt;/code&gt;. If you reject a promise without having a &lt;code&gt;catch&lt;/code&gt;, it will throw an exception (more accurately, an unhandled rejection) &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;var a = (new Promise((resolve, reject) =&amp;gt; {
+    reject("my error")
+})).catch((err) =&amp;gt; {
+    console.error(err)
+})
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;I'm guessing it is a specificity of V8 if this happens only under Chrome, but it makes sense to me&lt;/p&gt;
+[K5]
+Q: Can I somehow build webassembly code *without* the emscripten "glue"?
+A: &lt;p&gt;You can use emscripten to generate fairly minimal code output.&lt;/p&gt;
+&lt;p&gt;Consider the following trivial file &lt;code&gt;adder.c&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;int adder (int a, int b) {
+    return a + b;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Compile it like this (requires a fairly recent emscripten):&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;emcc -O2 -s WASM=1 -s SIDE_MODULE=1 -o adder.wasm
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;To see what it generated, disassemble it to wast textual form using binaryen's &lt;code&gt;wasm-dis&lt;/code&gt; (you can also use wasm2wast from wabt):&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;wasm-dis adder.wasm -o adder.wast
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;The disassembled source should look something like this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;(module
+ (type $0 (func (param i32 i32) (result i32)))
+ (type $1 (func))
+ (import "env" "memoryBase" (global $import$0 i32))
+ (import "env" "memory" (memory $0 256))
+ (import "env" "table" (table 0 anyfunc))
+ (import "env" "tableBase" (global $import$3 i32))
+ (global $global$0 (mut i32) (i32.const 0))
+ (global $global$1 (mut i32) (i32.const 0))
+ (export "__post_instantiate" (func $2))
+ (export "runPostSets" (func $1))
+ (export "_adder" (func $0))
+ (func $0 (type $0) (param $var$0 i32) (</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2309,13 +3162,126 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific details regarding the support of JDK 11 in AWS Lambda or the use of Corretto 11 with AWS Lambda. Therefore, I cannot provide a definitive answer to the question about AWS Lambda's support for JDK 11. If you need information on how to resolve deployment issues or further details regarding Java version compatibility in AWS Lambda, the context also does not provide any information related to that.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific details regarding the support of JDK 11 in AWS Lambda or the use of Corretto 11 with AWS Lambda. Therefore, I cannot provide a definitive answer to the question about AWS Lambda's support for JDK 11. If you need information on how to resolve deployment issues or further details regarding Java version compatibility in AWS Lambda, the context also does not provide any information related to that.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+$registerAndPromoteBean$1(AwsSecretsManagerConfigDataLocationResolver.java:113) ~[spring-cloud-starter-aws-secrets-manager-config-2.3.0-RC2.jar:2.3.0-RC2]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.doInvokeListener(SimpleApplicationEventMulticaster.java:176) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.invokeListener(SimpleApplicationEventMulticaster.java:169) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:143) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:131) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.boot.DefaultBootstrapContext.close(DefaultBootstrapContext.java:133) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.prepareContext(SpringApplication.java:392) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:325) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1311) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1300) ~[spring-boot-2.4.2.jar:2.4.2]
+        at com.brighttalk.service.securedsecrets
+[K2]
+Q: Tomcat fails to start using Eclipse, JRebel, and Spring Boot
+A: &lt;p&gt;JRebel cannot instrument class because &lt;em&gt;MBeanRegistrationSupport#setRegistrationBehavior&lt;/em&gt; method was removed by &lt;a href="https://github.com/spring-projects/spring-framework/commit/b5db5d3aac39ca7cff4ccca491652d9490a1d175#diff-c36e12d89e096da6108d667fb27b1c3dL165" rel="nofollow"&gt;b5db5d&lt;/a&gt; commit on spring-framework development branch.&lt;/p&gt;
+&lt;p&gt;We have updated our Spring integration and &lt;a href="https://zeroturnaround.com/software/jrebel/download/nightly-build/" rel="nofollow"&gt;JRebel Nighly build&lt;/a&gt; (choose standalone jar) should work fine.&lt;/p&gt;
+&lt;p&gt;Fix will be included in JRebel 6.5.2 which we plan to release next week.&lt;/p&gt;
+&lt;p&gt;Thank you for bug report, if you have any questions/issue please write to support@zeroturnaround.com.&lt;/p&gt;
+[K3]
+Q: SpringMVC XML error- Randomly
+A: &lt;p&gt;This kind of issue:&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;cvc-elt.1: Cannot find the declaration of element 'beans'.
+  root-context.xml /SwiftEmploymentMVC/src/main/webapp/WEB-INF/spring
+  line 3 XML Problem&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;generally is a &lt;strong&gt;dependency one&lt;/strong&gt;, that is caused by some &lt;strong&gt;missing classes&lt;/strong&gt;, themselves caused by using &lt;strong&gt;conflicting dependencies versions&lt;/strong&gt;.
+Even if you say everything is fine with your Apache server, you are using &lt;strong&gt;too much different versions for your Spring jars&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;By example, you use &lt;code&gt;spring-security-core&lt;/code&gt; in version &lt;code&gt;3.1.0.RELEASE&lt;/code&gt;, but &lt;code&gt;spring-security-config&lt;/code&gt; in version &lt;code&gt;4.0.3.RELEASE&lt;/code&gt;.
+Those jars are linked, and you are using 2 different major versions, which could be a problem.&lt;/p&gt;
+&lt;p&gt;If you don't know &lt;strong&gt;which dependencies versions are required by a jar&lt;/strong&gt;, have a look at &lt;a href="http://mvnrepository.com/" rel="nofollow"&gt;http://mvnrepository.com/&lt;/a&gt;.&lt;br&gt;
+It lists the different required dependencies by type.&lt;/p&gt;
+&lt;p&gt;If your case, I would suggest that you use your &lt;code&gt;org.springframework-version&lt;/code&gt; property for more (or all) of your Spring jars.&lt;/p&gt;
+[K4]
+Q: Error Creating Bean Error (Spring Cloud Config Client)
+A: &lt;p&gt;With help for Gregor, I was able to solve it. These are the changes I did:&lt;/p&gt;
+&lt;p&gt;I added a &lt;code&gt;messageConverter&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package com.gcp.logicalprovisioning.config.server;
+import org.slf4j.Logger;
+import org.slf4j.LoggerFactory;
+import org.springframework.beans.factory.annotation.Value;
+import org.springframework.boot.CommandLineRunner;
+import org.springframework.boot.SpringApplication;
+import org.springframework.boot.autoconfigure.EnableAutoConfiguration;
+import org.springframework.boot.autoconfigure.SpringBootApplication;
+import org.springframework.boot.autoconfigure.jdbc.DataSourceAutoConfiguration;
+import org.springframework.context.annotation.Bean;
+@SpringBootApplication
+@EnableAutoConfiguration(exclude={DataSourceAutoConfiguration.class})
+public class DemoClientApplication {
+    private static final Logger LOGGER = LoggerFactory.getLogger(DemoClientApplication.class);
+    public static void main(String[] args) {
+        SpringApplication.run(DemoClientApplication.class, args);
+    }
+    /**
+     * Output property from cloud-config-server on startup of app,
+     *
+     * also can be seen at:
+     * http://localhost:9090/env/APP.aaf.env
+     */
+    @Bean
+    public CommandLineRunner printProperties(@Value(&amp;quot;${APP.aaf.env}&amp;quot;) final String appProperty)  {
+        return args -&amp;gt; LOGGER.info(&amp;quot;APP.aaf.env is: [{}]&amp;quot;, appProperty);
+    }
+    @Bean
+    public RestTemplate restTemplate() {
+        final RestTemplate restTemplate = new RestTemplate();
+        List&amp;lt;HttpMessageConverter&amp;lt;?&amp;gt;&amp;gt; messageConverters = new ArrayList&amp;lt;&amp;gt;();
+        MappingJackson2HttpMessageConverter mappingJackson2HttpMessageConverter = new MappingJackson2HttpMessageConverter();
+        mappingJackson2HttpMessageConverter.setSupportedMediaTypes(Collections.singletonList(MediaType.ALL));
+        messageConverters.add(mappingJackson2HttpMessageConverter);
+        restTemplate.setMessageConverters(messageConverters
+[K5]
+Q: spring batch AsynchJob Launcher ,Error in setting job repo
+A: &lt;p&gt;Here is a working example made from &lt;a href="http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/" rel="nofollow"&gt;http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/&lt;/a&gt; and tested on wildfly 9.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;beans xmlns="http://www.springframework.org/schema/beans"
+       xmlns:batch="http://www.springframework.org/schema/batch" 
+       xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"
+       xsi:schemaLocation="http://www.springframework.org/schema/batch
+        http://www.springframework.org/schema/batch/spring-batch-2.2.xsd
+        http://www.springframework.org/schema/beans 
+        http://www.springframework.org/schema/beans/spring-beans-3.2.xsd
+    "&amp;gt;
+    &amp;lt;bean id="report" class="Report" scope="prototype" /&amp;gt;
+    &amp;lt;bean id="jobRepository"
+       class="org.springframework.batch.core.repository.support.MapJobRepositoryFactoryBean"&amp;gt;
+        &amp;lt;property name="transactionManager" ref="transactionManager" /&amp;gt;
+    &amp;lt;/bean&amp;gt;
+    &amp;lt;batch:job id="helloWorldJob"&amp;gt;
+        &amp;lt;batch:step id="step1"&amp;gt;
+            &amp;lt;batch:tasklet&amp;gt;
+                &amp;lt;batch:chunk reader="cvsItemReader" writer="xmlItemWriter"
+                                     commit-interval="10"&amp;gt;
+                &amp;lt;/batch:chunk&amp;gt;
+            &amp;lt;/batch:tasklet&amp;gt;
+        &amp;lt;/batch:step&amp;gt;
+    &amp;lt;/batch:job&amp;gt;
+    &amp;lt;bean id="jobLauncher"
+              class="org</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2379,24 +3345,181 @@
 To resolve this, you can explicitly specify the type of the listener you are adding. Since `StopListener` extends `StepListenerSupport`, you should utilize the appropriate method that takes a `StepListener` as a parameter. Here is how you can modify your code:
 ```java
 @Bean
-public Step dataFilterStep() {
+Public Step dataFilterStep() {
  return stepBuilderFactory.get("dataFilterStep")
- .&lt;UserInfo, UserInfo&gt;chunk(10)
- .reader(dataFilterItemReader())
- .processor(dataFilterItemProcessor())
- .writer(dataFilterWriter())
- .listener((StepExecutionListener) new StopListener()) // Explicitly cast to StepExecutionListener
- .build();
+.&lt;UserInfo, UserInfo&gt;chunk(10)
+.reader(dataFilterItemReader())
+.processor(dataFilterItemProcessor())
+.writer(dataFilterWriter())
+.listener((StepExecutionListener) new StopListener()) // Explicitly cast to StepExecutionListener
+.build();
 }
 ```
 By explicitly casting `StopListener` to `StepExecutionListener`, you clarify to the compiler which method overload you intend to use, thereby eliminating the ambiguity.
-Please verify that `StopListener` correctly implements the methods required from the `StepExecutionListener` interface to ensure proper functionality. The retrieved sources do not cover additional details or examples related to the use of `StepListenerSupport` or related listener implementations.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+Please verify that `StopListener` correctly implements the methods required from the `StepExecutionListener` interface to ensure proper functionality. [catatan: informasi tidak tersedia] additional details or examples related to the use of `StepListenerSupport` or related listener implementations.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+ }
+            }
+        }
+        protected void checkPauseState() {
+            while (paused.get()) {
+                pausedLock.lock();
+                try {
+                    pausedCondition.await();
+                } catch (InterruptedException ex) {
+                } finally {
+                    pausedLock.unlock();
+                }
+            }
+        }
+        protected void updateProgress(int progress) {
+            if (EventQueue.isDispatchThread()) {
+                pb.setValue(progress);
+            } else {
+                SwingUtilities.invokeLater(new Runnable() {
+                    @Override
+                    public void run() {
+                        updateProgress(progress);
+                    }
+                });
+            }
+        }
+        public  boolean isPaused() {
+            return paused.get();
+        }
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Make sure you make the time to read through &lt;a href="http://docs.oracle.com/javase/tutorial/essential/concurrency/" rel="nofollow"&gt;Concurrency in Java&lt;/a&gt;, especially the section on locks, and &lt;a href="http://docs.oracle.com/javase/tutorial/uiswing/concurrency/" rel="nofollow"&gt;Concurrency in Swing&lt;/a&gt;.&lt;/p&gt;
+[K2]
+Q: Getting away from BackgroundWorker towards TPL for a logging class
+A: &lt;p&gt;Right now your code isn't &lt;code&gt;thread-safe&lt;/code&gt; as you have this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public List&amp;lt;LogEvent&amp;gt; Events { get; private set; }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;List&amp;lt;T&amp;gt;&lt;/code&gt; isn't thread safe, and can be changed from outer code. And I can't see is it used at all.&lt;/p&gt;
+&lt;p&gt;Also, you really should use &lt;code&gt;CancellationToken&lt;/code&gt; in your code because of in other case you can get troubles: for example, you have 5 messages in queue, and you decide to cancel your work. In this case check for &lt;code&gt;Shutdown Log&lt;/code&gt; will break loop only after some time, which is confusing for end-user of your class.&lt;/p&gt;
+&lt;p&gt;Also, there is an overload for &lt;a href="https://msdn.microsoft.com/en-us/library/dd381908.aspx" rel="nofollow"&gt;&lt;code&gt;BlockingCollection&amp;lt;T&amp;gt;.Take&lt;/code&gt;&lt;/a&gt; Method with &lt;code&gt;CancellationToken&lt;/code&gt;, but in case of cancel you'll get to catch the &lt;code&gt;OperationCanceledException&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;try
+{
+    LogEvent anEvent = WriteQueue.Take(CancellationPending);
+}
+catch (OperationCanceledException ex)
+{
+    // handle stop here;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Infinite loop in very bad practice in multi-threading, I suggest not to use it.&lt;/p&gt;
+[K3]
+&gt;
+&lt;hr&gt;
+&lt;p&gt;There are some intent actions like NEW_OUTGOING_CALL AND BOOT_COMPLETED  which are excluded and can be implemented in receiver and placed in manifest like : &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public class MyReceiver extends BroadcastReceiver
+{
+@Override
+public void onReceive(Context context, Intent intent)
+{
+    Log.d("INSTA_BOOT : ", "\nBOOT_COMPLETE_EVENT_OF_INSTA....");
+    if (Build.VERSION.SDK_INT &amp;gt;= Build.VERSION_CODES.O)
+    {
+        context.startForegroundService(new Intent(context, WatchMan.class));
+    }
+    else
+    {
+        context.startService(new Intent(context, WatchMan.class));
+    }
+}
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;As i wanted to re-register or say want to restart foreground service on REBOOT OR BOOT-COMPLETE&lt;/p&gt;
+&lt;hr&gt;
+&lt;pre&gt;&lt;code&gt;CatchNumbers.java is a simple service which performs operation when receiver triggers perticular actions.
+&lt;/code&gt;&lt;/pre&gt;
+&lt;hr&gt;
+&lt;p&gt;It works good on every restart and as &lt;code&gt;android:excludeFromRecents="true"&lt;/code&gt; is not needed anymore as even if user removes it from &lt;code&gt;recents&lt;/code&gt; on Oreo it will restart the service as it is &lt;code&gt;STICKY&lt;/code&gt;. Hope it helps someone like me..!!&lt;/p&gt;
+[K4]
+ new GetContacts().execute();
+}
+private class GetContacts extends AsyncTask&amp;lt;Void, Void, Void&amp;gt; {
+    @Override
+    protected void onPreExecute() {
+        super.onPreExecute();
+        // Showing progress dialog
+        pDialog = new ProgressDialog(SingleContactActivity.this);
+        pDialog.setMessage("Please wait...");
+        pDialog.setCancelable(false);
+        // pDialog.setTitle("Post Details");
+        pDialog.show();
+    }
+    @Override
+    protected Void doInBackground(Void... arg0) {
+        // Creating service handler class instance
+        ServiceHandler sh = new ServiceHandler();
+        // Making a request to url and getting response
+        String jsonStr = sh.makeServiceCall(url, ServiceHandler.GET);
+        Log.d("Response: ", "&amp;gt; " + jsonStr);
+        if (jsonStr != null) {
+            try {
+                JSONObject jsonObj = new JSONObject(jsonStr);
+                // Getting JSON Array node
+                contacts = jsonObj.getJSONArray(TAG_CONTACTS);
+                // looping through All Contacts
+                JSONObject c = contacts.getJSONObject(0);
+                details = c.getString(TAG_POSTLINE);
+                imagepath = c.getString(TAG_Post_Img);
+                imagepath2 = c.getString(TAG_Post_Img_O);
+            } catch (JSONException e) {
+                e.printStackTrace();
+            }
+        } else {
+            Log.e("ServiceHandler", "Couldn't get any data from the url");
+        }
+        return null;
+    }
+    @Override
+    protected void onPostExecute(Void result) {
+        super.onPostExecute(result);
+        // Dismiss the progress dialog
+        if (pDialog.isShowing())
+            pDialog.dismiss();
+        /**/
+        TextView Details = (TextView) findViewById(R.id.details);
+        // Details.setText(details);
+        Details.setText(android.text.Html.fromHtml(details));
+    }
+}
+public class ServiceHandler {
+static String response = null;
+public final static int GET = 1;
+public final static int POST = 2;
+public ServiceHandler() {
+}
+/*
+ *
+[K5]
+ }
+}).ContinueWith(ex =&amp;gt; Logger.LogException(ex), TaskContinuationOptions.OnlyOnFaulted);
+&lt;/code&gt;&lt;/pre&gt;
+</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2433,10 +3556,61 @@
 By following these steps, you should be able to diagnose and potentially fix the "Stream does not support reading" error with Team Explorer. If the issue continues despite these interventions, further investigation into logs or configurations might be necessary.</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Cannot connect to my TFS project
+A: &lt;p&gt;It's a general situation (connectivity issue). To  narrow down this problem, try the following actions: &lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Check whether there is something useful in &lt;strong&gt;Event View&lt;/strong&gt; on your TFS
+server&lt;/li&gt;
+&lt;li&gt;Give a try with directly using IP address instead of server name when
+you are adding Team Foundation Sever in VS2017. Something like:
+&lt;code&gt;http://192.168.0.1:8080/tfs&lt;/code&gt;&lt;/li&gt;
+&lt;li&gt;Login in tfs &lt;strong&gt;web portal&lt;/strong&gt; in web browser on your develop machine to see
+if it's only a VS related issue&lt;/li&gt;
+&lt;li&gt;Run VS2017 in Administrator Mode. &lt;/li&gt;
+&lt;li&gt;Turn off your firewall temporarily, disable anti-virus software.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;For more ways to trouble shooting please take a look at this blog: &lt;a href="https://www.visualstudio.com/team-services/support/cant-connect-team-foundation-server/" rel="nofollow noreferrer"&gt;TF31002: Unable to connect to this Team Foundation Server&lt;/a&gt;&lt;/p&gt;
+[K2]
+Q: Significant Build Time Difference between Local and Remote Teams on Visual Studio
+A: &lt;p&gt;Not sure about &lt;code&gt;1.&lt;/code&gt;. ProcExp from Sysinternals may help&lt;/p&gt;
+&lt;p&gt;My main suggestion is that for &lt;code&gt;2.&lt;/code&gt;, &lt;code&gt;3.&lt;/code&gt; and &lt;code&gt;4.&lt;/code&gt;, you need to build with binary logs enabled and then you can really investigate what is taking up any part of the build with a tool called [MSBuild Structured Log Viewer].(&lt;a href="https://msbuildlog.com/" rel="nofollow noreferrer"&gt;https://msbuildlog.com/&lt;/a&gt;)&lt;/p&gt;
+&lt;p&gt;It's intimidating to look at binlogs because there is so much data but it will help you quickly narrow down what is going wrong.&lt;/p&gt;
+[K3]
+Q: VS 2005 Test Project Not Opening
+A: &lt;p&gt;VS 2005 Professional did not support Test projects (VS 2008 Pro &lt;em&gt;does&lt;/em&gt; support Test projects).  For VS 2005 with unit testing, you would have needed Test Edition or Team Suite.&lt;/p&gt;
+[K4]
+Q: TFS 2015.3 custom build step not sending variables to the script
+A: &lt;p&gt;Apparently I wasn't following closely enough... I missed the warning on &lt;a href="https://blogs.infosupport.com/custom-build-tasks-in-tfs-2015/" rel="noreferrer"&gt;this page&lt;/a&gt;:&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;&lt;strong&gt;Words of warning&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Tasks can be versioned, use this to your advantage. All build definitions use the latest available version of a specific task, you can’t change this behavior from the web interface, so always assume the latest version is being used.&lt;/p&gt;
+&lt;p&gt;If you don’t change the version number of your task when updating it, the build agents that have previously used your task will not download the newer version because the version number is still the same. This means that if you change the behavior of your task, you should always update the version number!&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Once I got that all straightened out, everything worked fine.&lt;/p&gt;
+[K5]
+Q: Agent.ToolsDirectory is not set error while running yarn task in TFS server 2015. How can I fix it?
+A: &lt;p&gt;"Agent.ToolsDirectory" variable was added from build agent version: 2.115.0 which is available after TFS2017 Update 1.&lt;/p&gt;
+&lt;p&gt;TFS2015 use the legacy 1.x agent which does not support this variable. Refer to this link for details: &lt;a href="https://github.com/Microsoft/vsts-task-lib/blob/master/node/docs/minagent.md#variables" rel="nofollow noreferrer"&gt;Variables&lt;/a&gt;.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2574,10 +3748,21 @@
 While there is no direct integration for reading GRASS layers into GeoPandas, your current approach is quite effective. The improved method further cleans up your logic, making it clearer and easier to maintain while ensuring good practices around resource management.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2672,10 +3857,189 @@
 This structure will allow Jest to handle the asynchronous nature of the calls and properly catch errors when they arise, as suggested by the practices discussed in regarding error handling with promises.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: unable to fix Unhandled Rejection error -
+A: &lt;p&gt;First, you should return your fetch request in your Promise.&lt;/p&gt;
+&lt;p&gt;Also, maybe i'm wrong but this error handling is much as needed :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;   }, error =&amp;gt; onFailure({error})
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You have already :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;).catch(e =&amp;gt; onFailure(e))
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;I think you can test it like that :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;const get = (query: Query) =&amp;gt; {
+   return new Promise((resolve, reject) =&amp;gt; {
+        //Is query.url() a request ? it can be the one which failed also.
+        return fetch(query.url(), {
+            method: 'GET',
+            headers: new Headers(),
+            mode: 'no-cors'
+        })
+        .then(response =&amp;gt; {
+            if (!response.ok) { 
+               throw Error(response.statusText) 
+            }
+            return resolve(response.json())
+        })
+        .catch(e =&amp;gt; reject(e))
+    })
+    // And also if the child request failed, your parent Promise will fail so you have to catch it well
+    .catch(e =&amp;gt; {console.log(e)})
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;EDIT: I forgot something, if you use &lt;code&gt;throw&lt;/code&gt; in a child callback, it will not work for sure every times, so maybe the &lt;code&gt;.catch&lt;/code&gt; after the &lt;code&gt;throw&lt;/code&gt; is never called, try to use &lt;code&gt;reject&lt;/code&gt; instead of &lt;code&gt;throw&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Like this :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;const get = (query: Query) =&amp;gt; {
+   return new Promise((resolve, reject) =&amp;gt; {
+        //Is query.url() a request ? it can be the one which failed also.
+        return fetch(query
+[K2]
+Q: Why is my terminal being spammed non-stop with the same error?
+A: &lt;p&gt;Instead of converting the promises that &lt;code&gt;node-fetch&lt;/code&gt; gives you back to callback style&lt;sup&gt;1&lt;/sup&gt;, you should embrace promises and use simple &lt;code&gt;async&lt;/code&gt;/&lt;code&gt;await&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;const fetch = require('node-fetch');
+async function script(keyword) {
+  const response = await request('https://hacker-news.firebaseio.com/v0/newstories.json?print=pretty');
+  let obj = await respose.json();
+  for (let i = 0; i &amp;lt; obj.length; i++) {
+    const response = request(`https://hacker-news.firebaseio.com/v0/item/${obj[i]}.json?print=pretty`);
+    const myData = response.json();
+    const s = moment.unix(myData.time).format('LLLL');
+    const link = `https://news.ycombinator.com/item?id=${myData.id}`;
+    if (myData.title.includes(keyword)) {
+      client.hmset(&amp;quot;requestedData&amp;quot;, {Title: myData.title, Upvotes: myData.score, Date: s, URL: link})
+      const reply = await new Promise((resolve, reject) =&amp;gt; {
+        client.hgetall(&amp;quot;requestedData&amp;quot;, function(err, reply) {
+          if (err) reject(err);
+          else resolve(reply);
+        });
+      });
+      console.log(reply)
+    }
+  }
+}
+script(&amp;quot;Software&amp;quot;).catch(console.error);
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;sub&gt;1: Your &lt;code&gt;cb&lt;/code&gt; was throwing some exception which was not handled anywhere, and rejected the promise that you ignored.&lt;/sub&gt;&lt;/p&gt;
+[K3]
+ clientStartPromise = client.start({
+            phoneNumber: phoneNumber,
+            password: async () =&amp;gt; {return password},
+            phoneCode: async () =&amp;gt; {
+                let code = await globalPhoneCodePromise.promise;
+                globalPhoneCodePromise = generatePromise();
+                return code;
+            },
+            onError: (err) =&amp;gt; {
+                console.log(err)
+                res.json({
+                    &amp;quot;status&amp;quot;: &amp;quot;error&amp;quot;,
+                    &amp;quot;setupStep&amp;quot;: 9,
+                    &amp;quot;message&amp;quot;: err
+                })
+            },
+        });
+        res.json({
+            &amp;quot;status&amp;quot;: &amp;quot;ok&amp;quot;,
+            &amp;quot;setupStep&amp;quot;: 1
+        })
+    } else if(setupStep == 2){
+        globalPhoneCodePromise.resolve(obtainedCode);
+        clientStartPromise.then(async () =&amp;gt; {
+            console.log(client.session.save());
+            console.log(&amp;quot;You should now be connected.&amp;quot;);
+            credentials = {
+                &amp;quot;apiId&amp;quot;: apiId,
+                &amp;quot;apiHash&amp;quot;: apiHash,
+                &amp;quot;stringSession&amp;quot;: client.session.save()
+            }
+            fs.writeFileSync(credentialsPath, JSON.stringify(credentials));
+            await client.sendMessage(&amp;quot;me&amp;quot;, { message: &amp;quot;Setup Completed!&amp;quot; });
+            res.json({
+                &amp;quot;status&amp;quot;: &amp;quot;ok&amp;quot;,
+                &amp;quot;setupStep&amp;quot;: 2
+            })
+        }).catch(err =&amp;gt; {
+            res.json({
+                &amp;quot;status&amp;quot;: &amp;quot;error&amp;quot;,
+                &amp;quot;setupStep&amp;quot;: 2,
+                &amp;quot;message&amp;quot;: err
+            })
+        })
+    }
+})
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Note: If you had tried a lot of times authenticating (testing with a wrong code
+[K4]
+Q: Unhandled rejection SequelizeUniqueConstraintError: Validation error
+A: &lt;p&gt;The call to &lt;code&gt;User.create()&lt;/code&gt; is returning a &lt;code&gt;Promise.reject()&lt;/code&gt;, but there is no &lt;code&gt;.catch(err)&lt;/code&gt; to handle it. Without catching the error and knowing the input values it's hard to say what the validation error is - the &lt;code&gt;request.body.email&lt;/code&gt; could be too long, etc.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&lt;em&gt;Catch the Promise reject to see the error/validation details&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;User.create({ name: request.body.email })
+.then(function(user) {
+    // you can now access the newly created user
+    console.log('success', user.toJSON());
+})
+.catch(function(err) {
+    // print the error details
+    console.log(err, request.body.email);
+});
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;&lt;em&gt;Update, since it's 2019 and you can use async/await&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;try {
+  const user = await User.create({ name: request.body.email });
+  // you can now access the newly created user
+  console.log('success', user.toJSON());
+} catch (err) {
+  // print the error details
+  console.log(err, request.body.email);
+}
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+ (error) =&amp;gt; {
+    const status = error.response?.status;
+    // Если токен истек, пытаемся обновить его
+    if (status === 401) {
+      try {
+        const newAccessToken = await refresh();
+        if (newAccessToken) {
+          error.config.headers.Authorization = `Bearer ${newAccessToken}`;
+          return service.request(error.config); // Повторяем запрос
+        }
+      } catch (refreshError) {
+        destroyToken();
+        window.location.replace('/logout');
+        return Promise.reject(refreshError);
+      }
+    }
+    // Если статус ошибки не определен
+    if (!status) {
+      console.error('Network error or server is unreachable');
+    }
+    return Promise.reject(error);
+  }
+);
+export { service, saveToken, destroyToken, refresh };
+&lt;/code&gt;&lt;/pre&gt;
+&lt;br/&gt;
+&lt;h4&gt;In my case sometimes error.response was undefined, so that is why I first updated access token if there is and error then logout&lt;/h4&gt;
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2724,10 +4088,87 @@
 If you troubleshoot these aspects and the issue persists, consider providing more detailed logs or messages produced during the rendering of your R Markdown file for further assistance.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Scraping Wikipedia with R to make a list and a data frame
+A: &lt;p&gt;A possibility is to use regular expressions. I've never done that with R but the library stringr seems to be recommended:
+&lt;a href="https://stackoverflow.com/questions/2192316/extract-a-regular-expression-match-in-r-version-2-10"&gt;Extract a regular expression match in R version 2.10&lt;/a&gt; ( &lt;a href="http://cran.r-project.org/web/packages/stringr/stringr.pdf" rel="nofollow noreferrer"&gt;http://cran.r-project.org/web/packages/stringr/stringr.pdf&lt;/a&gt; )&lt;/p&gt;
+&lt;p&gt;EDIT: Code that appears to work for me&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;library(XML)
+library(RCurl)
+options(RCurlOptions = list(cainfo = system.file("CurlSSL", "cacert.pem", package = "RCurl")))
+library(stringr)
+path&amp;lt;-"https://fr.wikipedia.org/wiki/Jeux_olympiques_d%27hiver_de_2010"
+webpage &amp;lt;- getURL(path)
+webpage &amp;lt;- readLines(tc &amp;lt;- textConnection(webpage)); close(tc)
+pagetree &amp;lt;- htmlTreeParse(webpage, error=function(...){}, useInternalNodes = TRUE, encoding = "UTF-8")
+# Extract table header and contents
+tablehead &amp;lt;- xpathSApply(pagetree, "//*/table/tr", xmlValue)
+country&amp;lt;-tablehead[31]
+country&amp;lt;-strsplit(country,"\n")
+# extract country
+bar &amp;lt;- function(x) str_trim(str_extract(x, "[^(]*"), side = "both")
+res1 &amp;lt;- sapply(country[[1]], bar)    
+# extract nb of athletes
+foo &amp;lt;- function(x) str_trim(str_match(x, "\\((.*?)\\)")[[2]], side = "both")
+res2 &amp;lt;- sapply(country[[
+[K2]
+Q: Charset for foreign languages
+A: &lt;p&gt;I suggest using UTF-8, that can encode any Unicode character.&lt;/p&gt;
+&lt;p&gt;But apart from declaring the encoding in the document itself, it’s more important that your code is actually encoded in UTF-8. So get yourself a editor that can handle this encoding properly and declare the encoding in the HTTP header as it has a &lt;a href="http://www.w3.org/TR/html4/charset.html#spec-char-encoding" rel="nofollow noreferrer"&gt;higher priority&lt;/a&gt;.&lt;/p&gt;
+[K3]
+code&gt;raise&lt;/code&gt; without an exception argument? That syntax is only allowed inside an &lt;code&gt;except&lt;/code&gt; block, and raises the exception currently being handled.  It doesn't work outside an &lt;code&gt;except&lt;/code&gt; block.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://github.com/brack3t/Djrill/issues/1" rel="nofollow"&gt;An open issue&lt;/a&gt; in Djrill mentions a send failure and links a fork that supposedly fixes it.  I suspect Djrill isn't well supported and you might try that fork or another solution entirely.&lt;/p&gt;
+[K4]
+Q: JSON Specification and usage of BOM/charset-encoding
+A: &lt;h2&gt;You are right&lt;/h2&gt;
+&lt;ol&gt;
+&lt;li&gt;&lt;strong&gt;The BOM character is illegal in JSON&lt;/strong&gt; (and not needed)&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;The MIME charset is illegal in JSON&lt;/strong&gt; (and not needed as well)&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;&lt;a href="https://www.rfc-editor.org/rfc/rfc7159#section-8.1" rel="noreferrer"&gt;RFC 7159, Section 8.1&lt;/a&gt;:&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;&lt;strong&gt;Implementations MUST NOT add a byte order mark to the beginning of a JSON text.&lt;/strong&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;This is put as clearly as it can be. This is the only &amp;quot;MUST NOT&amp;quot; in the entire RFC.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.rfc-editor.org/rfc/rfc7159#section-11" rel="noreferrer"&gt;RFC 7159, Section 11&lt;/a&gt;:&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;The MIME media type for JSON text is application/json.&lt;br/&gt;
+Type name:  application&lt;br/&gt;
+Subtype name:  json&lt;br/&gt;
+Required parameters:  n/a&lt;br/&gt;
+Optional parameters:  n/a&lt;br/&gt;
+[...]&lt;br/&gt;
+Note:  &lt;strong&gt;No &amp;quot;charset&amp;quot; parameter is defined for this registration.&lt;/strong&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;h2&gt;JSON encoding&lt;/h2&gt;
+&lt;p&gt;The only valid encodings of JSON are UTF-8, UTF-16 or UTF-32 and since the first character (or first two if there is more than one character) will always have a Unicode value lower than 128 (there is no valid JSON text that can include higher values of the first two characters) it is always possible to know which of the valid encodings and which endianness was used just by looking at the byte stream.&lt;/p&gt;
+&lt;h
+[K5]
+Q: wget: Unsupported scheme on non-http URL
+A: &lt;p&gt;wget for windows doesn't support https&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;unsupported scheme&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;tested : GNU Wget 1.9.1, a non-interactive network retriever&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2843,10 +4284,21 @@
 By implementing this structure, you will have a flexible and scalable way to handle contributions that can accommodate your various use cases effectively.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2894,10 +4346,21 @@
 By following these guidelines, you should be able to fix the issue and structure your code according to the best practices of the Flex framework.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2939,15 +4402,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover detailed steps for installing NumPy specifically on Python 3.3.5 on Mac OSX 10.9. However, one of the sources mentions that if you want to install Python and some commonly used libraries like NumPy and Matplotlib, using Anaconda is highly recommended, as it simplifies the installation process and automatically includes many useful libraries (SO-42096280). 
-If you're determined to install NumPy without using Anaconda, typically using `pip` would be the go-to method, which is not discussed in the provided sources, but is common practice. You can try running the command `pip install numpy` in your terminal after ensuring you have installed Python and pip correctly.
-If issues persist, I would suggest checking whether you need to install Xcode command line tools that help with building packages from source. Again, specific steps to troubleshoot or fix errors related to building or the `setup.py` file were not covered in the retrieved context.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] detailed steps for installing NumPy specifically on Python 3.3.5 on Mac OSX 10.9. However, one of if you want to install Python and some commonly used libraries like NumPy and Matplotlib, using Anaconda is highly recommended, as it simplifies the installation process and automatically includes many useful libraries (SO-42096280). 
+If you're determined to install NumPy without using Anaconda, typically using `pip` would be the go-to method, which is not discussed, but is common practice. You can try running the command `pip install numpy` in your terminal after ensuring you have installed Python and pip correctly.
+If issues persist, I would suggest checking whether you need to install Xcode command line tools that help with building packages from source. Again, specific steps to troubleshoot or fix errors related to building or the `setup.py` file were not covered.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: Why pypy is not recognizing my python 2.7/3.4 modules and packages?
+A: &lt;p&gt;PyPy 2.4 is a rather outdated version which contains no support for numpy (even if you tried to install it separately).&lt;/p&gt;
+&lt;p&gt;In any case it is very unlikely that even a brand-new version of PyPy would reduce the memory usage of a numpy-heavy program.&lt;/p&gt;
+&lt;p&gt;If you're hitting MemoryError at the scale of ~1-3GB of data in a single process, on a 32-bit OS, then it seems clear to me that you need a 64-bit OS.&lt;/p&gt;
+[K2]
+&lt;/strong&gt;: As discussed in the chat: The error was due to the conda env ignoring the CC variable. After installing python+pip via homebrew and the required python packages via pip, this answer's steps worked for the OP.&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;All in all, here's a setup.py that worked for me (macOS 10.5.7, gcc-10):&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;try:
+    from setuptools import setup
+except ImportError:
+    from distutils.core import setup
+from distutils.extension import Extension
+from Cython.Build import cythonize
+from torch.utils.cpp_extension import BuildExtension, CppExtension, CUDAExtension
+import numpy
+# Get the numpy include directory.
+numpy_include_dir = numpy.get_include()
+# Extensions
+# pykdtree (kd tree)
+pykdtree = Extension(
+    'im2mesh.utils.libkdtree.pykdtree.kdtree',
+    sources=[
+        'im2mesh/utils/libkdtree/pykdtree/kdtree.c',
+        'im2mesh/utils/libkdtree/pykdtree/_kdtree_core.c'
+    ],
+    language='c',
+    extra_compile_args=['-std=c99', '-O3', '-fopenmp'],
+    extra_link_args=['-lgomp'],
+    include_dirs=[numpy_include_dir]
+)
+# mcubes (marching cubes algorithm)
+mcubes_module = Extension(
+    'im2mesh.utils.libmcubes.mcubes',
+    sources=[
+        'im2mesh/utils/libmcubes/mcubes.pyx',
+        'im2mesh/utils/libmcubes/pywrapper.cpp',
+        'im2mesh/utils/libmcubes/marchingcubes.cpp'
+    ],
+    language='c++',
+    extra_compile_args=['-std=c++11'],
+    include_dirs=[numpy_include_dir]
+)
+# triangle hash (efficient mesh intersection)
+triangle_hash_module = Extension(
+[K3]
+Q: Google foo.bar Challenge Issue: Can't import libraries
+A: &lt;p&gt;Unfortunately numpy is not a standard library in python 2.7, and is not supported by foobar.  For a complete list of available modules, I suggest looking here: &lt;a href="https://docs.python.org/2/library/" rel="noreferrer"&gt;https://docs.python.org/2/library/&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: How is Anaconda related to Python?
+A: &lt;p&gt;Anaconda is a Python-based data processing and scientific computing platform. It has built in many very useful third-party libraries. Installing Anaconda is equivalent to automatically installing Python and some commonly used libraries such as Numpy, Pandas, Scrip, and Matplotlib, so it makes the installation so much easier than regular Python installation. If you don't install Anaconda, but instead only install Python from python.org, you also need to use pip to install various libraries one by one. It is painful and you need to consider compatibility, thus it is highly recommended to directly install Anaconda.&lt;/p&gt;
+[K5]
+Q: dpkg error: pycompile: not found
+A: &lt;p&gt;(EDIT: works in Python 3.11 down to 3.5)&lt;/p&gt;
+&lt;p&gt;Ahhhh, yes.  The venerable &amp;quot;Catch-22&amp;quot; situation of Debian package management.  It boils down to Debian depending on &lt;code&gt;py3compile&lt;/code&gt; as part of the &lt;code&gt;libpython3.x&lt;/code&gt; package when that package provides the &lt;code&gt;py3compile&lt;/code&gt; as well; it's a no-go, there.&lt;/p&gt;
+&lt;p&gt;I too was bitten by this unable to get &lt;code&gt;py3compile&lt;/code&gt; working again for I had too deleted the entire /usr/[/local]/lib/python3* directories.&lt;/p&gt;
+&lt;p&gt;Once done, nothing in Debian package management tool can help you get back to a working Python3 environment.  You must do meat-ball surgery.&lt;/p&gt;
+&lt;p&gt;Reconstruction of Python3 in Debian entails three critical things:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Restoring &lt;code&gt;py3compile&lt;/code&gt; script (for most of you, you already have this)&lt;/li&gt;
+&lt;li&gt;Restoring libpython3.7&lt;/li&gt;
+&lt;li&gt;Restoring python binary&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;One could do the RE-copying of /usr[/local]/lib directory from another working Debian host/system. But this time, I shall detail the steps from within the broken host in question (as if you do NOT have another working host).&lt;/p&gt;
+&lt;h1&gt;Step 1 - Download Packages&lt;/h1&gt;
+&lt;p&gt;Download the impacted Debian packages:&lt;/p&gt;
+&lt;pre class="lang-bash prettyprint-override"&gt;&lt;code&gt;cd /tmp
+apt-get download libpython3.7-minimal
+apt-get download python3.7-minimal
+apt-get download python3-minimal # (this is important)
+apt-get download libpython3.7-stdlib</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2984,21 +4534,65 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>To port your JavaScript application into Silverlight while maintaining the document management functionality you described, you can consider the following suggestions based on the provided context:
+          <t>To port your JavaScript application into Silverlight while maintaining the document management functionality you described, you can consider the following suggestions:
 1. **Universal Generator vs. Document Type-specific Generators**: You are correct in identifying the two options for generating forms:
  - Creating one universal generator for both editing and viewing forms could simplify your application but would require a robust metadata mechanism to define styles and handling for various document types dynamically. This idea is akin to "inventing a new CSS," where you'd dictate the presentation rules based on the document type and possibly leveraging XAML capabilities.
  - Alternatively, maintaining a specific generator for each document type (as in your current system) would allow for more granular control but could lead to complexity with frequent changes. Given that you want to avoid recompilation and streamline the addition of document types, the first option with a universal generator might align better with your needs, although it would require significant design upfront to accommodate different styles and behaviors.
 2. **XSLT Support in Silverlight**: Silverlight does not natively support XSLT as JavaScript does, which means you'll need to find a way to implement the transformation logic that was previously handled by XSLT in your JavaScript application. You could use C# to perform the transformations manually, reading your XML documents and applying the necessary rules to produce XAML. This approach would necessitate coding equivalent filtering and transformation logic typically achieved with XSLT.
 3. **Dynamic Assembly Loading**: Your prototype, where each generator is stored in a separate assembly and loaded dynamically, is an interesting strategy. While it offers modularity, it could become unwieldy as the number of document types increases. If you opt to retain this approach, consider creating a more generalized loader that could handle patterns of document types efficiently, thereby reducing the load and management work involved.
 4. **Design Metadata File**: If you decide to go with the universal generator approach, developing a metadata file to define how forms should be generated is plausible. This metadata can specify aesthetics (like styles and layouts) and functional behaviors (e.g., what fields are necessary for each document type). You may want to consider a format that allows for easy updates, possibly leveraging XML or JSON for structure.
-5. **Error Handling and Contextual Work**: Keep in mind that when loading XAML programmatically, each interaction might require the context of how elements interrelate, as Silverlight has restrictions compared to the JavaScript environment. You need to ensure that the components you load can reference their event handlers and associated logic correctly, as indicated in the context about XAML files and serialization issues .
+5. **Error Handling and Contextual Work**: Keep in mind that when loading XAML programmatically, each interaction might require the context of how elements interrelate, as Silverlight has restrictions compared to the JavaScript environment. You need to ensure that the components you load can reference their event handlers and associated logic correctly, about XAML files and serialization issues.
 By addressing these areas, you should be able to port your JavaScript application into Silverlight more effectively while keeping the capability to handle various document types dynamically.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: The perfect web UI framework (with Microsoft stack?) - architecture question?
+A: &lt;p&gt;SilverLight would give you the compile-time support and wouldn't have you writing "script".&lt;/p&gt;
+[K2]
+Q: Business web-app in .NET - which technology to pick?
+A: &lt;p&gt;if you're planning to support iphone/android/non-win, then say goodbye to silverlight. then again if you're planning to support smartphones, you'd need to do separate designs for small vs large form factor devices. dockable interfaces are too cluttered for small devices.&lt;/p&gt;
+&lt;p&gt;Technology? HTML5 would be nice but only recent browsers support it, and even then only support bits &amp;amp; pieces of the standard.&lt;/p&gt;
+&lt;p&gt;MVC vs webforms? doesn't really matter. both just a way of spitting out HTML.&lt;/p&gt;
+&lt;p&gt;You'll need to do some "screwing around with Javascript or non-server technologies". Telerik offer a lot of the components you mentioned for webforms, though they do tend to bloat. &lt;/p&gt;
+&lt;p&gt;Based lightly on what your requirements are:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;list views: native in webforms/mvc&lt;/li&gt;
+&lt;li&gt;tree views: telerik, or a jQuery plugin&lt;/li&gt;
+&lt;li&gt;grids: native html tables work best IMO, or you can do do a databound something in asp.net or telerik&lt;/li&gt;
+&lt;li&gt;charts: free plugin, telerik, dundas, or something like SSRS if you have something of a reporting nature&lt;/li&gt;
+&lt;li&gt;docking ui: reconsider your need for this. If you're still keen asp.net has webparts built in or you can get a package from jQuery UI&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;overall you may be looking for a "quick" way to web-enable your app, but they are two different beasts and will perform as such. if you do a straight conversion using every plugin available, it will take you a lot of time to learn each component, a lot of page bloat, a lot of bugs, and it will never feel right. my suggestion is to invest the same time learning
+[K3]
+Q: Alternatives to Multiple Listboxes?
+A: &lt;p&gt;Why do you say Silverlight only supports Windows?  It's great on Macs as well!&lt;/p&gt;
+[K4]
+Q: Serialization in Silverlight
+A: &lt;p&gt;It looks like you are trying to serialize individual parts of a XAML file using XamlReader.Load on individual snippets of XML. That will not work as you are not including the XML namespaces (e.g. from the parent page). &lt;/p&gt;
+&lt;p&gt;Each piece of Xaml you load needs to be self-contained (as if it were a page itself). &lt;/p&gt;
+&lt;p&gt;If you also have events defined in controls within the XAML, that would explain the &lt;code&gt;Event handler is not supported by XamlReader&lt;/code&gt; error message as the loader has no context in which to work out what code-behind belongs to the Xaml (as there is no code-behind using load).&lt;/p&gt;
+[K5]
+Q: Silverlight and Java end of life in various browsers
+A: &lt;p&gt;Not sure about Firefox, but MS does not support Silverlight in Spartan as of the current preview build but will continue supporting the plugin in IE 11 desktop mode.  The end of life support on Silverlight is dated on 10/12/2021 for V5 - &lt;a href="https://support.microsoft.com/en-us/lifecycle/search/default.aspx?alpha=Silverlight&amp;amp;Filter=FilterNO" rel="nofollow"&gt;link&lt;/a&gt;&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3034,10 +4628,74 @@
 In summary, instead of using `addChild()`, leverage `addElement()` for adding elements in Flex containers to align with the framework's design principles.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Migrating to Flex mxmlc from ActionScript 2 mtasc
+A: &lt;p&gt;I don't think I can answer all of your question, but I'll try to provide some answers:&lt;/p&gt;
+&lt;p&gt;ActionScript 3 is a substantial change from ActionScript 2. Its a complete architectural overhaul, not just a minor update and its not backwards compatible, so short of a re-write, its usually pretty difficult to tweak non-trivial as2 to compile as as3. It's pretty much like an entirely new language . So it might be best to take a step back and see whats changed in the language, because it's a lot. &lt;/p&gt;
+&lt;p&gt;The biggest thing is the formalized &lt;a href="http://help.adobe.com/en_US/ActionScript/3.0_ProgrammingAS3/WS5b3ccc516d4fbf351e63e3d118a9b90204-7f36.html" rel="nofollow"&gt;class inheritance&lt;/a&gt;, over prototypical inheritance.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;"Flash will simply create an instance of the "main class"', whatever that is."&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;So, when you compile from the command-line, you give it the path to the "main class":&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;mxmlc.exe "c:\dev\project\SomeClass.as"&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;with &lt;code&gt;SomeClass.as&lt;/code&gt; looking like this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package {
+    import flash.display.Sprite;
+    public class SomeClass extends Sprite {}
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Upon initialization, flash will create an instance of this class and attach it to the stage. This will be the similar to the AS2 concept of &lt;code&gt;_root&lt;/code&gt;. The &lt;code&gt;-src&lt;/code&gt; switch passed to &lt;code&gt;mxmlc.exe&lt;/code&gt; sets the path to the rest
+[K2]
+Q: Exact difference between add-ons, plugins and extensions
+A: &lt;p&gt;General rule of thumb:&lt;/p&gt;
+&lt;h2&gt;Plugins&lt;/h2&gt;
+&lt;p&gt;When you're talking about a web browser, a plugin talks about a NPAPI or similar plugin, which is specific to the page. IE doesn't support "plugins" per se, but they have activex controls which can fill a similar function, though there are also BHO (Browser Helper Object) ActiveX controls which are more similar to extensions.  Thus we (the FireBreath team) usually use the term "plugin" to refer to something that works like a NPAPI plugin and the term "extension" to refer to something that works like a typical extension (firefox XPI, Chrome CRX, etc).&lt;/p&gt;
+&lt;p&gt;Plugins only know about the page they are in; they don't know anything else about the browser or what is loaded in other pages.&lt;/p&gt;
+&lt;p&gt;Plugins have been responsible for a lot of security problems, since they actually run native code.  This has led to a lot of discrimination against them -- much of it deserved.  Because of this, and because NPAPI is a royal pain in the neck (hence FireBreath was created), most browsers are trying to phase out plugins.  Plugins should never be used unless there is no other way to solve your problem.&lt;/p&gt;
+&lt;p&gt;That said, there are a lot of cases where they are the only option.&lt;/p&gt;
+&lt;h2&gt;Extensions&lt;/h2&gt;
+&lt;p&gt;An extension is something that is specific to the browser, and they are a bit different on each browser, but tend to be able to learn more about the overall state of the browser; they may be automatically added to pages, accessible separately from a page, etc.&lt;/p&gt;
+&lt;h2&gt;Add-ons&lt;/h2&gt;
+&lt;p&gt;Add-on is more of a generic term which is used to mean a lot of different things.  What it actually means
+[K3]
+Q: Is Flash or Flex better to build a user interactive ordering "wizard" website?
+A: &lt;p&gt;Short answer is &lt;strong&gt;to take best from both of them.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;And here is a short story, which describe how big Flash project could be done.&lt;/p&gt;
+&lt;p&gt;Company receive order for a project X, and there are two departments are going to work on it, D (Designers who are going to create all fancy graphic for the project) and P (Programmers who are going to input some life into the lifeless design). &lt;/p&gt;
+&lt;p&gt;While guys from the P department drinking bear in the basement and creating data model for the project X, configuring software, and doing all routine stuff that are need to be done before starting a new project. Guys from the D department open &lt;strong&gt;Flash&lt;/strong&gt; which is familiar for them, as they spent all their life in Ps,Ai and other Adobe products. (&lt;em&gt;Flash is good, really good, if you want to play with a graphic objects. Move them left or right, add some fancy effects, create animation and stuff like that. Creating graphical objects for the future Flash project inside the Flash IDE is more natural.&lt;/em&gt;). &lt;/p&gt;
+&lt;p&gt;Nobody from the D department had never write a line of code, so when they finish creating first part of graphical assets they just compile this to the .swc file and pass it to the P department, where good fellows already start to wrote some code inside &lt;strong&gt;Flash Builder&lt;/strong&gt; which is  looks familiar for them, as they  spent a lot amount of time coding with different programming languages inside &lt;a href="http://en.wikipedia.org/wiki/List_of_Eclipse-based_software" rel="nofollow"&gt;Eclipse based IDE&lt;/a&gt;. &lt;/p&gt;
+&lt;p&gt;So in the end the project X, is nicely separated into the two parts: graphical assets which are created inside Flash - which was
+[K4]
+ just depends on who is talking, but the mozilla definition is probably as good as any; it could be anything that adds functionality to your web browser, regardless of the context.&lt;/p&gt;
+&lt;h2&gt;Key Differences&lt;/h2&gt;
+&lt;p&gt;Extensions tend to be automatic once installed.  Plugins are instantiated in one of two ways: 1) by an &lt;code&gt;&amp;lt;object&amp;gt;&lt;/code&gt; or &lt;code&gt;&amp;lt;embed&amp;gt;&lt;/code&gt; tag in the HTML of a web page, or 2) because they are registered to be the handler for a mimetype which the browser doesn't support.&lt;/p&gt;
+&lt;h1&gt;FireBreath&lt;/h1&gt;
+&lt;p&gt;FireBreath deals with plugins.  It has nothing to do with typical browser extensions, only plugins.  It is a C++ framework, not a javascript framework, and it allows you to add functionality that can be used from within a web page.  Typically FireBreath plugins are used from inside a &lt;code&gt;&amp;lt;object&amp;gt;&lt;/code&gt; tag.&lt;/p&gt;
+&lt;h1&gt;FireBreath post-NPAPI&lt;/h1&gt;
+&lt;p&gt;As you may or may not know, Chrome has dropped support for NPAPI plugins (as of version 45) and Firefox has done so as of version 52 (excluding the version 52 Extended Support Release, which will support them for another year).  FireBreath 2.0 is now being used in production by several companies and can produce "plugins" (not really plugins, but work similarly) which can work with Google Chrome and Firefox via Native Messaging via a helper extension. The main limitation is drawing; there is no way to draw directly to the browser across native messaging (well, no good way, and no way at all on platforms other than windows).&lt;/p&gt;
+&lt;p&gt;Eventually we may add support for some abstraction to draw using Canvas / WebGL over the native messaging bridge in FireBreath 2.0, but that hasn
+[K5]
+p&gt;
+&lt;p&gt;One key difference is not &lt;code&gt;f&lt;/code&gt; can be restricted to only working on &lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3164,10 +4822,21 @@
 By following these steps, you should be able to diagnose and resolve the access denied issue with MySQL. If issues persist, consider checking MySQL server logs for additional context on the failed connections.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3271,10 +4940,112 @@
 By following these steps, you should be able to resolve the issues related to `CardView` and `RecyclerView` not being recognized in your project. If you need to continue using older libraries, ensure that they are compatible with your current configurations, but transitioning to AndroidX is strongly advisable for better future support.</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+Q: Android CardView layout broken pre-API 28
+A: &lt;p&gt;You can use &lt;a href="https://github.com/intuit/sdp" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;SDP&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt; - a scalable size unit&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+  implementation 'com.intuit.sdp:sdp-android:1.0.6'
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FYI&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; &amp;lt;android.support.v7.widget.CardView 
+  xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+  xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+  xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+  android:layout_width=&amp;quot;125dp&amp;quot;
+  android:layout_height=&amp;quot;40dp&amp;quot;
+  android:layout_marginEnd=&amp;quot;8dp&amp;quot;
+  app:cardCornerRadius=&amp;quot;165dp&amp;quot;
+  app:cardElevation=&amp;quot;8dp&amp;quot;
+  app:contentPadding=&amp;quot;8dp&amp;quot;
+  &amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Leads to inconsistency. Different layouts end up hard-coding different font sizes and margins, making the app appear less polished.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;TRY&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;?xml version=&amp;quot;1.0&amp;quot; encoding=&amp;quot;utf-8&amp;quot;?&amp;gt;
+   &amp;lt;android.support.v7.widget.CardView 
+    xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+    xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+    xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+    android:layout_width=&amp;quot;@dimen/_125sdp&amp;quot;
+    android
+[K3]
+Q: Didn't find class "android.support.v7.widget.CardView"
+A: &lt;p&gt;i try you xml &lt;a href="https://i.sstatic.net/LLLdf.png" rel="nofollow noreferrer"&gt;&lt;img src="https://i.sstatic.net/LLLdf.png" alt="enter image description here"&gt;&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;click on {Change to android.support.v7.widget.CardView}&lt;/p&gt;
+&lt;p&gt;no crashed occurred &lt;/p&gt;
+[K4]
+Q: Error inflating android.support.v7.widget.CardView
+A: &lt;p&gt;At first add &lt;strong&gt;&lt;code&gt;setContentView();&lt;/code&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;override fun onCreate(savedInstanceState: Bundle?) {
+    super.onCreate(savedInstanceState)
+    setContentView(R.layout.activity_main) //missing
+    val recyclerView = findViewById(R.id.contactsView) as RecyclerView
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use Exact version &lt;strong&gt;&lt;code&gt;App Level&lt;/code&gt;&lt;/strong&gt; &lt;code&gt;build.gradle&lt;/code&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; dependencies {
+       implementation 'com.android.support:cardview-v7:28.0.0'
+       implementation 'com.android.support:recyclerview-v7:28.0.0'
+      }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;h2&gt;FYI&lt;/h2&gt;
+&lt;p&gt;You are using very old versions. If you want to use latest then libraries will not work unless you make the following changes in your app:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Upgrade compileSdkVersion to 28 or later.&lt;/li&gt;
+&lt;li&gt;Update your app to use Jetpack (AndroidX).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;AndroidX replaces the original support library APIs with packages in the androidx namespace. Read official guideline about &lt;a href="https://developer.android.com/jetpack/androidx" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;AndroidX Overview&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Your &lt;strong&gt;&lt;code&gt;Cardview&lt;/code&gt;&lt;/strong&gt; &amp;amp; &lt;strong&gt;&lt;code&gt;recyclerview&lt;/code&gt;&lt;/strong&gt; will&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; implementation 'androidx.cardview:cardview:1.0.0'
+ implementation 'androidx.recyclerview:recyclerview:1.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Android L CardView and RecyclerView
+A: &lt;p&gt;&lt;strong&gt;Can I use these widgets in older versions&lt;/strong&gt; :&lt;/p&gt;
+&lt;p&gt;Yes you can. Those can be supported from API level = 7.&lt;/p&gt;
+&lt;p&gt;To use this in android studio add bellow line in your app build.gradle file.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Like :&lt;/strong&gt; &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+....
+compile 'com.android.support:cardview-v7:21.0.+'
+compile 'com.android.support:recyclerview-v7:21.0.+'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;}&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3314,10 +5085,99 @@
 In Java, tools like Lombok provide a workaround by generating methods and other code at compile time using annotations (e.g., `@Data`). This approach doesn't have the same drawbacks as traditional macros because the tools can be designed to understand and handle these annotations, making it easier to integrate them with IDE features . Overall, while macros offer flexibility and power, their impact on tooling and developer experience necessitates careful design to ensure compatibility with development environments.</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+builder" rel="nofollow noreferrer"&gt;https://docs.python.org/3/library/venv.html#an-example-of-extending-envbuilder&lt;/a&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;User &lt;em&gt;wim&lt;/em&gt; made an interesting suggestion here:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://stackoverflow.com/a/60217751"&gt;https://stackoverflow.com/a/60217751&lt;/a&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;I have a tool called &lt;em&gt;ve&lt;/em&gt; that does something similar:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://pypi.org/project/ve/" rel="nofollow noreferrer"&gt;https://pypi.org/project/ve/&lt;/a&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;There are some answers to similar questions, suggesting to modify the &lt;em&gt;wheel&lt;/em&gt; files bundled with &lt;em&gt;ensurepip&lt;/em&gt; in Python's standard library, but I wouldn't recommend that.&lt;/p&gt;
+&lt;p&gt;Similar questions:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://stackoverflow.com/q/51720909/11138259"&gt;How to get &amp;quot;python -m venv&amp;quot; to directly install latest pip version&lt;/a&gt;&lt;/li&gt;
+&lt;li&gt;&lt;a href="https://stackoverflow.com/q/29689514/11138259"&gt;Why &amp;#39;python3 -m venv myenv&amp;#39; installs older version of pip into myenv than any version of pip I can find anywhere on the system?&lt;/a&gt;&lt;/li&gt;
+&lt;/ul&gt;
+[K2]
+ have to move the original statement).&lt;/p&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;hr&gt;
+&lt;p&gt;&lt;a href="http://www.sable.mcgill.ca/soot/"&gt;Soot&lt;/a&gt; is a good framework to do this. It has a number of intermediate representations that make bytecode analysis more convenient (e.g. Jimple).&lt;/p&gt;
+&lt;p&gt;You can build a &lt;a href="http://www.sable.mcgill.ca/soot/doc/soot/toolkits/graph/BlockGraph.html"&gt;BlockGraph&lt;/a&gt; based on your method body, for example an &lt;a href="http://www.sable.mcgill.ca/soot/doc/soot/toolkits/graph/ExceptionalBlockGraph.html"&gt;ExceptionalBlockGraph&lt;/a&gt;. Once you've decomposed the control flow graph into such a block graph, from the nodes, you should be able to identity the dominators (i.e. blocks that have an arrow coming back to them). This will give you the start of the loop.&lt;/p&gt;
+&lt;p&gt;You may find something similar done in &lt;a href="http://www.harbulot.com/phd-thesis.pdf"&gt;sections 4.3 to 4.7 of this dissertation&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;EDIT:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Following the discussion with @Peter in comments to his answer. Talking the same example:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public int foo(int i, int j) {
+    while (true) {
+        try {
+            while (i &amp;lt; j)
+                i = j++ / i;
+        } catch (RuntimeException re) {
+            i = 10;
+            continue;
+        }
+        break;
+    }
+    return j;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This time, compiled with the Eclipse compiler (no specific option: simply autocompilation from within the IDE). 
+This code hasn't been obfuscated (apart from being bad code, but that's a different
+[K3]
+Q: Code demo (live) snippets
+A: &lt;p&gt;There is a full tutorial on how to create Code Snippets for Visual Studio &lt;a href="http://msdn.microsoft.com/en-us/library/vstudio/ms165393%28v=vs.100%29.aspx" rel="nofollow"&gt;here&lt;/a&gt;.&lt;br&gt;
+A complete walk through on how to create a code snippet can also be found on the MSDN site &lt;a href="http://msdn.microsoft.com/en-us/library/ms165394.aspx" rel="nofollow"&gt;here&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;They have also created a &lt;a href="https://visualstudiogallery.msdn.microsoft.com/3260eed5-c3c2-44f8-b705-a332d3a9f64b" rel="nofollow"&gt;utility&lt;/a&gt; to make it easier to create your own code snippets, a full blog entry about how to use the utility from the VS blog can be found &lt;a href="http://blogs.msdn.com/b/visualstudio/archive/2014/01/15/visually-creating-snippets.aspx" rel="nofollow"&gt;here&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;The basics of creating a code snippet are as follows:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;Create a folder somewhere on your drive that you want to store all your code snippets into&lt;/li&gt;
+&lt;li&gt;Create the different snippet files in this directory (as explained in the links above)&lt;/li&gt;
+&lt;li&gt;Add this directory to your VS's list of snippets by going to &lt;em&gt;Tools&lt;/em&gt; -&gt; &lt;em&gt;Code Snippets Manager&lt;/em&gt; (or &lt;kbd&gt;Ctrl&lt;/kbd&gt;&lt;kbd&gt;k&lt;/kbd&gt;+&lt;kbd&gt;Ctrl&lt;/kbd&gt;&lt;kbd&gt;b&lt;/kbd&gt;)&lt;/li&gt;
+&lt;li&gt;Create a file with the extension &lt;code&gt;.snippet&lt;/code&gt; inside this folder and edit the file with the code content that you would like the snippet to be.&lt;/li&gt;
+&lt;li&gt;After
+[K4]
+ol&gt;
+&lt;p&gt;These requirements of using procedures and supporting short circuit evaluation are logically inconsistent, so you cannot have them coexisted in the language. Macros can support non-strict evaluations &lt;a href="https://en.wikipedia.org/wiki/Evaluation_strategy#Call_by_macro_expansion" rel="nofollow noreferrer"&gt;by expansion&lt;/a&gt;, so here they are.&lt;/p&gt;
+&lt;p&gt;However, the limitation above is due to Scheme's design choice. The notion of functions and non-strict evaluation do not clash in nature. In a language providing "functions" (other than Scheme's procedures) supporting non-strict evaluation, similar constructs can be actually implemented. Notably, &lt;a href="https://web.cs.wpi.edu/~jshutt/kernel.html" rel="nofollow noreferrer"&gt;the Kernel language&lt;/a&gt;, as a Scheme-like derivation, provides both applicative combiners (like Scheme's procedures) and operative combiners (replacement of macros but being first-class like procedures, e.g. allowing being passed to another combiner as an operand), which can be collectively considered "functions". The standard derivations (non-primitive combiners) in the language include &lt;em&gt;both&lt;/em&gt; &lt;code&gt;$and?&lt;/code&gt; (an operative as Scheme's &lt;code&gt;and&lt;/code&gt; macro, with short circuit evaluation) and &lt;code&gt;and?&lt;/code&gt; (an applicative which guarantees the operand always evaluated first, like an ordinary strict-evaluating function). Klisp, as an implementation, provides the derivation of &lt;code&gt;$and?&lt;/code&gt; as the distinguishing example in &lt;a href="http://klisp.org" rel="nofollow noreferrer"&gt;its homepage&lt;/a&gt;.&lt;/p&gt;
+[K5]
+Q: which pattern should i adopt to comment my php code?
+A: &lt;p&gt;Consider commenting your code with &lt;strong&gt;documentation&lt;/strong&gt; in mind: Program documentation can be auto-generated from source code comments, which is very useful and will become an issue sooner or later.&lt;/p&gt;
+&lt;p&gt;I think it's safe to say that &lt;a href="http://www.phpdoc.org/" rel="nofollow noreferrer"&gt;phpDocumentor's&lt;/a&gt; notation has reached the status of PHP industry standard.  Their &lt;a href="http://manual.phpdoc.org/HTMLSmartyConverter/HandS/phpDocumentor/tutorial_phpDocumentor.pkg.html" rel="nofollow noreferrer"&gt;tutorial&lt;/a&gt; gives a good rundown on how it works. &lt;a href="http://manual.phpdoc.org/HTMLSmartyConverter/HandS/phpDocumentor/tutorial_sample3.pkg.html" rel="nofollow noreferrer"&gt;Here&lt;/a&gt; is a complete sample PHP file with phpDoc style comments. In short, the documentation standard is to precede every file, class, and method with "docBlocks":&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;/**  
+ * This is a description of my function
+ * @param string this is a description of the first parameter
+ * @param int this is a description of the second parameter
+ * @return int this describes what the function returns
+ */ 
+ function myfunc ($param1, $param2)
+  { ...  }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;phpDocumentor has a number of predefined &lt;code&gt;@keyword&lt;/code&gt; keywords: &lt;code&gt;@license&lt;/code&gt;, &lt;code&gt;@version&lt;/code&gt;, &lt;code&gt;@deprecated&lt;/code&gt; and many, many more.&lt;/p&gt;
+&lt;p&gt;many PHP IDEs recognize this kind of notation, and are able to extract lookup information from it that comes up when you type.&lt;/p&gt;
+&lt;p&gt;A keyword that many IDEs use to compile task lists is  &lt;code&gt;@todo&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;One area</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3358,10 +5218,123 @@
 By following these steps, you should be able to successfully configure your AWS Lambda function to work with Java 11 and deploy it without errors. Make sure to verify every component of your setup to ensure compatibility with the Java version you are trying to use.</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+$registerAndPromoteBean$1(AwsSecretsManagerConfigDataLocationResolver.java:113) ~[spring-cloud-starter-aws-secrets-manager-config-2.3.0-RC2.jar:2.3.0-RC2]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.doInvokeListener(SimpleApplicationEventMulticaster.java:176) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.invokeListener(SimpleApplicationEventMulticaster.java:169) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:143) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:131) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.boot.DefaultBootstrapContext.close(DefaultBootstrapContext.java:133) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.prepareContext(SpringApplication.java:392) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:325) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1311) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1300) ~[spring-boot-2.4.2.jar:2.4.2]
+        at com.brighttalk.service.securedsecrets
+[K2]
+Q: Tomcat fails to start using Eclipse, JRebel, and Spring Boot
+A: &lt;p&gt;JRebel cannot instrument class because &lt;em&gt;MBeanRegistrationSupport#setRegistrationBehavior&lt;/em&gt; method was removed by &lt;a href="https://github.com/spring-projects/spring-framework/commit/b5db5d3aac39ca7cff4ccca491652d9490a1d175#diff-c36e12d89e096da6108d667fb27b1c3dL165" rel="nofollow"&gt;b5db5d&lt;/a&gt; commit on spring-framework development branch.&lt;/p&gt;
+&lt;p&gt;We have updated our Spring integration and &lt;a href="https://zeroturnaround.com/software/jrebel/download/nightly-build/" rel="nofollow"&gt;JRebel Nighly build&lt;/a&gt; (choose standalone jar) should work fine.&lt;/p&gt;
+&lt;p&gt;Fix will be included in JRebel 6.5.2 which we plan to release next week.&lt;/p&gt;
+&lt;p&gt;Thank you for bug report, if you have any questions/issue please write to support@zeroturnaround.com.&lt;/p&gt;
+[K3]
+Q: SpringMVC XML error- Randomly
+A: &lt;p&gt;This kind of issue:&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;cvc-elt.1: Cannot find the declaration of element 'beans'.
+  root-context.xml /SwiftEmploymentMVC/src/main/webapp/WEB-INF/spring
+  line 3 XML Problem&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;generally is a &lt;strong&gt;dependency one&lt;/strong&gt;, that is caused by some &lt;strong&gt;missing classes&lt;/strong&gt;, themselves caused by using &lt;strong&gt;conflicting dependencies versions&lt;/strong&gt;.
+Even if you say everything is fine with your Apache server, you are using &lt;strong&gt;too much different versions for your Spring jars&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;By example, you use &lt;code&gt;spring-security-core&lt;/code&gt; in version &lt;code&gt;3.1.0.RELEASE&lt;/code&gt;, but &lt;code&gt;spring-security-config&lt;/code&gt; in version &lt;code&gt;4.0.3.RELEASE&lt;/code&gt;.
+Those jars are linked, and you are using 2 different major versions, which could be a problem.&lt;/p&gt;
+&lt;p&gt;If you don't know &lt;strong&gt;which dependencies versions are required by a jar&lt;/strong&gt;, have a look at &lt;a href="http://mvnrepository.com/" rel="nofollow"&gt;http://mvnrepository.com/&lt;/a&gt;.&lt;br&gt;
+It lists the different required dependencies by type.&lt;/p&gt;
+&lt;p&gt;If your case, I would suggest that you use your &lt;code&gt;org.springframework-version&lt;/code&gt; property for more (or all) of your Spring jars.&lt;/p&gt;
+[K4]
+Q: Error Creating Bean Error (Spring Cloud Config Client)
+A: &lt;p&gt;With help for Gregor, I was able to solve it. These are the changes I did:&lt;/p&gt;
+&lt;p&gt;I added a &lt;code&gt;messageConverter&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package com.gcp.logicalprovisioning.config.server;
+import org.slf4j.Logger;
+import org.slf4j.LoggerFactory;
+import org.springframework.beans.factory.annotation.Value;
+import org.springframework.boot.CommandLineRunner;
+import org.springframework.boot.SpringApplication;
+import org.springframework.boot.autoconfigure.EnableAutoConfiguration;
+import org.springframework.boot.autoconfigure.SpringBootApplication;
+import org.springframework.boot.autoconfigure.jdbc.DataSourceAutoConfiguration;
+import org.springframework.context.annotation.Bean;
+@SpringBootApplication
+@EnableAutoConfiguration(exclude={DataSourceAutoConfiguration.class})
+public class DemoClientApplication {
+    private static final Logger LOGGER = LoggerFactory.getLogger(DemoClientApplication.class);
+    public static void main(String[] args) {
+        SpringApplication.run(DemoClientApplication.class, args);
+    }
+    /**
+     * Output property from cloud-config-server on startup of app,
+     *
+     * also can be seen at:
+     * http://localhost:9090/env/APP.aaf.env
+     */
+    @Bean
+    public CommandLineRunner printProperties(@Value(&amp;quot;${APP.aaf.env}&amp;quot;) final String appProperty)  {
+        return args -&amp;gt; LOGGER.info(&amp;quot;APP.aaf.env is: [{}]&amp;quot;, appProperty);
+    }
+    @Bean
+    public RestTemplate restTemplate() {
+        final RestTemplate restTemplate = new RestTemplate();
+        List&amp;lt;HttpMessageConverter&amp;lt;?&amp;gt;&amp;gt; messageConverters = new ArrayList&amp;lt;&amp;gt;();
+        MappingJackson2HttpMessageConverter mappingJackson2HttpMessageConverter = new MappingJackson2HttpMessageConverter();
+        mappingJackson2HttpMessageConverter.setSupportedMediaTypes(Collections.singletonList(MediaType.ALL));
+        messageConverters.add(mappingJackson2HttpMessageConverter);
+        restTemplate.setMessageConverters(messageConverters
+[K5]
+Q: spring batch AsynchJob Launcher ,Error in setting job repo
+A: &lt;p&gt;Here is a working example made from &lt;a href="http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/" rel="nofollow"&gt;http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/&lt;/a&gt; and tested on wildfly 9.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;beans xmlns="http://www.springframework.org/schema/beans"
+       xmlns:batch="http://www.springframework.org/schema/batch" 
+       xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"
+       xsi:schemaLocation="http://www.springframework.org/schema/batch
+        http://www.springframework.org/schema/batch/spring-batch-2.2.xsd
+        http://www.springframework.org/schema/beans 
+        http://www.springframework.org/schema/beans/spring-beans-3.2.xsd
+    "&amp;gt;
+    &amp;lt;bean id="report" class="Report" scope="prototype" /&amp;gt;
+    &amp;lt;bean id="jobRepository"
+       class="org.springframework.batch.core.repository.support.MapJobRepositoryFactoryBean"&amp;gt;
+        &amp;lt;property name="transactionManager" ref="transactionManager" /&amp;gt;
+    &amp;lt;/bean&amp;gt;
+    &amp;lt;batch:job id="helloWorldJob"&amp;gt;
+        &amp;lt;batch:step id="step1"&amp;gt;
+            &amp;lt;batch:tasklet&amp;gt;
+                &amp;lt;batch:chunk reader="cvsItemReader" writer="xmlItemWriter"
+                                     commit-interval="10"&amp;gt;
+                &amp;lt;/batch:chunk&amp;gt;
+            &amp;lt;/batch:tasklet&amp;gt;
+        &amp;lt;/batch:step&amp;gt;
+    &amp;lt;/batch:job&amp;gt;
+    &amp;lt;bean id="jobLauncher"
+              class="org</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3404,17 +5377,62 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>The context provided does not specifically address the questions regarding the migration of class libraries from .NET Standard 2.1 to .NET 6 or whether it is worth doing so. Therefore, I cannot provide a definitive answer on those specific inquiries or the implications of not migrating.
-However, I can support the following claims based on the retrieved sources:
-1. The error you encountered when trying to upgrade to EF Core 6.0 indicates that Microsoft.EntityFrameworkCore 6.0.0 is not compatible with .NET Standard 2.1. Instead, it only supports .NET 6.0 ().
-2. There is a suggestion in the context that transitioning from .NET Standard 2.1 to newer versions such as .NET 6.0 is necessary for compatibility with entities like EF Core 6.0, as .NET 6 is the current framework that provides support for this version of EF Core ().
-For further information or more detailed guidance, the retrieved sources do not cover the full scope of your questions about the reasoning behind moving to .NET 6 or potential losses.</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the questions regarding the migration of class libraries from.NET Standard 2.1 to.NET 6 or whether it is worth doing so. Therefore, I cannot provide a definitive answer on those specific inquiries or the implications of not migrating.
+However, I can support the following claims:
+1. The error you encountered when trying to upgrade to EF Core 6.0 indicates that Microsoft.EntityFrameworkCore 6.0.0 is not compatible with.NET Standard 2.1. Instead, it only supports.NET 6.0 ().
+2. There is a suggestion that transitioning from.NET Standard 2.1 to newer versions such as.NET 6.0 is necessary for compatibility with entities like EF Core 6.0, as.NET 6 is the current framework that provides support for this version of EF Core ().
+For further information or more detailed guidance, [catatan: informasi tidak tersedia] the full scope of your questions about the reasoning behind moving to.NET 6 or potential losses.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: how to use EF6.0 in .netframework 4.6.2 class library project referenced inside ASPNET Core 2.0 project
+A: &lt;p&gt;The Microsoft article &lt;a href="https://learn.microsoft.com/en-us/aspnet/core/data/entity-framework-6" rel="nofollow noreferrer"&gt;Get Started with ASP.NET Core and Entity Framework 6&lt;/a&gt; has the steps necessary for using Entity Framework 6 from a ASP.NET Core project.&lt;/p&gt;
+&lt;p&gt;Regarding the &lt;code&gt;NotSupportedException&lt;/code&gt;, I would refer to the related question &lt;a href="https://stackoverflow.com/q/52185029/4387459"&gt;System.NotSupportedException: Unable to determine the provider name for provider factory of type 'System.Data.SqlClient.SqlClientFactory'&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;I ran into the same issue because I failed to change the Core &lt;code&gt;.csproj&lt;/code&gt; file from &lt;code&gt;&amp;lt;TargetFramework&amp;gt;netcoreapp2.2&amp;lt;/TargetFramework&amp;gt;&lt;/code&gt; to &lt;code&gt;&amp;lt;TargetFramework&amp;gt;net471&amp;lt;/TargetFramework&amp;gt;&lt;/code&gt; (which the article told me to do, but for some reason I thought wasn't necessary in Core 2.2). &lt;/p&gt;
+&lt;p&gt;I provided more explanation and details in the &lt;a href="https://stackoverflow.com/a/54116150/4387459"&gt;posted explanation/answer&lt;/a&gt; to the question I referenced above.&lt;/p&gt;
+[K2]
+Q: Is .Net 7 backwards compatible with .Net 6?
+A: &lt;p&gt;According to this post - &lt;a href="https://learn.microsoft.com/en-us/dotnet/core/compatibility/7.0" rel="noreferrer"&gt;https://learn.microsoft.com/en-us/dotnet/core/compatibility/7.0&lt;/a&gt; - it doesn't look like it, which makes sense since it's a major version change.&lt;/p&gt;
+&lt;p&gt;The fact that that .NET 7 will not be supported for as long as .NET 6 will be is a completely separate beast entirely as .NET 6 is a LTS (Long Term Support) release and will be supported with bug and security fixes for (has to look it up) 3 years.&lt;/p&gt;
+&lt;p&gt;.NET 7 however is a STS (Standard Term Support) release and will only be supported for 18 months (6 months beyond the release of .NET 8).&lt;/p&gt;
+&lt;p&gt;.NET 8 will be a LTS release and will again be supported for 3 years providing 1 year of overlap in support for .NET 6 and .NET 8.&lt;/p&gt;
+&lt;p&gt;More info on the support lifecycle of .NET and .NET Core versions can be found here: &lt;a href="https://dotnet.microsoft.com/en-us/platform/support/policy/dotnet-core" rel="noreferrer"&gt;https://dotnet.microsoft.com/en-us/platform/support/policy/dotnet-core&lt;/a&gt;&lt;/p&gt;
+[K3]
+Q: How to compile .NET Core 2.1 API project to target .NET Framework 4.7
+A: &lt;p&gt;&lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; indeed does not support .NET Framework 4.7 - so you &lt;strong&gt;cannot&lt;/strong&gt; trivially do this.&lt;/p&gt;
+&lt;p&gt;It &lt;em&gt;might&lt;/em&gt; be that you can use some manual sub-set of the things that &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; targets, and get it to work - but this will only help if you are just using &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; as a meta-package, and don't need something out of &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; itself. So: you could try dropping the &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; dependency, see what fails, and try adding packages back in. The list of things that &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; imports can be seen by expanding "Dependencies" on the &lt;a href="https://www.nuget.org/packages/Microsoft.AspNetCore.App/" rel="nofollow noreferrer"&gt;nuget page&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;But: it is entirely possible that it &lt;em&gt;just isn't possible&lt;/em&gt;.&lt;/p&gt;
+[K4]
+Q: Using ServiceStack with Full .NET Framework
+A: &lt;p&gt;If you want to run on &lt;strong&gt;classic ASP.NET&lt;/strong&gt; or HttpListener you should only reference the main &lt;code&gt;"ServiceStack.Admin"&lt;/code&gt; packages (i.e. without .Core suffix) which contain both .NET Standard 2.0 and .NET Framework v4.5 builds. In a .NET Framework Application it will use the &lt;strong&gt;.NET v4.5&lt;/strong&gt; Framework builds.&lt;/p&gt;
+&lt;p&gt;If you want to create new &lt;strong&gt;ASP.NET Core&lt;/strong&gt; Apps on the .NET Framework you should &lt;a href="http://docs.servicestack.net/templates-corefx#reference-core-packages" rel="nofollow noreferrer"&gt;reference .Core packages instead&lt;/a&gt; which only contains &lt;strong&gt;.NET Standard 2.0&lt;/strong&gt; builds to force .NET Framework Applications to use the .NET Standard builds that are required for running in ASP.NET Core Apps.&lt;/p&gt;
+&lt;p&gt;I strongly recommend starting with one of the &lt;a href="http://docs.servicestack.net/templates-corefx" rel="nofollow noreferrer"&gt;ASP.NET Core .NET Framework Templates&lt;/a&gt; to create a working project with the correct dependencies:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ npm install -g @servicestack/cli
+$ dotnet-new web-corefx AcmeNetFx
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You should &lt;strong&gt;never reference both&lt;/strong&gt;, also you can only use the same version number of all packages together, i.e. you can't use the deprecated &lt;code&gt;ServiceStack.Api.Swagger.Core&lt;/code&gt; package with v5.2.1 assemblies.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;ServiceStack.Api.Swagger&lt;/code&gt; contains the old &lt;a href="http://docs.servicestack.net/swagger-api" rel="nofollow noreferrer"&gt;v1.2 version of Swagger&lt;/a&gt;, you likely want to reference &lt;code
+[K5]
+ .net standard.  I target .net 4.6.1, .net standard 2.0, and .net core 2.1 since I have had issues resolving .net standard-only packages.  Perhaps that will change in future.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3528,13 +5546,108 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover how to get the background color of an `XSSFSimpleShape` object in the Apache POI framework. Therefore, I cannot provide an answer using the context available.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] how to get the background color of an `XSSFSimpleShape` object in the Apache POI framework. Therefore, I cannot provide an answer using the context available.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+kCTForegroundColorAttributeName,nil];
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+.fillStyle = 'green';
+        balContext.fill();
+    }
+    this.draw();
+}​
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: setBackgroundDrawable not working properly
+A: &lt;p&gt;I will suggest not to use the color code directly this way while you are trying to set the color programmatically. It will not take it. just try out this way..&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;getSupportActionBar().setBackgroundDrawable(new ColorDrawable(mContext.getResources().getColor(Color.BLACK)));
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Hope it will work for you. &lt;/p&gt;
+[K4]
+Q: Background Color in Java Graphics 2D is always black color
+A: &lt;p&gt;&lt;strong&gt;Problem #1:&lt;/strong&gt; Extending from &lt;code&gt;JFrame&lt;/code&gt;.  Generally this is discouraged as it locks you into a single use case (you can't really add the frame to anything else), besides, you're not really adding any new functionality to the class.  Better to simply create an instance when you need it&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Problem #2:&lt;/strong&gt; Overriding &lt;code&gt;paint&lt;/code&gt; of a top level container (&lt;code&gt;JFrame&lt;/code&gt;).  This is generally discouraged for a number of reasons: It's all to easy to break the paint chain (which you've done); it's not double buffered (say hello to flickering updates); child components can be painted without requiring the parent container to be repainted (hello weird paint updates and artificates).  &lt;/p&gt;
+&lt;p&gt;Better to create a custom class, extending from something like &lt;code&gt;JPanel&lt;/code&gt; and override it's &lt;code&gt;paintComponent&lt;/code&gt; method and perform your custom painting there (and call &lt;code&gt;super.paintComponent&lt;/code&gt; before you do any custom painting)&lt;/p&gt;
+&lt;p&gt;See &lt;a href="http://www.oracle.com/technetwork/java/painting-140037.html" rel="nofollow noreferrer"&gt;Painting in AWT and Swing&lt;/a&gt; and &lt;a href="http://docs.oracle.com/javase/tutorial/uiswing/painting/" rel="nofollow noreferrer"&gt;Performing Custom Painting&lt;/a&gt; for more details&lt;/p&gt;
+&lt;p&gt;Something like...&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://i.sstatic.net/NgJrI.png" alt="Painting"&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;import java.awt.Color;
+import java.awt.Dimension;
+import java.awt.DisplayMode;
+import java.awt.EventQueue;
+import java.awt.Font;
+import java.awt.Graphics;
+import java.awt.Graphics2D;
+import
+[K5]
+());
+        getContentPane().add(new TestStringComponent());
+        pack();
+    }
+    public static void main(String[] args) {
+        java.awt.EventQueue.invokeLater(new Runnable() {
+            public void run() {
+                new FontTest().setVisible(true);
+            }
+        });
+    }
+}
+class TestStringComponent extends JComponent {
+    protected void paintComponent(Graphics g) {
+        Graphics2D g2d = (Graphics2D) g;
+        g.setColor(getBackground());
+        g.fillRect(0, 0, getWidth(), getHeight());
+        g.setColor(getForeground());
+        Font mainFont = new Font("Segoe Print", Font.PLAIN, 25);
+        Font fallbackFont = new Font("Serif", Font.PLAIN, 25);
+        String s = "Test 漢鼎繁古印 Test 漢鼎繁古印 Test";
+        g2d.drawString(createFallbackString(s, mainFont, fallbackFont).getIterator(), 20, 30);
+    }
+    public Dimension getPreferredSize() {
+        return new Dimension(500, 40);
+    }
+    private AttributedString createFallbackString(String text, Font mainFont, Font fallbackFont) {
+        AttributedString result = new AttributedString(text);
+        int textLength = text.length(); 
+        result.addAttribute(TextAttribute.FONT, mainFont, 0, textLength);
+        boolean fallback = false;
+        int fallbackBegin = 0;
+        for (int i = 0; i &amp;lt; text.length(); i++) {
+            boolean curFallback = !mainFont.canDisplay(text.charAt(i));
+            if (curFallback != fallback) {
+                fallback = curFallback;
+                if (fallback) {
+                    fallbackBegin = i;
+                } else {
+                    result.addAttribute(TextAttribute.FONT, fallbackFont, fallbackBegin, i);
+                }
+            }
+        }
+        return result;
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3621,10 +5734,21 @@
 By following these conventions, you should be able to successfully log e-commerce events such as `VIEW_ITEM` and `SELECT_ITEM` without encountering the Error 21.</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3742,10 +5866,21 @@
 This configuration should resolve your issue, allowing the AVPlayer to successfully handle the audio streaming through FFmpeg.</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3846,10 +5981,155 @@
 If you still face issues, check the scikit-learn version you are using, as the method and its availability can depend on the version.</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: How to get the coefficients from RFE using sklearn?
+A: &lt;pre&gt;&lt;code&gt;from sklearn.linear_model import LogisticRegression
+from sklearn.feature_selection import RFE
+reg = LogisticRegression()
+rfe = RFE(reg, no of features u want to select)
+rfe.fit(X, Y)
+print(rfe.support_)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;you will get to know which features are important and its a better way of looking it.&lt;/p&gt;
+[K2]
+    #the rest in this function are as they were before, beginning with:
+    for new_values in grid:
+        X_eval = X.copy()
+        ....
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Then comment out the first 20 lines of the definition of &lt;code&gt;partial_dependence&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def partial_dependence(estimator, X, features, response_method='auto',
+                   percentiles=(0.05, 0.95), grid_resolution=100,
+                   method='auto'):
+    ... (skipping docstring)
+    # if not (is_classifier(estimator) or is_regressor(estimator)):
+    #     raise ValueError(
+    #         "'estimator' must be a fitted regressor or classifier."
+    #     )
+    # 
+    # if isinstance(estimator, Pipeline):
+    #     # TODO: to be removed if/when pipeline get a `steps_` attributes
+    #     # assuming Pipeline is the only estimator that does not store a new
+    #     # attribute
+    #     for est in estimator:
+    #         # FIXME: remove the None option when it will be deprecated
+    #         if est not in (None, 'drop'):
+    #             check_is_fitted(est)
+    # else:
+    #     check_is_fitted(estimator)
+    # 
+    # if (is_classifier(estimator) and
+    #         isinstance(estimator.classes_[0], np.ndarray)):
+    #     raise ValueError(
+    #         'Multiclass-multioutput estimators are not supported'
+    #     )
+    #The rest of the function continues as it was:
+    # Use check_array only on lists and other non-array-likes / sparse. Do not
+    # convert DataFrame into a NumPy array.
+    if not(hasattr(X, '__array__') or sparse.issparse(X)):
+        X = check_array(X, force_all_finite='allow-nan
+[K3]
+_column_indices
+from sklearn.utils.validation import check_is_fitted
+from sklearn.tree._tree import DTYPE
+from sklearn.exceptions import NotFittedError
+from sklearn.ensemble._gb import BaseGradientBoosting
+from sklearn.ensemble._hist_gradient_boosting.gradient_boosting import (
+    BaseHistGradientBoosting)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;(they had previously been relative paths like &lt;code&gt;from ..utils.extmath import cartesian&lt;/code&gt; etc.)&lt;/p&gt;
+&lt;p&gt;Then, the only functions that are changed are these:&lt;/p&gt;
+&lt;p&gt;From &lt;code&gt;_partial_dependence_brute&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def _partial_dependence_brute(est, grid, features, X, response_method):
+    ... (skipping docstring)
+    averaged_predictions = []
+    # define the prediction_method (predict, predict_proba, decision_function).
+    # if is_regressor(est):
+    #     prediction_method = est.predict
+    # else:
+    #     predict_proba = getattr(est, 'predict_proba', None)
+    #     decision_function = getattr(est, 'decision_function', None)
+    #     if response_method == 'auto':
+    #         # try predict_proba, then decision_function if it doesn't exist
+    #         prediction_method = predict_proba or decision_function
+    #     else:
+    #         prediction_method = (predict_proba if response_method ==
+    #                              'predict_proba' else decision_function)
+    #     if prediction_method is None:
+    #         if response_method == 'auto':
+    #             raise ValueError(
+    #                 'The estimator has no predict_proba and no '
+    #                 'decision_function method.'
+    #             )
+    #         elif response_method == 'predict_proba':
+    #             raise ValueError('The estimator has no predict_proba method.')
+    #         else:
+    #             raise ValueError(
+    #                 'The estimator has no decision_function method.')
+    prediction_method = est.predict
+[K4]
+Q: Optimize this function with numpy (or other vectorization methods)
+A: &lt;p&gt;There's no reason to use loops here. And you really shouldn't use Numba or Cython for this stuff - linear algebra expressions like the one you have are the whole reason behind vectorized operations in Numpy.&lt;/p&gt;
+&lt;p&gt;Since this type of problem is going to pop up again and again if you keep using Numpy, I would recommend getting a basic handle on linear algebra in Numpy. You might find this book chapter helpful:&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.safaribooksonline.com/library/view/python-for-data/9781449323592/ch04.html" rel="nofollow"&gt;https://www.safaribooksonline.com/library/view/python-for-data/9781449323592/ch04.html&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;As for your specific situation: start by creating numpy arrays from your variables:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;import numpy as np
+W = np.array(W)
+p = np.array(p)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Now, your \bar p_i^2 are defined by a dot product. That's easy:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;bar_p_i = p.T.dot(W)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Note the T, for the transpose, because the dot product takes the sum of the elements indexed by the last index of the first matrix and the first index of the second matrix. The transpose inverts the indices so the first index becomes the last.&lt;/p&gt;
+&lt;p&gt;You H_t is defined by a sum. That's also easy:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;H_T = 1 - bar_p_i.sum()
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Similarly for your H_S:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;H_S = 1 - ((bar_p_i**2).T.dot(W)).sum()
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: how to calculate error part in of fitted line of polyfit to data?
+A: &lt;p&gt;Your variable &lt;code&gt;sstot&lt;/code&gt; is a scalar and will be reset for each iteration of your loop. This means that when you run the following line:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;results = pd.DataFrame({'skills':columns, 'coef': coef, 'error':error, 'error2':sstot}) 
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;The column &lt;code&gt;error2&lt;/code&gt; will be set to scalar value of sstot in the most recent iteration of your for loop, which is why error2 has all the same value.&lt;/p&gt;
+&lt;p&gt;I am guessing that you meant to keep track of sstot for each &lt;code&gt;skill&lt;/code&gt;, so you can create a list called &lt;code&gt;error2, then set the column &lt;/code&gt;error2&lt;code&gt;equal to this list (like the lists you created for&lt;/code&gt;coef&lt;code&gt;and&lt;/code&gt;error`). For example:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def polyfit(df,columns, degree):
+    coef=[]
+    error=[]
+    error2=[]
+    x = np.array(list(range(0,df.shape[0])))
+    for skill in columns:
+        y=df[skill]
+        y=pd.to_numeric(y)
+        coeffs = np.polyfit(x, y, degree)
+        # Polynomial Coefficients
+        coef.append(coeffs.tolist()[0])
+        # r-squared
+        p = np.poly1d(coeffs)
+        # fit values, and mean
+        yhat = p(x)                         # or [p(z) for z in x]
+        ybar = np.sum(y)/len(y)          # or sum(y)/len(y)
+        ssreg = np.sum((yhat-ybar)**2)   # or sum([ (yihat - ybar)**2 for yihat in yhat])
+        sstot = np</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3936,16 +6216,118 @@
  implementation 'androidx.cardview:cardview:1.0.0'
  implementation 'androidx.recyclerview:recyclerview:1.1.0'
  ```
- This change will ensure compatibility and prevent issues related to the legacy support library and AndroidX. The migration to AndroidX is recommended and is necessary if you want to use recent versions of libraries .
-2. **Check Compile SDK Version**: Ensure that your `compileSdkVersion` is set to a recent version (API 28 or later), which is compatible with the latest libraries. You currently have it set to 29, which is fine, but make sure that all libraries are compatible with this version .
-3. **Verify the XML Layout**: If your XML file still shows errors after making changes in `build.gradle`, ensure that you are correctly referencing the CardView and RecyclerView in your XML layout using the Java namespace relevant to the library you are using (i.e., `androidx` if you've migrated). The XML should be correctly formatted to avoid any issues .
-Following these steps should resolve the issue of `CardView` and `RecyclerView` not being recognized in your project. The retrieved sources support migration to AndroidX and the use of correct dependencies but do not cover all aspects of the issue such as the layout file specifics or additional tooling for migration.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
+ This change will ensure compatibility and prevent issues related to the legacy support library and AndroidX. The migration to AndroidX is recommended and is necessary if you want to use recent versions of libraries.
+2. **Check Compile SDK Version**: Ensure that your `compileSdkVersion` is set to a recent version (API 28 or later), which is compatible with the latest libraries. You currently have it set to 29, which is fine, but make sure that all libraries are compatible with this version.
+3. **Verify the XML Layout**: If your XML file still shows errors after making changes in `build.gradle`, ensure that you are correctly referencing the CardView and RecyclerView in your XML layout using the Java namespace relevant to the library you are using (i.e., `androidx` if you've migrated). The XML should be correctly formatted to avoid any issues.
+Following these steps should resolve the issue of `CardView` and `RecyclerView` not being recognized in your project. Migration to AndroidX and the use of correct dependencies but do not cover all aspects of the issue such as the layout file specifics or additional tooling for migration.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+Q: Android CardView layout broken pre-API 28
+A: &lt;p&gt;You can use &lt;a href="https://github.com/intuit/sdp" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;SDP&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt; - a scalable size unit&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+  implementation 'com.intuit.sdp:sdp-android:1.0.6'
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FYI&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; &amp;lt;android.support.v7.widget.CardView 
+  xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+  xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+  xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+  android:layout_width=&amp;quot;125dp&amp;quot;
+  android:layout_height=&amp;quot;40dp&amp;quot;
+  android:layout_marginEnd=&amp;quot;8dp&amp;quot;
+  app:cardCornerRadius=&amp;quot;165dp&amp;quot;
+  app:cardElevation=&amp;quot;8dp&amp;quot;
+  app:contentPadding=&amp;quot;8dp&amp;quot;
+  &amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Leads to inconsistency. Different layouts end up hard-coding different font sizes and margins, making the app appear less polished.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;TRY&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;?xml version=&amp;quot;1.0&amp;quot; encoding=&amp;quot;utf-8&amp;quot;?&amp;gt;
+   &amp;lt;android.support.v7.widget.CardView 
+    xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+    xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+    xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+    android:layout_width=&amp;quot;@dimen/_125sdp&amp;quot;
+    android
+[K3]
+Q: Didn't find class "android.support.v7.widget.CardView"
+A: &lt;p&gt;i try you xml &lt;a href="https://i.sstatic.net/LLLdf.png" rel="nofollow noreferrer"&gt;&lt;img src="https://i.sstatic.net/LLLdf.png" alt="enter image description here"&gt;&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;click on {Change to android.support.v7.widget.CardView}&lt;/p&gt;
+&lt;p&gt;no crashed occurred &lt;/p&gt;
+[K4]
+Q: Error inflating android.support.v7.widget.CardView
+A: &lt;p&gt;At first add &lt;strong&gt;&lt;code&gt;setContentView();&lt;/code&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;override fun onCreate(savedInstanceState: Bundle?) {
+    super.onCreate(savedInstanceState)
+    setContentView(R.layout.activity_main) //missing
+    val recyclerView = findViewById(R.id.contactsView) as RecyclerView
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use Exact version &lt;strong&gt;&lt;code&gt;App Level&lt;/code&gt;&lt;/strong&gt; &lt;code&gt;build.gradle&lt;/code&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; dependencies {
+       implementation 'com.android.support:cardview-v7:28.0.0'
+       implementation 'com.android.support:recyclerview-v7:28.0.0'
+      }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;h2&gt;FYI&lt;/h2&gt;
+&lt;p&gt;You are using very old versions. If you want to use latest then libraries will not work unless you make the following changes in your app:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Upgrade compileSdkVersion to 28 or later.&lt;/li&gt;
+&lt;li&gt;Update your app to use Jetpack (AndroidX).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;AndroidX replaces the original support library APIs with packages in the androidx namespace. Read official guideline about &lt;a href="https://developer.android.com/jetpack/androidx" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;AndroidX Overview&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Your &lt;strong&gt;&lt;code&gt;Cardview&lt;/code&gt;&lt;/strong&gt; &amp;amp; &lt;strong&gt;&lt;code&gt;recyclerview&lt;/code&gt;&lt;/strong&gt; will&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; implementation 'androidx.cardview:cardview:1.0.0'
+ implementation 'androidx.recyclerview:recyclerview:1.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Android L CardView and RecyclerView
+A: &lt;p&gt;&lt;strong&gt;Can I use these widgets in older versions&lt;/strong&gt; :&lt;/p&gt;
+&lt;p&gt;Yes you can. Those can be supported from API level = 7.&lt;/p&gt;
+&lt;p&gt;To use this in android studio add bellow line in your app build.gradle file.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Like :&lt;/strong&gt; &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+....
+compile 'com.android.support:cardview-v7:21.0.+'
+compile 'com.android.support:recyclerview-v7:21.0.+'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;}&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4006,7 +6388,7 @@
 1. **DbContext Configuration**:
  Make sure your DbContext is correctly configured to use the connection string from your `web.config` or `appsettings.json` based on the environment (development, staging, production). You can set the connection string in the constructor of your DbContext like this:
  ```csharp
- public ApplicationDbContext() : base("DbContextNameThatResidesInWebConfig") 
+ public ApplicationDbContext(): base("DbContextNameThatResidesInWebConfig") 
  { 
  // Initialization logic if needed
  } 
@@ -4019,7 +6401,7 @@
  ```
  For this, ensure your `Configuration.cs` is set up properly:
  ```csharp
- internal sealed class Configuration : DbMigrationsConfiguration&lt;ApplicationDbContext&gt;
+ internal sealed class Configuration: DbMigrationsConfiguration&lt;ApplicationDbContext&gt;
  {
  public Configuration()
  {
@@ -4031,24 +6413,110 @@
  }
  }
  ```
- The above snippet corresponds to managing how migrations are applied and provides a location for seed data if needed .
+ The above snippet corresponds to managing how migrations are applied and provides a location for seed data if needed.
 3. **Handling Migration Issues**:
- The error message "there is already a table called XXX ..." typically suggests that the migrations may be out of sync with your database's current state. To resolve this:
+ The error message "there is already a table called XXX..." typically suggests that the migrations may be out of sync with your database's current state. To resolve this:
  - Ensure that the migrations are applied correctly to the target database using `Update-Database`. You can specify the connection string explicitly if necessary.
  - Check that your migrations folder doesn't contain any manual edits that could conflict with the database state.
  - You can use commands like `Remove-Migration` to roll back changes if needed, but be careful as this may lead to data loss.
- If you need to prevent data loss during model changes, ensure you are correctly managing your migrations and applying them only when necessary, so as not to create duplicates .
+ If you need to prevent data loss during model changes, ensure you are correctly managing your migrations and applying them only when necessary, so as not to create duplicates.
 4. **Deploying with Publish Profiles**: 
  Set up your Azure App Service publish profiles to define which connection string to use for each environment. In the Azure portal, ensure you have the correct connection strings defined for development, staging, and production environments. These will override the local settings when published.
 5. **Testing and Validation**:
  After making changes, always run migrations in a local environment before deploying them to Azure. Validate that your local setup reflects the expected behavior of the Azure environment to help catch any discrepancies early.
-By following these steps, you should be able to effectively manage your MVC application with multiple Azure SQL databases using Entity Framework migrations while utilizing different app service environments as specified in your publish profiles. The above guidance does not cover specifics about testing or deploying with Azure DevOps, as the retrieved sources do not cover that part.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+By following these steps, you should be able to effectively manage your MVC application with multiple Azure SQL databases using Entity Framework migrations while utilizing different app service environments as specified in your publish profiles. The above guidance does not cover specifics about testing or deploying with Azure DevOps, [catatan: informasi tidak tersedia] that part.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: Format of the initialization string does not conform to specification - using same string for EF that worked for SqlClient
+A: &lt;p&gt;Normally, the Dbcontext MyDatabaseContext will contains the dbcontext option inside the option, you could set the connection string.&lt;/p&gt;
+&lt;p&gt;I suggest you could re-check your MyDatabaseContext.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public class ApplicationDbContext  :DbContext
+{
+    public ApplicationDbContext(DbContextOptions&amp;lt;ApplicationDbContext&amp;gt; options)
+        : base(options)
+    {
+    }
+ }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;And make sure you have set the connectionstring well.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;var connectionString = builder.Configuration.GetConnectionString(&amp;quot;DefaultConnection&amp;quot;) ?? throw new InvalidOperationException(&amp;quot;Connection string 'DefaultConnection' not found.&amp;quot;);
+builder.Services.AddDbContext&amp;lt;ApplicationDbContext&amp;gt;(options =&amp;gt;
+    options.UseSqlServer(connectionString));
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Then inside the controller or else, you should use the dependency injection instead of directly new the dbcontext.&lt;/p&gt;
+&lt;p&gt;Like below:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public class HomeController : Controller
+{
+    private readonly ApplicationDbContext _applicationDbContext;
+    public HomeController( ApplicationDbContext applicationDbContext )
+    {
+        _applicationDbContext = applicationDbContext;
+    }
+    public IActionResult Index()
+    {
+         var result =  _applicationDbContext.Users.Where(u =&amp;gt; u.Email.Equals(useremail));
+Console.WriteLine(result.Count());
+        return View();
+    }
+ }
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+Q: Issues deploying mvc application that has users and needs an update on the database
+A: &lt;p&gt;Class where you override &lt;code&gt;Seed&lt;/code&gt; method need inheriting from &lt;code&gt;DropCreateDatabaseAlways&amp;lt;TContext&amp;gt;&lt;/code&gt;. 
+Error : &lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;no suitable method found to override&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Mean only that base class not contains &lt;code&gt;Seed&lt;/code&gt; method. You can override it like:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;internal sealed class Configuration : DbMigrationsConfiguration&amp;lt;YourContext&amp;gt;
+{
+    protected override void Seed(YourContext context)
+    {
+        //add data
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: Transfer SQL Server Objects Task and Azure SQL - USE statement is not supported to switch between databases
+A: &lt;p&gt;Transfer SQL Server Objects task is using SMO in the background, which then uses the "USE" statement. This makes Transfer SQL Objects incompatible for connecting to Azure SQL Database.&lt;/p&gt;
+&lt;p&gt;My recommendation is to use Azure SQL Data Sync if you are only synchronizing tables: &lt;a href="https://msdn.microsoft.com/library/azure/hh456371.aspx" rel="nofollow"&gt;https://msdn.microsoft.com/library/azure/hh456371.aspx&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Let me know how you go with it.&lt;/p&gt;
+&lt;p&gt;Julie&lt;/p&gt;
+[K4]
+=xxxxxx" providerName="System.Data.SqlClient"/&amp;gt;
+ &amp;lt;/connectionStrings&amp;gt;
+&amp;lt;/configuration&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Also make sure you have your Framework target set to 4.0. See here for details: &lt;a href="http://msdn.microsoft.com/en-us/library/bb398197.aspx" rel="nofollow"&gt;http://msdn.microsoft.com/en-us/library/bb398197.aspx&lt;/a&gt;&lt;/p&gt;
+[K5]
+Q: Azure SQL multiple Elastic Pools (Multi-Tenant SaaS)
+A: &lt;p&gt;&lt;strong&gt;Answer context&lt;/strong&gt;  &lt;/p&gt;
+&lt;p&gt;Before answering your specific questions, let me add some context about the solution I see. With multi-tenancy comes tenant management. And, just like in the document you've linked to, there's probably going to be some sort of catalog holding all tenant-specific information. One of these pieces of information could (most probably will) be a connection string to the tenant-specific database.&lt;/p&gt;
+&lt;p&gt;Imagine a tenant connects and the system gets the database to connect to from the catalog, based on which tenant it is (let's call it the context of the tenant). The application will hand the connection string over to the rest of the application to work with.  &lt;/p&gt;
+&lt;p&gt;Now here's the beauty of the solution: that connection string can point (virtually) anywhere. It could point towards a database in a pool, or it could point to a managed instance. It could even point to an on-premises database that has been made available over the internet. All because the application is agnostic of where the data is, it just gets a connection string and goes to work.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&lt;em&gt;1. What happens if my app exceeds 500 users? What are the options to scale this efficiently? (when you reach the limit of the Elastic Pool)&lt;/em&gt;&lt;/strong&gt;  &lt;/p&gt;
+&lt;p&gt;Assuming that by users you mean tenants: nothing happens. New databases are created in any location that's accessible to the application, for instance in a new pool. And since the connection string for a tenant can point anywhere, that's totally fine. &lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&lt;em&gt;2. How well would the option fit with EF Core migrations?&lt;/em&gt;&lt;/strong&gt;  &lt;/p&gt;
+&lt;p&gt;The option fits as well with EF Core migrations as it does with any other</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4075,14 +6543,54 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover specific recommendations for a server operating system tailored to your requirements of running a basic server to handle file storage and scheduled synchronization with OneDrive and Google Drive. However, they do mention that if you are technically skilled, you might consider using a lightweight operating system like Linux (Ubuntu) for a server setup, especially if you have the capability to maintain production machines (). 
-The suggestion of using Ubuntu as a server OS is aligned with what you've heard about it being suitable for your needs; however, specific configurations or steps on how to implement the synchronization are not covered in the available context. Therefore, while it's clear Ubuntu is a potential option, further details or guidance on your exact requirement are not available.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] specific recommendations for a server operating system tailored to your requirements of running a basic server to handle file storage and scheduled synchronization with OneDrive and Google Drive. However, they do mention that if you are technically skilled, you might consider using a lightweight operating system like Linux (Ubuntu) for a server setup, especially if you have the capability to maintain production machines (). 
+The suggestion of using Ubuntu as a server OS is aligned with what you've heard about it being suitable for your needs; however, specific configurations or steps on how to implement the synchronization are not covered. Therefore, while it's clear Ubuntu is a potential option, further details or guidance on your exact requirement are not available.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Database on a server without installation?
+A: &lt;p&gt;If you are going to store data on a network share and have concurrent users accessing it you are going to need a db that can handle concurrent access. MS Access will quickly die if under concurrent access as will SQL Lite. &lt;/p&gt;
+&lt;p&gt;SQL Server Express is free and works very well. PostgreSQL as suggested by Maxim is an open source full featured db that will do the job very well but may be overkill.&lt;/p&gt;
+&lt;p&gt;You could also look at Redis ... fast lightweight in memory no sql db that also has capability to persist to file. &lt;/p&gt;
+[K2]
+Q: Developing App with node Express , React and MySQL. How / where should i store images?
+A: &lt;p&gt;It's generally not recommended to store images directly in the db. It's a waste of space, and the performance is usually poor. The most common approach would be to store them in the file system, while you would persist only URLs in the DB. You can also use the Cloud like S3 or as you mentioned Firebase Storage. There's also an option to go with CDN like Cloudflare.&lt;/p&gt;
+&lt;p&gt;If your website is primarily static I would go for CDN or filesystem. Some CDNs offer a pay-as-you-go pricing model, which might be what you want for a low-medium budget website.&lt;/p&gt;
+[K3]
+Q: What is a fast, bulk upload, media management system I can install on my website?
+A: &lt;p&gt;I'd recommend drupal. There are many like it but I'd say that this is one of the best ones.&lt;/p&gt;
+&lt;p&gt;There are thousands of modules you can add and a lot for media.&lt;/p&gt;
+[K4]
+Q: Web server statics repository -or- ZFS vs. NTFS
+A: &lt;p&gt;It all depends on your skill level and how much load you are getting on your servers.&lt;/p&gt;
+&lt;p&gt;If you have spare (physical) resources and have the technical skills and experience to maintain production machines running different operating systems, I'd recommend going running lighttpd on either Linux or FreeBSD. A light OS install with a static file optimized server will perform faster than Apache or IIS on a heavy OS.&lt;/p&gt;
+&lt;p&gt;However, unless you are extremely comfortable with these solutions, just stick to IIS on Windows. Move the static files to their own machine if you have sufficient load. If you aren't currently thinking about multiple ASP.Net frontends, there's probably no need to spin off the static files yet unless we're talking multiple gigabytes of files.&lt;/p&gt;
+[K5]
+Q: Enterprise NoSQL Stack Solution for Mobile/Web
+A: &lt;p&gt;I totally agree with the answer from @Philipp. In the case of using CouchDB you will minimum want to use a proxy server in front to enable SSL.&lt;/p&gt;
+&lt;p&gt;Almost all of your requirements can be fulfilled by CouchDB. Especially the upcoming v2 will give you the "datacenter-needs".&lt;/p&gt;
+&lt;p&gt;But it's simply very complex to answer what should be the right tool for you purpose. If you get some business model requirements on top like lets say: throttling - then you will definitely need an application server middleware like &lt;a href="http://mcavage.me/node-restify/" rel="nofollow"&gt;http://mcavage.me/node-restify/&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Maybe it's a good idea to spend some money to professionals like
+&lt;a href="http://www.neighbourhood.ie/couchdb-support/" rel="nofollow"&gt;http://www.neighbourhood.ie/couchdb-support/&lt;/a&gt; ? (I'm not involved)&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4118,13 +6626,100 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific context of integrating Blazor Server with OpenIdDict and the proper handling of access tokens for introspection. They focus on AngularJS, CORS, and general API authentication with JWT, among other unrelated topics. Therefore, I cannot provide a concrete answer based on the available context.</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific context of integrating Blazor Server with OpenIdDict and the proper handling of access tokens for introspection. They focus on AngularJS, CORS, and general API authentication with JWT, among other unrelated topics. Therefore, I cannot provide a concrete answer.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: AngularJS $http, CORS and Basic authentication with Jersey
+A: &lt;p&gt;So here's what's going on. The &lt;a href="https://developer.mozilla.org/en-US/docs/Glossary/Preflight_request" rel="nofollow noreferrer"&gt;CORS Preflight request&lt;/a&gt; is an &lt;code&gt;OPTIONS&lt;/code&gt; request. This request happens &lt;em&gt;prior&lt;/em&gt; to the real request. It checks with the server to see if the request is allowed. In response to the preflight request, the server should send back the &lt;code&gt;Access-Control-X-X&lt;/code&gt; headers like you are in your &lt;code&gt;getAllUserLogInHistoryAngular&lt;/code&gt; method.&lt;/p&gt;
+&lt;p&gt;So what is happening in your case during the preflight, is that it hits the Basic Auth filter and automatically gets rejected without adding the CORS response headers. Your putting the CORS response headers in the resource method does nothing and is useless. Generally the CORS should be handled in a filter so it handles all requests prior to hitting the resource methods.&lt;/p&gt;
+&lt;p&gt;Here's what you should do. Just like you did for Basic Auth, use a &lt;code&gt;ContainerRequestFilter&lt;/code&gt; to handle the CORS. You want this filter to be called before the Auth filter because the CORS preflight doesn't care about authentication and it will not send the authentication credentials with the request. In this filter, you should check to see if it is a CORS preflight request. Generally this can be done by checking for an &lt;code&gt;OPTIONS&lt;/code&gt; method and he presence of the &lt;code&gt;Origin&lt;/code&gt; header. If it is a preflight, then abort the request and add the CORS headers in a &lt;code&gt;ContainerResponseFilter&lt;/code&gt;. It might look something like&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;@Provider
+@PreMatching
+public class CorsFilter implements ContainerRequestFilter, ContainerResponseFilter {
+    @Override
+    public void filter(Container
+[K2]
+Q: Pass authentication information from MVC into angular
+A: &lt;p&gt;I can share what I do in my own apps, and although I am using ui-router, the same technique &lt;a href="https://stackoverflow.com/questions/19937751/angular-how-use-one-resolve-for-all-the-routes-of-my-application/19938307#19938307"&gt;can easily be applied to the built in router&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Basic logical workflow:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;Automatically add a &lt;code&gt;resolve&lt;/code&gt; to every route that fetches the user's current auth status and caches it.&lt;/li&gt;
+&lt;li&gt;Check if route requires authentication, and reject if user is not logged in, otherwise allow to proceed normally.&lt;/li&gt;
+&lt;li&gt;On &lt;code&gt;$routeChangeError&lt;/code&gt; (or something similar) check to see what action to perform.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;The advantage of this is it allows you to have a great deal of flexibility with regard to providing a nice client side experience with security.&lt;/p&gt;
+&lt;h2&gt;Adding Credentials to Every Route:&lt;/h2&gt;
+&lt;pre&gt;&lt;code&gt;let originalStateFunction = $stateProvider.state;
+$stateProvider.state = function (state, config) {
+  //
+  // The "allowAnonymous" is something we added manually
+  // This will become important later because we might have
+  // routes that don't require authentication, like say
+  // the login page
+  //
+  if (angular.isDefined(config) &amp;amp;&amp;amp; !config.allowAnonymous) {
+      _.defaults(config.resolve || (config.resolve = {}), {
+          /*@ngInject*/
+          userSession: function userSessionSecurityCheck($q, sessionService) {
+              let def = $q.defer();        
+              sessionService.getSession()
+                .then(session =&amp;gt; {
+                   if(!session.isAuthenticated){
+                      def.reject({
+                        error:'AUTHENTICATION_REQUIRED'
+                      });
+                   }
+                });
+              return def.promise;
+[K3]
+Q: Get data from access token
+A: &lt;p&gt;Use the JWT ruby gem&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;x = Net::HTTP.post_form(URI.parse('http://somesite.com/get_token'), params)
+@res = ActiveSupport::JSON.decode(x.body) 
+id_token = @res['id_token']
+id_data = JWT.decode id_token, 'secret', false
+&lt;/code&gt;&lt;/pre&gt;
+[K4]
+Q: Migrating expressjs app to serverless - express-session problem
+A: &lt;p&gt;One solution is to use the JSON Token. The session are stored directly on the client side.&lt;/p&gt;
+&lt;p&gt;In theory, at first connexion, you set a token for the session, and send it to the client.&lt;/p&gt;
+&lt;p&gt;Each time the user call the Api, you send the JSON Token. On the server side, you fill it with the data you need (it's an object)... And send it again to the client...&lt;/p&gt;
+&lt;p&gt;There are a lot of implementation of this process, and with JWT: &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://serverless.com/blog/strategies-implementing-user-authentication-serverless-applications/" rel="nofollow noreferrer"&gt;https://serverless.com/blog/strategies-implementing-user-authentication-serverless-applications/&lt;/a&gt;
+&lt;a href="https://ponyfoo.com/articles/json-web-tokens-vs-session-cookies" rel="nofollow noreferrer"&gt;https://ponyfoo.com/articles/json-web-tokens-vs-session-cookies&lt;/a&gt;
+....&lt;/p&gt;
+&lt;hr&gt;
+&lt;p&gt;According to Amazon, the best approch to manage session is to set it in a third party, as you tried you said...&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://aws.amazon.com/fr/blogs/compute/going-serverless-migrating-an-express-application-to-amazon-api-gateway-and-aws-lambda/" rel="nofollow noreferrer"&gt;https://aws.amazon.com/fr/blogs/compute/going-serverless-migrating-an-express-application-to-amazon-api-gateway-and-aws-lambda/&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Extract : &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;* Storing local state is unreliable due to automatic scaling. Consider going stateless (using REST),
+* or use an external state store (for MongoDB, you can use the connect-mongo package)
+app.use(session({ secret: process
+[K5]
+Q: MEAN-Stack - UnauthorizedError: No authorization token was found
+A: &lt;p&gt;The route is protected from your backend aka your server.js
+your server which im assuming is being run on port 3000 is protected unless you provide a token on your indicated method to which your authorizer will extract from usually its the headers.&lt;/p&gt;
+&lt;p&gt;to over come this i recommend getting a token from aka do a request that will produce one, usually there's a route setup and you can use postman to post data to get a token, once you have a token use postman to send a get request to that same route you couldn't get access to but make sure you add the header authorization or w.e it's looking for the token on. then you'll get access.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4198,10 +6793,21 @@
 With this approach, you should see each field instance correctly receive its respective class based on its content, such as `rating-1`, `rating-5`, and `rating-8`, without the overlap you were experiencing previously.</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4265,10 +6871,84 @@
 It's important to note that, as of now, native support for suggesting values from JSON files directly within the editor might not be available in PhpStorm, based on limited capabilities mentioned in user discussions (). Therefore, combining PHP arrays, annotations, or external scripts may be your best alternative approach until more robust support is possibly added in the future.</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: howto set up autocomplete for php in eclipse similar to java
+A: &lt;p&gt;If you would like to have some basic auto complete feature you can use &lt;strong&gt;NotePad++&lt;/strong&gt; (&lt;a href="http://notepad-plus-plus.org/download/v6.5.html" rel="nofollow noreferrer"&gt;download&lt;/a&gt;) for a quick and easy starter. This is a really great minimal program that can be used very efficiently to code in many different languages. It provides huge ammount of different functions. It is a must have tool for any developer.&lt;/p&gt;
+&lt;p&gt;I used Notepad++ to write ten thousands of lines of PHP code, it worked really great for me.&lt;/p&gt;
+&lt;p&gt;Otherwise &lt;strong&gt;PDT also supports autocomplete&lt;/strong&gt;. Make sure that you have a &lt;strong&gt;PHP project added&lt;/strong&gt; and then your are in a &lt;strong&gt;PHP file&lt;/strong&gt; (.php extension). If you have Java autocomplete working in the same project then I think that you are in a Java project, try adding a PHP project, then a new PHP source file. Then PHP autocomplete should be working well in this source file.&lt;/p&gt;
+&lt;p&gt;Make sure also that you have &lt;strong&gt;PHP perspective&lt;/strong&gt; selected.&lt;/p&gt;
+&lt;p&gt;I hope you can get by now starting using PHP! Have luck and good times using this great language!&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://i.sstatic.net/0kQmy.jpg" alt="Eclipse interface"&gt;&lt;/p&gt;
+[K2]
+Q: How to set the VSCode use tab switch the suggest?
+A: &lt;p&gt;It can be done with the help of the &lt;code&gt;when&lt;/code&gt; clause by adding this to your &lt;code&gt;keybindings.json&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-json prettyprint-override"&gt;&lt;code&gt;{
+    &amp;quot;key&amp;quot;: &amp;quot;tab&amp;quot;,
+    &amp;quot;command&amp;quot;: &amp;quot;selectNextSuggestion&amp;quot;,
+    &amp;quot;when&amp;quot;: &amp;quot;suggestWidgetVisible &amp;amp;&amp;amp; suggestWidgetMultipleSuggestions&amp;quot;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This way the binding won't affect the behaviour of Tab when there are no suggestions shown (i.e. when editing text, of course depending on what the vim keybindings override); it will still insert the suggestion if it's only one (since &lt;code&gt;suggestWidgetMultipleSuggestions&lt;/code&gt; will evaluate to false; if you want consistency, just remove it from the &lt;code&gt;when&lt;/code&gt; clause, leaving only &lt;code&gt;suggestWidgetVisible&lt;/code&gt; there).&lt;/p&gt;
+&lt;p&gt;Similar thing for &lt;code&gt;Shift+Tab&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-json prettyprint-override"&gt;&lt;code&gt;{
+    &amp;quot;key&amp;quot;: &amp;quot;shift+tab&amp;quot;,
+    &amp;quot;command&amp;quot;: &amp;quot;selectPrevSuggestion&amp;quot;,
+    &amp;quot;when&amp;quot;: &amp;quot;suggestWidgetVisible &amp;amp;&amp;amp; suggestWidgetMultipleSuggestions&amp;quot;
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;Enter&lt;/code&gt; shouldn't need to be overridden, but if for some reason it does, it should go like this:&lt;/p&gt;
+&lt;pre class="lang-json prettyprint-override"&gt;&lt;code&gt;{
+    &amp;quot;key&amp;quot;: &amp;quot;enter&amp;quot;,
+    &amp;quot;command&amp;quot;: &amp;quot;acceptSelectedSuggestion&amp;quot;,
+    &amp;quot
+[K3]
+Q: How do you open that window of code suggestions?
+A: &lt;p&gt;Thanks! By pressing ctrl + space it pops up the auto suggestion list ~ Nice!&lt;/p&gt;
+[K4]
+Q: Difference between WebStorm and PHPStorm
+A: &lt;blockquote&gt;
+  &lt;p&gt;PhpStorm supports all the features of WebStorm but some are not bundled so you might need to install the corresponding plugin for some framework via Settings &gt; Plugins &gt; Install JetBrains Plugin.&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;&lt;a href="https://intellij-support.jetbrains.com/hc/en-us/community/posts/206578639/comments/207578829" rel="nofollow noreferrer"&gt;Official comment - jetbrains.com&lt;/a&gt;&lt;/p&gt;
+[K5]
+Q: JQuery autocomplete returning data array with label and value, but not showing labels as suggestions
+A: &lt;p&gt;I suspect the issue is here:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;data: 'action=get_listing_names&amp;amp;name=' + name,
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;The variable is &lt;code&gt;name&lt;/code&gt; yet UI passes an Object in with this: &lt;code&gt;{ term: '' }&lt;/code&gt;. Change it to:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;data: 'action=get_listing_names&amp;amp;name=' + name.term,
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This will provide the text from the input.&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;&lt;strong&gt;Function&lt;/strong&gt;: The third variation, a callback, provides the most flexibility and can be used to connect any data source to Autocomplete, including JSONP. The callback gets two arguments:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;p&gt;A request object, with a single &lt;code&gt;term&lt;/code&gt; property, which refers to the value currently in the text input. For example, if the user enters &lt;code&gt;&amp;quot;new yo&amp;quot;&lt;/code&gt; in a city field, the Autocomplete &lt;code&gt;term&lt;/code&gt; will equal &lt;code&gt;&amp;quot;new yo&amp;quot;&lt;/code&gt;.&lt;/p&gt;
+&lt;/li&gt;
+&lt;li&gt;&lt;p&gt;A response callback, which expects a single argument: the data to suggest to the user. This data should be filtered based on the provided term, and can be in any of the formats described above for simple local data. It's important when providing a custom source callback to handle errors during the request. You must always call the &lt;code&gt;response&lt;/code&gt; callback even if you encounter an error. This ensures that the widget always has the correct state.&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;More full example:&lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="false" data-console="true" data-babel="false"&gt;
+&lt;div class="</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4364,10 +7044,21 @@
 Feel free to ask more questions if you need further clarification or assistance!</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4402,10 +7093,50 @@
 This approach will give you a functional server with minimal overhead and the capability to synchronize files as needed.</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Database on a server without installation?
+A: &lt;p&gt;If you are going to store data on a network share and have concurrent users accessing it you are going to need a db that can handle concurrent access. MS Access will quickly die if under concurrent access as will SQL Lite. &lt;/p&gt;
+&lt;p&gt;SQL Server Express is free and works very well. PostgreSQL as suggested by Maxim is an open source full featured db that will do the job very well but may be overkill.&lt;/p&gt;
+&lt;p&gt;You could also look at Redis ... fast lightweight in memory no sql db that also has capability to persist to file. &lt;/p&gt;
+[K2]
+Q: Developing App with node Express , React and MySQL. How / where should i store images?
+A: &lt;p&gt;It's generally not recommended to store images directly in the db. It's a waste of space, and the performance is usually poor. The most common approach would be to store them in the file system, while you would persist only URLs in the DB. You can also use the Cloud like S3 or as you mentioned Firebase Storage. There's also an option to go with CDN like Cloudflare.&lt;/p&gt;
+&lt;p&gt;If your website is primarily static I would go for CDN or filesystem. Some CDNs offer a pay-as-you-go pricing model, which might be what you want for a low-medium budget website.&lt;/p&gt;
+[K3]
+Q: What is a fast, bulk upload, media management system I can install on my website?
+A: &lt;p&gt;I'd recommend drupal. There are many like it but I'd say that this is one of the best ones.&lt;/p&gt;
+&lt;p&gt;There are thousands of modules you can add and a lot for media.&lt;/p&gt;
+[K4]
+Q: Web server statics repository -or- ZFS vs. NTFS
+A: &lt;p&gt;It all depends on your skill level and how much load you are getting on your servers.&lt;/p&gt;
+&lt;p&gt;If you have spare (physical) resources and have the technical skills and experience to maintain production machines running different operating systems, I'd recommend going running lighttpd on either Linux or FreeBSD. A light OS install with a static file optimized server will perform faster than Apache or IIS on a heavy OS.&lt;/p&gt;
+&lt;p&gt;However, unless you are extremely comfortable with these solutions, just stick to IIS on Windows. Move the static files to their own machine if you have sufficient load. If you aren't currently thinking about multiple ASP.Net frontends, there's probably no need to spin off the static files yet unless we're talking multiple gigabytes of files.&lt;/p&gt;
+[K5]
+Q: Enterprise NoSQL Stack Solution for Mobile/Web
+A: &lt;p&gt;I totally agree with the answer from @Philipp. In the case of using CouchDB you will minimum want to use a proxy server in front to enable SSL.&lt;/p&gt;
+&lt;p&gt;Almost all of your requirements can be fulfilled by CouchDB. Especially the upcoming v2 will give you the "datacenter-needs".&lt;/p&gt;
+&lt;p&gt;But it's simply very complex to answer what should be the right tool for you purpose. If you get some business model requirements on top like lets say: throttling - then you will definitely need an application server middleware like &lt;a href="http://mcavage.me/node-restify/" rel="nofollow"&gt;http://mcavage.me/node-restify/&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Maybe it's a good idea to spend some money to professionals like
+&lt;a href="http://www.neighbourhood.ie/couchdb-support/" rel="nofollow"&gt;http://www.neighbourhood.ie/couchdb-support/&lt;/a&gt; ? (I'm not involved)&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4434,7 +7165,7 @@
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>The issue you are encountering with the BlackBerry application description text exceeding 255 characters is likely related to the constraints imposed by the Eclipse plugin for BlackBerry development. In the BlackBerry ecosystem, especially in earlier versions like the BlackBerry JRE 5.0.0, there are often strict limits on the length of certain fields in the BlackBerry_App_Descriptor.xml file.
-In your case, since the application description works without errors when it's 255 characters or fewer, but fails when it exceeds that limit, it suggests that the plugin enforces this character limit. While this issue might not have a straightforward solution directly cited from your provided contexts, I can recommend the following approaches to resolve it:
+In your case, since the application description works without errors when it's 255 characters or fewer, but fails when it exceeds that limit, it suggests that the plugin enforces this character limit. While this issue might not have a straightforward solution directly cited I can recommend the following approaches to resolve it:
 1. **Shorten the Description**: As a temporary workaround, consider shortening your application description to 255 characters or fewer until you can find a more permanent solution.
 2. **Check Updates**: Ensure you are using the most updated version of the BlackBerry development tools, as there may be patches or updates that address this limitation.
 3. **Consult BlackBerry Documentation**: Look at the latest BlackBerry development documentation or forums for any additional advice on this specific constraint.
@@ -4442,10 +7173,55 @@
 These steps should help you manage the character limit issue while you work towards a more scalable solution.</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Blackberry @Override notation error
+A: &lt;p&gt;Blackberry development is built on top of j2me, which has the language features of Java 1.3.  This means it doesn't support annotations. You can remove the @Override annotations and your code will work.  Remember these are optional although recommended anyways.&lt;/p&gt;
+&lt;p&gt;What I do, is write //@Override instead. When/If annotations are added in the future it will be easy to do a regex replace and remove the comment marks.&lt;/p&gt;
+[K2]
+Q: java.io.UnsupportedEncodingException: ISO-8859-8, text/xml
+A: &lt;p&gt;&lt;code&gt;ISO-8859-8&lt;/code&gt; is not one of the &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/StandardCharsets.html" rel="nofollow noreferrer"&gt;standard charsets&lt;/a&gt; that Java &lt;em&gt;needs&lt;/em&gt; to support, i.e. which are guaranteed to be found (unless you have a corrupted installation).&lt;/p&gt;
+&lt;p&gt;In your case, the difference seems to be in the Windows 10 environment. I would check first that it has support for &lt;code&gt;ISO-8859-8&lt;/code&gt; (I don't know how though, I'm not a Windows user). It may need to be installed/enabled separately.&lt;/p&gt;
+&lt;p&gt;If you're &lt;strong&gt;certain&lt;/strong&gt; that your Windows 10 does support that encoding, then it's a problem with Java not being able to make the connection between the two, and you'll probably have to delve into &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/spi/CharsetProvider.html" rel="nofollow noreferrer"&gt;charset providers&lt;/a&gt;, but let's hope you don't have to go there.&lt;/p&gt;
+[K3]
+Q: The encoding 'UTF-8' is not supported by the Java runtime
+A: &lt;p&gt;Most probably someone put a catch() expecting to have only unsupported encoding exceptions, so he used the appropriate message. But he has used too wide exception specification (e.g. catch( Exception ex ) ), so when at runtime he's got something else (non-valid XML, NPE, ... ) the message became misleading.&lt;/p&gt;
+[K4]
+Q: Does Blackberry support Android OS
+A: &lt;p&gt;Although Android and Blackberry both use Java, they expose very different application APIs to developers.  So I don't think it is possible to run Android apps on a Blackberry - YET.  RIM has already announced that they are planning on supporting Android apps on the upcoming Blackberry Playbook tablet.&lt;/p&gt;
+[K5]
+Q: Eclipse - "Incompatible JVM. Version 1.8.0_261 of the JVM is not suitable for this product. Version: 11 or greater is required"
+A: &lt;p&gt;For Ubuntu users, refer to the answer &lt;a href="https://stackoverflow.com/a/64049648/14489697"&gt;https://stackoverflow.com/a/64049648/14489697&lt;/a&gt; by howlger. Add the following lines in file &lt;code&gt;eclipse.ini&lt;/code&gt; before &lt;code&gt;-vmargs&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-none prettyprint-override"&gt;&lt;code&gt;-vm
+/usr/lib/jvm/adoptopenjdk-14-openj9-amd64/bin/java
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Above is the Java install location. Change this according to yours.&lt;/p&gt;
+&lt;p&gt;I'm using,&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Eclipse IDE for Enterprise Java Developers (includes Incubating components)&lt;/li&gt;
+&lt;li&gt;Version: 2020-12 (4.18.0)&lt;/li&gt;
+&lt;li&gt;Build id: 20201210-1552&lt;/li&gt;
+&lt;li&gt;OS: Linux, v.5.4.0-42-generic, x86_64 / gtk 3.22.30&lt;/li&gt;
+&lt;li&gt;Java version: 14.0.2&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4477,18 +7253,62 @@
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>To develop OpenGL 4.x applications on Linux, you can use several commonly used libraries:
-1. **GLEW (OpenGL Extension Wrangler Library)**: This library is used to manage OpenGL extensions and is a good choice for accessing OpenGL APIs on Linux. GLEW allows you to utilize modern OpenGL features efficiently and is cross-platform, meaning you can use it without issues when transitioning from Windows to Linux .
-2. **GLFW (Graphics Library Framework)**: GLFW is another cross-platform library that helps with managing OpenGL contexts, windows, and inputs. Just like GLEW, it should work seamlessly on Linux .
-3. **Mesa**: For implementing OpenGL, you can also use Mesa3D, which is an open-source OpenGL implementation for Linux. It supports up to OpenGL 4.x, although the availability can depend on the specific graphics drivers and the version of Mesa you are using . It’s important to note that Mesa may have some limitations compared to proprietary drivers from AMD or NVIDIA but should work well for many use cases .
-4. **Vendor-specific drivers**: If you're targeting specific hardware, such as AMD or NVIDIA graphics cards, their proprietary drivers may provide even better performance and support for OpenGL 4.x features. They typically come as closed-source implementations and may provide a more feature-complete support than Mesa .
-Since you are interested in a "pure" C++ solution and wish to avoid frameworks like Qt, GLEW and GLFW would be suitable choices for your development on Linux. The retrieved sources indicate that both libraries are well-suited for handling OpenGL tasks cross-platform, including Linux, without additional dependencies . 
-For installation, you would typically install these libraries using your package manager, such as `apt` or `dnf`, depending on the Linux distribution you are using .</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
+1. **GLEW (OpenGL Extension Wrangler Library)**: This library is used to manage OpenGL extensions and is a good choice for accessing OpenGL APIs on Linux. GLEW allows you to utilize modern OpenGL features efficiently and is cross-platform, meaning you can use it without issues when transitioning from Windows to Linux.
+2. **GLFW (Graphics Library Framework)**: GLFW is another cross-platform library that helps with managing OpenGL contexts, windows, and inputs. Just like GLEW, it should work seamlessly on Linux.
+3. **Mesa**: For implementing OpenGL, you can also use Mesa3D, which is an open-source OpenGL implementation for Linux. It supports up to OpenGL 4.x, although the availability can depend on the specific graphics drivers and the version of Mesa you are using. It’s important to note that Mesa may have some limitations compared to proprietary drivers from AMD or NVIDIA but should work well for many use cases.
+4. **Vendor-specific drivers**: If you're targeting specific hardware, such as AMD or NVIDIA graphics cards, their proprietary drivers may provide even better performance and support for OpenGL 4.x features. They typically come as closed-source implementations and may provide a more feature-complete support than Mesa.
+Since you are interested in a "pure" C++ solution and wish to avoid frameworks like Qt, GLEW and GLFW would be suitable choices for your development on Linux. Both libraries are well-suited for handling OpenGL tasks cross-platform, including Linux, without additional dependencies. 
+For installation, you would typically install these libraries using your package manager, such as `apt` or `dnf`, depending on the Linux distribution you are using.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Is it possible to use OpenGL 4.5 features with latest mesa libraries?
+A: &lt;blockquote&gt;
+  &lt;p&gt;I want to use latest OpenGL features on Ubuntu. And I have installed mesa-common-dev but as far as I understand mesa does not support OpenGL 4.5 features. &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;All that matters is, that your actual OpenGL implementation supports the profile you want. The Linux ABI on OpenGL is pinned to OpenGL-1.2 (LSB5 has been released recently, so expect upcoming  distribution releases to follow it, which bumped it to OpenGL-2.1).&lt;/p&gt;
+&lt;p&gt;Anything that goes beyond the ABI requirements is done through the extension mechanism. I.e. use load function pointers through &lt;em&gt;…GetProcAddress&lt;/em&gt; and introduce new tokens with a &lt;code&gt;glext.h&lt;/code&gt;. This processes has been repacked into OpenGL extension wrapper-loader libraries like GLEW.&lt;/p&gt;
+&lt;p&gt;The stuff mesa-common-dev provides is what's written down in the Linux LSB ABI specs… in a vendor neutral way, so you can compile your program using mesa-common-dev stuff, but it will work with the NVidia or AMD/ATI drivers as well.&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;Also how can I use OpenGL via hardware without any API ? &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;By definition you can't. OpenGL is an API. If you remove the API you remove OpenGL. If your intention is working the naked GPU on the bare metal, well, that would boil down to writing a full driver. In a few weeks/months Vulkan will be released and this gets you much closer to the GPU than OpenGL.&lt;/p&gt;
+[K2]
+Q: I need openGl 2.0 but my graphic card support 1.5
+A: &lt;p&gt;It's possible that updating drivers might help some, but probably won't make that jump. Otherwise, you could use something like &lt;a href="http://www.mesa3d.org/" rel="nofollow noreferrer"&gt;Mesa3D&lt;/a&gt;, which does the rendering in software. It can be slow, but does support up through OpenGL 2.1 (including shaders), if memory serves.&lt;/p&gt;
+[K3]
+Q: What percentage of Windows boxes have OpenGL support
+A: &lt;p&gt;As I recall, Windows XP comes with 1.1 support out of the box. Vista upgrades this to 1.5. So you can at least count on those as an absolute minimum.&lt;/p&gt;
+&lt;p&gt;Apart from that, the GPU drivers from pretty much any vendor gives you &lt;em&gt;at least&lt;/em&gt; 2.0 support.&lt;/p&gt;
+&lt;p&gt;But if I were you, I'd reconsider DirectX. I don't know what you hate about it, but it does have some advantages. The tool support is vastly better (ie, there are tools available. And PIX is nothing short of amazing), the API is up to date, and well designed, rather than accumulated over 20 years of a committee working at cross purposes, and if this is limited to Windows anyway, cross-platform doesn't really matter. (On the other hand, of course, if you do need cross-platform capabilities, it doesn't really matter what else DirectX can offer, it won't deliver that one killer feature)&lt;/p&gt;
+[K4]
+Q: Starting to learn OpenGL. On modern Linux, how are all these concepts related?
+A: &lt;p&gt;OpenGL is an interface.  To use it, you need an implementation.  There are many implementations of OpenGL.  Because each implementation is different, your program will behave differently when you run it with different implementations, even though your program is the same.  A typical OpenGL implementation with a hardware renderer will consist of some code that runs in user space (a dynamic library), code that runs in the kernel (the device driver), code that runs in your X.org server (the DDX driver), and code that runs on the graphics card itself (the firmware).  That's four different pieces of code!&lt;/p&gt;
+&lt;p&gt;AMD and nVidia provide proprietary OpenGL implementations for Linux.  These implementations have closed-source drivers which &lt;a href="https://unix.stackexchange.com/questions/118116/linux-what-is-a-tainted-kernel"&gt;&lt;em&gt;taint the kernel,&lt;/em&gt;&lt;/a&gt; which means that if something goes wrong, the Linux developers can't help you.  They support recent OpenGL versions (e.g. 4.5, if your hardware is capable) with the full compatibility profile support.&lt;/p&gt;
+&lt;p&gt;Mesa provides an open-source OpenGL implementation for Linux.  This implementation can use the Noveau or Radeon open-source drivers, which do not taint the kernel.  Mesa also has a software implementation, called llvmpipe, which runs on your CPU only and doesn't need drivers.  It's impressively fast for what it is, but it is much slower than even an outdated hardware implementation.  Mesa recently started supporting OpenGL 4.x series, but it will take some time before it filters through distro release cycles, so you're more likely to see OpenGL 3.3--and that's only for the core profile, you're limited to 3.0 with the compatibility profile (similar to how it works on
+[K5]
+ OS X).&lt;/p&gt;
+&lt;p&gt;Because Mesa developers have limited access to documentation about the graphics cards, and limited development resources, the Mesa implementation on your AMD or nVidia card is usually slower than the vendor's implementation, and it usually supports fewer OpenGL extensions.  However, the Mesa implementation is very solid, it doesn't taint your kernel, and some of the Mesa implementations are even Valgrind-clean.&lt;/p&gt;
+&lt;p&gt;Installing OpenGL just means installing an OpenGL implementation on your system (you know, with &lt;code&gt;dnf&lt;/code&gt; or &lt;code&gt;apt&lt;/code&gt; or whatever).  This usually means a choice between the vendor implementation and the Mesa implementation... except for Intel integrated graphics, where Mesa &lt;em&gt;is&lt;/em&gt; the vendor implementation.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4548,18 +7368,73 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>The context you provided does not cover specifics about efficiently deleting Redis keys in bulk via a wildcard pattern. Here’s a breakdown based on what is available:
-1. Your original implementation using the `KeysAsync` method is noted to not scale well and resulted in `RedisTimeoutExceptions`, but the sources do not provide direct alternatives or specific mechanisms for bulk deletion by wildcard pattern. Therefore, information about performance issues with the `KeysAsync` method arises from your context but doesn't give an alternative method explicitly suited to your needs .
-2. Your potential solution to use a Redis `SET` to track the keys seems reasonable. Although the sources do not explicitly confirm this method's effectiveness or viability, they do indicate that different instances of Redis can serve different caches, which implies some flexibility in your design . 
+          <t>[catatan: informasi tidak tersedia] specifics about efficiently deleting Redis keys in bulk via a wildcard pattern. Here’s a breakdown based on what is available:
+1. Your original implementation using the `KeysAsync` method is noted to not scale well and resulted in `RedisTimeoutExceptions`, but [catatan: informasi tidak tersedia] direct alternatives or specific mechanisms for bulk deletion by wildcard pattern. Therefore, information about performance issues with the `KeysAsync` method arises from your context but doesn't give an alternative method explicitly suited to your needs.
+2. Your potential solution to use a Redis `SET` to track the keys seems reasonable. [catatan: informasi tidak tersedia] this method's effectiveness or viability, they do indicate that different instances of Redis can serve different caches, which implies some flexibility in your design. 
 3. Using a `SET` to hold all related keys and then deleting them as a bulk operation could be an efficient way to manage your keys, as iterating through a set may yield better performance compared to using wildcard patterns directly with `KeysAsync`. However, the cited sources do not validate this or suggest improved deletion strategies for your scenario.
-4. There is a mention of having the ability to manage keys through various configurations, indicating that varying strategies can be employed based on application design, but no direct method was given specific to your use case .
-Thus, the retrieved sources do not comprehensively cover the specific implementation of your proposed solution or provide alternatives for efficiently deleting keys in Redis based on a wildcard pattern.</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
+4. There is a mention of having the ability to manage keys through various configurations, indicating that varying strategies can be employed based on application design, but no direct method was given specific to your use case.
+Thus, [catatan: informasi tidak tersedia] the specific implementation of your proposed solution or provide alternatives for efficiently deleting keys in Redis based on a wildcard pattern.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Memcached with Windows and .NET
+A: &lt;p&gt;I'm suprised no one here has yet to mention &lt;a href="http://code.google.com/p/redis/" rel="noreferrer"&gt;Redis&lt;/a&gt; - it is one of the most feature-rich and fastest (110,000 SET's per second on an entry level linux box) key-value data stores with rich data-structure support for strings, sets, lists, sorted sets and hashes.  &lt;/p&gt;
+&lt;p&gt;Although windows is not an officially supported platform, it runs perfectly under windows with all tests passing. I have windows builds (using Cygwin) available here:
+&lt;a href="https://github.com/ServiceStack/ServiceStack.Redis#redis-server-builds-for-windows" rel="noreferrer"&gt;https://github.com/ServiceStack/ServiceStack.Redis#redis-server-builds-for-windows&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;It also has client bindings for nearly every programming language in use today. I maintain a rich Open Source C# Redis client with native API support for any C# POCO type, transaction support and Thread-safe client managers that are ready to be dropped into any IOC at:
+&lt;a href="https://github.com/ServiceStack/ServiceStack.Redis" rel="noreferrer"&gt;https://github.com/ServiceStack/ServiceStack.Redis&lt;/a&gt;&lt;/p&gt;
+[K2]
+Q: more that 1mb data in memcahed nodejs
+A: &lt;p&gt;Options available :&lt;/p&gt;
+&lt;p&gt;1/ Make sure you are using compression while storing them in memcached, your nodejs memcached driver would be supporting gzip compression.&lt;/p&gt;
+&lt;p&gt;2/ Split the data into multiple keys&lt;/p&gt;
+&lt;p&gt;3/ Increase max object size to more than 1 MB ( but that may increase fragmentation,decrease performance based on your cache usage ) &lt;/p&gt;
+&lt;p&gt;4/ Use redis as cache instead of memcached if your object sizes are usually large. Redis string datatype supports objects upto 512 MB in size, that would be easily available as direct get,set interface in any standard nodejs-redis cache driver&lt;/p&gt;
+[K3]
+ have an RDB snapshot from time to time is a great idea for doing database backups, for faster restarts, and in the event of bugs in the AOF engine.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note: for all these reasons we'll likely end up unifying AOF and RDB into a single persistence model in the future (long term plan).&lt;/strong&gt;
+Refer &lt;a href="https://redis.io/topics/persistence" rel="nofollow noreferrer"&gt;Redis Persistence&lt;/a&gt;&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;Does this mean that we could host different caches for different purposes, for eg. one cache to host user information and another cache to host order information. Or is it so that one redis instance would be master and the others could be slaves for read operations but both would serve the same cache for eg. user_information. &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Both will work.It depends on your configuration, if you want to configure both master and slave in &lt;a href="http://blog.awareshop.com/2015/01/11/redis-master-slave-setup-on-single-machine/" rel="nofollow noreferrer"&gt;same machine&lt;/a&gt; for serving for single cache you can do that or else you want &lt;a href="https://stackoverflow.com/questions/39352899/running-multiple-instance-of-redis-on-centos"&gt;different instances of redis&lt;/a&gt; for serving different caches you can also do that.&lt;/p&gt;
+[K4]
+Q: How does Redis run on multi-core cpus
+A: &lt;blockquote&gt;
+  &lt;p&gt;It is recommended that you can run multiple redis instances to use multi-core CPUs?&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;First of all, redis is not designed for multi-core CPU.However, you can run multiple instances of redis in multi-core CPU.But it does not provide such guarantee.&lt;/p&gt;
+&lt;p&gt;For example, if you launch six instances on hexa-core, there will be 6 different processes that the OS will have to get scheduled on the six cores. It is up to the OS to perform this load balancing, optimizing the performance of the system.If you want to enforce the process to be execute in specific cores you can go with modern OS.But it will seriously impact the performance of redis.&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;If Redis supports persistence why would anyone use NoSQL Databases like DynamoDB etc.?&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Redis isn't the best fit for persistent storage as it's mainly performance focused.The major difference between redis and NOSQL databases is the way of writing data.Redis usually commits data in the periodic basis where NOSQL database like DynamoDB commits data for every transaction this makes DynamoDB to be slower than redis. &lt;/p&gt;
+&lt;p&gt;However you can also make redis to commit for each query by changing their configuration.It will also decreases the performance of the redis.If you want &lt;code&gt;DynamoDB like Persistence&lt;/code&gt; What they are saying.,&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;The general indication is that you should use both persistence methods if you want a degree of data safety comparable to what PostgreSQL can provide you.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;If you care a lot about your data, but still can live with a few minutes of data loss in case of disasters, you can simply use RDB alone.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;There are many users using AOF alone, but we discourage it since to
+[K5]
+ some specialized for cache DB like Memcached or Redis. Also instead of a threshold in a form of length of &lt;code&gt;colors&lt;/code&gt; you may use some specialized cache library that support a LRU cache or &lt;a href="https://en.wikipedia.org/wiki/Cache_replacement_policies" rel="nofollow noreferrer"&gt;some other replacement police&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Finally if your logic is that the result for given set of colors is just a union of the results for each color, you may try to cover those rare big combinations of colors on the client side by caching results for each color alone and then if the color combination is not in cache directly, compute it by merging the items in the cached results for each color.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4765,7 +7640,7 @@
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>To address the issue of EditText fields snapping into view on smaller mobile displays, you can use a `ScrollView` to allow the entire form to be scrollable. This setup should enable the view to adjust when the keyboard appears, making sure that all fields including the 'Next' button are visible.
-Here’s an example implementation based on the context provided:
+Here’s an example implementation:
 1. **Wrap your layout in a ScrollView**: The top-level layout in your XML should be a `ScrollView`. This will allow the user to scroll through the form when the keyboard is visible.
  ```xml
  &lt;ScrollView
@@ -4776,12 +7651,12 @@
  &lt;RelativeLayout
  android:layout_width="match_parent"
  android:layout_height="wrap_content"&gt;
- ...
+...
  &lt;/RelativeLayout&gt;
  &lt;/ScrollView&gt;
  ```
- The `fillViewport` attribute can be set to true to ensure that the ScrollView fills the available space, which can improve the layout’s behavior when the keyboard is presented .
-2. **Use appropriate layout parameters**: Make sure your child layouts (like `RelativeLayout` for your login fields) are set properly to `wrap_content` for height so that they don't take unnecessary space when the keyboard is up .
+ The `fillViewport` attribute can be set to true to ensure that the ScrollView fills the available space, which can improve the layout’s behavior when the keyboard is presented.
+2. **Use appropriate layout parameters**: Make sure your child layouts (like `RelativeLayout` for your login fields) are set properly to `wrap_content` for height so that they don't take unnecessary space when the keyboard is up.
 3. **Consider using ViewTreeObserver.OnGlobalLayoutListener**: By implementing `ViewTreeObserver.OnGlobalLayoutListener`, you can detect when the keyboard is open and potentially scroll the view to ensure that the relevant EditText fields and buttons are always visible when focused. Here’s a snippet:
  ```java
  scrollView.getViewTreeObserver().addOnGlobalLayoutListener(new ViewTreeObserver.OnGlobalLayoutListener() {
@@ -4791,14 +7666,215 @@
  }
  });
  ```
- This strategy was mentioned in the context .
+ This strategy was mentioned.
 By implementing these strategies, you should achieve an improved user experience where all form fields and buttons are visible when interacting with the EditText fields, especially on smaller screens.</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+gt;
+            &amp;lt;TextView
+                android:id="@+id/anyid"
+                android:layout_width="wrap_content"
+                android:layout_height="wrap_content"
+                android:layout_gravity="center"/&amp;gt;
+            &amp;lt;Button
+                android:layout_width="wrap_content"
+                android:layout_height="55dp"
+                android:id="@+id/anyotherid"
+                style="@style/AppTheme.Button"
+                android:layout_marginTop="20dp"
+                android:layout_gravity="center_horizontal"
+                android:textStyle="bold"
+                android:padding="10dp"
+                android:textSize="20sp"
+                android:text="Submit"/&amp;gt;
+        &amp;lt;/LinearLayout&amp;gt;
+    &amp;lt;/ScrollView&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;This works great for me. :)&lt;/p&gt;
+[K2]
+ android:inputType="textPassword"
+    android:ems="10"
+    android:id="@+id/loginPassword_id"
+    android:textAlignment="center"
+    android:hint="Enter Application Password"
+    android:textColor="#ffffff"
+    android:textColorHint="#000000"
+    android:layout_below="@+id/appLogoImage_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+    android:layout_alignParentEnd="true"
+    android:layout_marginTop="@dimen/margin_50"
+    android:background="@android:color/transparent"
+    android:visibility="visible"
+    android:textCursorDrawable="@drawable/white_cursor" /&amp;gt;
+&amp;lt;TextView
+    android:layout_width="wrap_content"
+    android:layout_height="wrap_content"
+    android:textAppearance="?android:attr/textAppearanceMedium"
+    android:text="REGISTRATION"
+    android:id="@+id/regTitle_id"
+    android:layout_below="@+id/appLogoImage_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+    android:layout_alignParentEnd="true"
+    android:textColor="#ffffff"
+    android:textAlignment="center"
+    android:layout_marginTop="@dimen/margin_50"
+    android:visibility="invisible"
+    android:textStyle="bold" /&amp;gt;
+&amp;lt;EditText
+    android:layout_width="wrap_content"
+    android:layout_height="wrap_content"
+    android:inputType="textNoSuggestions|text"
+    android:ems="10"
+    android:id="@+id/regName_id"
+    android:layout_below="@+id/loginPassword_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+[K3]
+ android:layout_centerHorizontal="true"
+        android:layout_marginTop="96dp"
+        android:id="@+id/editText3"
+        android:hint="password" /&amp;gt;
+    &amp;lt;EditText
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:inputType="textPassword"
+        android:ems="10"
+        android:layout_below="@+id/editText3"
+        android:layout_alignRight="@+id/editText3"
+        android:layout_alignEnd="@+id/editText3"
+        android:id="@+id/editText4"
+        android:hint="confirm" /&amp;gt;
+    &amp;lt;Button
+        android:text="SIGN IN"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:layout_alignParentBottom="true"
+        android:id="@+id/button2"
+        android:layout_below="@+id/editText4"
+        android:layout_centerHorizontal="true" /&amp;gt;
+&amp;lt;/RelativeLayout&amp;gt;
+    &amp;lt;/ScrollView&amp;gt;
+&amp;lt;/RelativeLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;In your &lt;code&gt;Activity&lt;/code&gt; set the referance of the &lt;code&gt;ScrollView&lt;/code&gt; and the main &lt;code&gt;RelativeLayout&lt;/code&gt;
+Also set &lt;code&gt;ViewTreeObserver.OnGlobalLayoutListener&lt;/code&gt; on your main &lt;code&gt;RelativeLayout&lt;/code&gt; and implements the &lt;code&gt;onGlobalLayout()&lt;/code&gt; method.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Take a look at the example below:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public class MainActivity extends AppCompatActivity implements ViewTreeObserver.OnGlobalLayoutListener {
+    private ScrollView scrollView;
+    private RelativeLayout activity_main_RL;
+    @Override
+    protected void onCreate(Bundle savedInstanceState) {
+        super.onCreate(savedInstanceState);
+        setContentView(R.layout.activity_main);
+        scrollView = (ScrollView) findViewById(R.id.scroolView);
+        activity_main_RL =
+[K4]
+Q: Android - Struggiling to layout my application when virtual keyboard is visible
+A: &lt;p&gt;What I usually do is using &lt;code&gt;ScrollView&lt;/code&gt;:&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://i.sstatic.net/lERk2.gif" rel="nofollow noreferrer"&gt;&lt;img src="https://i.sstatic.net/lERk2.gif" alt="enter image description here"&gt;&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Define the &lt;code&gt;ScroolView&lt;/code&gt; in your &lt;code&gt;Layout&lt;/code&gt; like below (or just copy paste the code):&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;RelativeLayout
+    xmlns:android="http://schemas.android.com/apk/res/android"
+    xmlns:tools="http://schemas.android.com/tools"
+    android:id="@+id/activity_main"
+    android:layout_width="match_parent"
+    android:layout_height="match_parent"
+    tools:context="com.igor.test.MainActivity"&amp;gt;
+    &amp;lt;android.support.v7.widget.Toolbar
+        android:layout_width="match_parent"
+        android:layout_height="wrap_content"
+        android:background="?attr/colorPrimary"
+        android:theme="?attr/actionBarTheme"
+        android:minHeight="?attr/actionBarSize"
+        android:layout_alignParentTop="true"
+        android:layout_alignParentLeft="true"
+        android:layout_alignParentStart="true"
+        android:id="@+id/appTitleBar"
+        android:elevation="4dp"&amp;gt;
+        &amp;lt;TextView
+            android:text="@string/app_name"
+            android:layout_width="wrap_content"
+            android:layout_height="wrap_content"
+            android:id="@+id/toolbarText"
+            android:textAppearance="@style/TextAppearance.AppCompat.Title"
+            android:textColor="?android:attr/textColorPrimaryInverse" /&amp;gt;
+    &amp;lt;/android.support.v7.widget.Toolbar&amp;gt;
+    &amp;lt;android.support.v7
+[K5]
+    android:layout_marginTop="20dp"
+    android:gravity="center_horizontal"
+    android:orientation="horizontal"&amp;gt;
+    &amp;lt;TextView
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:drawableLeft="@drawable/msg" /&amp;gt;
+    &amp;lt;EditText
+        android:id="@+id/e1"
+        android:layout_width="300dp"
+        android:layout_height="wrap_content"
+        android:hint="  E-Mail/Adresse" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&amp;lt;LinearLayout
+    android:layout_width="match_parent"
+    android:layout_height="wrap_content"
+    android:gravity="center_horizontal"
+    android:orientation="horizontal"&amp;gt;
+    &amp;lt;TextView
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:drawableLeft="@drawable/lock" /&amp;gt;
+    &amp;lt;EditText
+        android:id="@+id/e2"
+        android:layout_width="300dp"
+        android:layout_height="wrap_content"
+        android:hint="  Password"
+        android:paddingTop="12dp" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&amp;lt;LinearLayout
+    android:layout_width="match_parent"
+    android:layout_height="match_parent"
+    android:gravity="center"&amp;gt;
+    &amp;lt;Button
+        android:id="@+id/b1"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:text="Sign In" /&amp;gt;
+    &amp;lt;Button
+        android:id="@+id/b2"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:text="Register" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;the src for the imageview bg.xml is &lt;/p&gt;
+&lt;pre</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4826,13 +7902,58 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the issue of a Blackberry application description text error for more than 255 characters. No information is provided regarding the specific error mentioned in the context.</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the issue of a Blackberry application description text error for more than 255 characters. No information is provided regarding the specific error mentioned.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Blackberry @Override notation error
+A: &lt;p&gt;Blackberry development is built on top of j2me, which has the language features of Java 1.3.  This means it doesn't support annotations. You can remove the @Override annotations and your code will work.  Remember these are optional although recommended anyways.&lt;/p&gt;
+&lt;p&gt;What I do, is write //@Override instead. When/If annotations are added in the future it will be easy to do a regex replace and remove the comment marks.&lt;/p&gt;
+[K2]
+Q: java.io.UnsupportedEncodingException: ISO-8859-8, text/xml
+A: &lt;p&gt;&lt;code&gt;ISO-8859-8&lt;/code&gt; is not one of the &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/StandardCharsets.html" rel="nofollow noreferrer"&gt;standard charsets&lt;/a&gt; that Java &lt;em&gt;needs&lt;/em&gt; to support, i.e. which are guaranteed to be found (unless you have a corrupted installation).&lt;/p&gt;
+&lt;p&gt;In your case, the difference seems to be in the Windows 10 environment. I would check first that it has support for &lt;code&gt;ISO-8859-8&lt;/code&gt; (I don't know how though, I'm not a Windows user). It may need to be installed/enabled separately.&lt;/p&gt;
+&lt;p&gt;If you're &lt;strong&gt;certain&lt;/strong&gt; that your Windows 10 does support that encoding, then it's a problem with Java not being able to make the connection between the two, and you'll probably have to delve into &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/spi/CharsetProvider.html" rel="nofollow noreferrer"&gt;charset providers&lt;/a&gt;, but let's hope you don't have to go there.&lt;/p&gt;
+[K3]
+Q: The encoding 'UTF-8' is not supported by the Java runtime
+A: &lt;p&gt;Most probably someone put a catch() expecting to have only unsupported encoding exceptions, so he used the appropriate message. But he has used too wide exception specification (e.g. catch( Exception ex ) ), so when at runtime he's got something else (non-valid XML, NPE, ... ) the message became misleading.&lt;/p&gt;
+[K4]
+Q: Does Blackberry support Android OS
+A: &lt;p&gt;Although Android and Blackberry both use Java, they expose very different application APIs to developers.  So I don't think it is possible to run Android apps on a Blackberry - YET.  RIM has already announced that they are planning on supporting Android apps on the upcoming Blackberry Playbook tablet.&lt;/p&gt;
+[K5]
+Q: Eclipse - "Incompatible JVM. Version 1.8.0_261 of the JVM is not suitable for this product. Version: 11 or greater is required"
+A: &lt;p&gt;For Ubuntu users, refer to the answer &lt;a href="https://stackoverflow.com/a/64049648/14489697"&gt;https://stackoverflow.com/a/64049648/14489697&lt;/a&gt; by howlger. Add the following lines in file &lt;code&gt;eclipse.ini&lt;/code&gt; before &lt;code&gt;-vmargs&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-none prettyprint-override"&gt;&lt;code&gt;-vm
+/usr/lib/jvm/adoptopenjdk-14-openj9-amd64/bin/java
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Above is the Java install location. Change this according to yours.&lt;/p&gt;
+&lt;p&gt;I'm using,&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Eclipse IDE for Enterprise Java Developers (includes Incubating components)&lt;/li&gt;
+&lt;li&gt;Version: 2020-12 (4.18.0)&lt;/li&gt;
+&lt;li&gt;Build id: 20201210-1552&lt;/li&gt;
+&lt;li&gt;OS: Linux, v.5.4.0-42-generic, x86_64 / gtk 3.22.30&lt;/li&gt;
+&lt;li&gt;Java version: 14.0.2&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4946,10 +8067,21 @@
 By following these steps, you should be able to resolve the issues with `CardView` and `RecyclerView` not being recognized in your XML layout. If you run into any more specific issues during the migration, please provide the error messages for further assistance.</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5013,10 +8145,82 @@
 These steps generally help resolve issues related to pushing changes to a remote repository when faced with errors about missing objects or invalid references.</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: remote: fatal: fsck error in packed object when pushing oh-my-zsh repo to new remote
+A: &lt;p&gt;&lt;a href="https://gitlab.com/gitlab-org/gitaly/issues/787" rel="nofollow noreferrer"&gt;In theory, this was already fixed at GitLab.&lt;/a&gt;  Why it is showing up for you, I have no idea.&lt;/p&gt;
+&lt;p&gt;The problem here is that &lt;code&gt;https://github.com/robbyrussell/oh-my-zsh&lt;/code&gt; itself is (somewhat) broken.  This has nothing to do with anything you did.  Meanwhile, your &lt;code&gt;gitlab.com&lt;/code&gt; service is configured to be ultra-strict.  This &lt;em&gt;also&lt;/em&gt; &lt;strong&gt;probably&lt;/strong&gt; has nothing to do with anything you did—but you'll need to change it, or else give up on the idea of sending &lt;em&gt;this&lt;/em&gt; repository to &lt;code&gt;gitlab.com&lt;/code&gt;.  (Or, perhaps your best bet, get them to note that their fix has un-fixed itself.)&lt;/p&gt;
+&lt;p&gt;If you clone the URL above and run &lt;code&gt;git fsck&lt;/code&gt; on your own clone, you'll see this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ git fsck
+Checking object directories: 100% (256/256), done.
+warning in tree 2b7227859263b6aabcc28355b0b994995b7148b6: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree a18c4d13c2a5fa2d4ecd5346c50e119b999b807d: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree 84df066176c8da3fd59b13731a86d90f4f1e5c9d: zeroPaddedFile
+[K2]
+Q: GIT 2nd PUSH is failing
+A: &lt;blockquote&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Git will not allow you to push changes if our branch is not up to date with the server&lt;/p&gt;
+&lt;p&gt;Once you try to &lt;code&gt;push&lt;/code&gt; your code to the remote repo git verify that your &amp;quot;local&amp;quot; branch has all the latest code from the remote branch. If it see that you are missing some commits it will not let you push the code to the remote.&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h3&gt;How to fix it?&lt;/h3&gt;
+&lt;p&gt;Its very simple - you simply need to pull the changes from the server in one of the following ways:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;# assuming you are on the desired branch
+# update your local server with all the latest code from the server
+# This is an optional command but its a good practice to always be 
+# synchronized with the server
+git fetch --all --prune
+# now pull (pull = fetch + merge) the changes from the server to your branch
+git pull origin &amp;lt;branch name&amp;gt;
+# now your local branch is up to date and contains all the &amp;quot;server&amp;quot; code as well
+# push your changes to the remote branch
+git push origin &amp;lt;branch name&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: "fatal: strange pathname '-im/somerepo.git' blocked
+A: &lt;p&gt;The leading &lt;code&gt;-&lt;/code&gt; character caused security issues in previous versions of git. It seems your Ubuntu installation contains the fixed Debian version that blocks your fetch attempt. You should rename the repository on BitBucket, and update your local configuration accordingly.&lt;/p&gt;
+&lt;p&gt;&lt;a href="http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2" rel="nofollow noreferrer"&gt;http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff" rel="nofollow noreferrer"&gt;https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: GitHub repository disabled when changing from private to public
+A: &lt;p&gt;Contacted GitHub support and they unlocked the repository. It may have happened because I changed the repo from private to public during their outage. Everything works fine now&lt;/p&gt;
+[K5]
+Q: merging local repo with github repo is resulting in a fatal error
+A: &lt;p&gt;Errors tell that your local branch is behind from master.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;1) Try &lt;code&gt;git pull origin master --rebase&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;if it does not work then local and remote branch, not in sync.
+you have to first sync your local master branch with remote master.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;follow following steps:&lt;/strong&gt;&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;copy your new commit hash which you recently commit.&lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git fetch origin&lt;/code&gt; &lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git reset --hard origin/master&lt;/code&gt; # to sync your
+local master with remoter master &lt;/li&gt;
+&lt;li&gt;cherry-pick your commit: &lt;code&gt;git cherry-pick your_commit_hash&lt;/code&gt;&lt;/li&gt;
+&lt;li&gt;&lt;code&gt;git push origin master&lt;/code&gt; # to push your commit
+Let me know if it still not resolved.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Thanks!&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5105,18 +8309,110 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover specific solutions for fixing the problem of rewriting all files and only having new timestamps for changed files in your git post-receive hook setup. However, I can suggest potential resolutions based on common Git practices.
+          <t>[catatan: informasi tidak tersedia] specific solutions for fixing the problem of rewriting all files and only having new timestamps for changed files in your git post-receive hook setup. However, I can suggest potential resolutions based on common Git practices.
 Typically, when files are pushed and checked out in a post-receive hook, if all files are being rewritten (even those that haven't changed), it could be related to the manner in which files are updated in the working directory. Here are some ways to potentially improve your workflow:
 1. **Use a Deployment Strategy**: Instead of checking out the branch in the post-receive hook and overwriting all files, consider using a deployment strategy that only updates the changed files. This could involve creating a build step that uses tools designed to manage file changes more intelligently (like `rsync` for deployment).
 2. **Conditional Checkout**: Modify the checkout commands to only overwrite files that have changed. For instance, you might want to explore using `git diff` or similar commands to identify modified files and only deploy those.
 3. **File Timestamps**: Ensure that the way files are checked out respects file timestamps. Some deployment tools (like those mentioned before) can intelligently handle this by only copying files that differ based on checksums, which may help maintain the original timestamps for unchanged files.
-These suggestions are based on standard practices in Git workflows but do not come directly from the provided sources. Thus, these recommendations aim to address the issue outlined but are not derived from the specific contexts you provided.</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
+These suggestions are based on standard practices in Git workflows but do not come directly. Thus, these recommendations aim to address the issue outlined but are not derived from the specific contexts you provided.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: GIT Branches - editing files
+A: &lt;p&gt;What you are describing is mostly default behavior of git, except there are a couple gotchas.  Some background, and then some possible solutions:&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Background&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;By "mostly default behavior", I mean: The point of branches &lt;em&gt;is&lt;/em&gt; (in part) that you can switch back and forth between versions of a file, by switching between the branches.  &lt;/p&gt;
+&lt;p&gt;But this only works for changes associated with the branch; and that association only occurs when you &lt;code&gt;commit&lt;/code&gt; the changes.  When you just edit, save, and maybe stage the file, but without committing it - then your changes exist in the work tree and maybe in the index, but git doesn't associate them with the branch yet.  &lt;/p&gt;
+&lt;p&gt;So when you run &lt;code&gt;git checkout&lt;/code&gt; to switch branches, probably git should issue a warning and refuse the checkout - and in some circumstances where data could otherwise be lost it will.  But in the case where the file is the same in last commits to both branches, it will keep the changes in the worktree and/or index while switching branches.  (At the command line, it does at least give you a little feedback to tell you this happened.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ git checkout master
+M       file1
+Switched to branch 'master'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;says that uncommitted changes were carried over in &lt;code&gt;file1&lt;/code&gt;.)&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Solutions&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;em&gt;Commit&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;The first solution you might've seen in the comments is to commit your changes.  If the changes are ready to commit, this is a good solution.  Even if they aren't ready to be part of a permanent commit, as long as
+[K2]
+Q: Is it a bad idea to run multiple git repos in the same directory using the $GIT_DIR environment variable or --git-dir flag?
+A: &lt;p&gt;As &lt;a href="https://stackoverflow.com/a/38354178/1256452"&gt;chepner answered&lt;/a&gt;, it &lt;em&gt;is&lt;/em&gt; useful, it's just a bit (or a lot) of a pain in the butt, as you yourself noted, since you must also set &lt;code&gt;$GIT_WORK_TREE&lt;/code&gt; or use &lt;code&gt;--work-tree&lt;/code&gt; in various cases.  You also have the issue that there is only a single staging area, &lt;code&gt;$GIT_DIR/index&lt;/code&gt;, for each repository, regardless of the work-tree.  You can override this as well by setting &lt;code&gt;$GIT_INDEX_FILE&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;(The next part is going in a different direction than you are; I include it for completeness.)&lt;/p&gt;
+&lt;p&gt;In older versions of Git there is a script that tries to make this easier, and in Git version 2.5, the script was (mostly) replaced with a new command, &lt;code&gt;git worktree&lt;/code&gt;, that lets you add explicit separate work-trees (each of which is &lt;em&gt;meant&lt;/em&gt; to be on a different branch, with checking to make sure it stays that way).  Git knows how to deal with these automatically, and takes care of the &lt;code&gt;--git-dir&lt;/code&gt;, &lt;code&gt;--work-tree&lt;/code&gt;, and separate index files for you, &lt;em&gt;also&lt;/em&gt; automatically.  But there are some bugs in it, with ongoing fixes; I would not recommend using this until at least Git version 2.6, and preferably 2.9 or whatever the latest is now, if you're going to use it heavily.&lt;/p&gt;
+[K3]
+ you don't &lt;code&gt;push&lt;/code&gt; the commit you could always edit it back out of history later - e.g. by doing the next commit with the &lt;code&gt;--amend&lt;/code&gt; option.&lt;/p&gt;
+&lt;p&gt;&lt;em&gt;Stash&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;But maybe you have some staged changes, and additional unstaged changes, and you don't want to mix them together into a single commit just yet.  Or maybe for some other reason you just don't feel that committing the changes is the right thing to do.&lt;/p&gt;
+&lt;p&gt;Another thing you can do is &lt;em&gt;stash&lt;/em&gt; the changes.  This really does still create temporary commits, but it tries to keep the staged and unstaged changes separate, and provides support for restoring your changes to their previous state.  See &lt;code&gt;git stash&lt;/code&gt; documentation.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;git checkout branch
+# edit some stuff
+git add .
+# edit more stuff
+git stash
+# NOTE: at this point it will look like your changes have simply been
+# reverted; but they haven't.
+git checkout master
+# now you have the `master` versions of all files
+# ... do stuff ...
+git checkout branch
+git stash pop
+# branch version of file is back
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;em&gt;Multiple Work Trees&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;The &lt;code&gt;stash&lt;/code&gt; is not bad, but not always perfect.&lt;/p&gt;
+&lt;p&gt;Maybe you want uncommitted changes on multiple branches at the same time.  This could be done with stashes, but then you have to keep things straight - like which stash belongs on which branch.  (&lt;code&gt;git&lt;/code&gt; can help a little with this, but it's still easy to mess up.)  So another solution to consider:&lt;/p&gt;
+&lt;p&gt;Your repo can have multiple work trees, each corresponding to a different branch.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;git
+[K4]
+Q: GIT 2nd PUSH is failing
+A: &lt;blockquote&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Git will not allow you to push changes if our branch is not up to date with the server&lt;/p&gt;
+&lt;p&gt;Once you try to &lt;code&gt;push&lt;/code&gt; your code to the remote repo git verify that your &amp;quot;local&amp;quot; branch has all the latest code from the remote branch. If it see that you are missing some commits it will not let you push the code to the remote.&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h3&gt;How to fix it?&lt;/h3&gt;
+&lt;p&gt;Its very simple - you simply need to pull the changes from the server in one of the following ways:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;# assuming you are on the desired branch
+# update your local server with all the latest code from the server
+# This is an optional command but its a good practice to always be 
+# synchronized with the server
+git fetch --all --prune
+# now pull (pull = fetch + merge) the changes from the server to your branch
+git pull origin &amp;lt;branch name&amp;gt;
+# now your local branch is up to date and contains all the &amp;quot;server&amp;quot; code as well
+# push your changes to the remote branch
+git push origin &amp;lt;branch name&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Difference between git push and git push -f
+A: &lt;p&gt;&lt;code&gt;git push -f&lt;/code&gt; is short for &lt;code&gt;git push --force&lt;/code&gt;. It forces a push when otherwise git would reject your &lt;code&gt;git push&lt;/code&gt; because you changed your repo history in your pushing repository. (&lt;strong&gt;EDIT:&lt;/strong&gt; But that is only half the story. Forced pushes also let you overwrite someone else's commits which have been pushed after your last pull.) Use case:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;Your repositories are at commit A. You change something locally and commit it (commit B).&lt;/li&gt;
+&lt;li&gt;You push B to your remote repo. Both are at B now.&lt;/li&gt;
+&lt;li&gt;You decide to change something again and replace your commit B by commit B'.&lt;/li&gt;
+&lt;li&gt;You want to push your commit B' to the remote repository. A plain &lt;code&gt;git push&lt;/code&gt; will not work. You can now remove commit B from your remote repo and push B' instead with &lt;code&gt;git push --force&lt;/code&gt;.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;This is ok, if only you are using that remote repo (Or no one else did a pull between B and B'). So, no, not a good idea on github.&lt;/p&gt;
+&lt;p&gt;Hope that helps.&lt;/p&gt;
+&lt;p&gt;(&lt;strong&gt;EDIT:&lt;/strong&gt; You can also check the GIT &lt;a href="https://git-scm.com/docs/git-push" rel="noreferrer"&gt;documentation&lt;/a&gt; or the GitHub &lt;a href="https://help.github.com/articles/adding-an-existing-project-to-github-using-the-command-line/" rel="noreferrer"&gt;help&lt;/a&gt;) &lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5155,13 +8451,85 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover a specific approach to resolve the issue of "missing necessary objects" and "remote: error: refs/pull/904/head does not point to a valid object!" mentioned in your problem. Therefore, I'm unable to provide a solution based on the given context.</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] a specific approach to resolve the issue of "missing necessary objects" and "remote: error: refs/pull/904/head does not point to a valid object!" mentioned in your problem. Therefore, I'm unable to provide a solution.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: remote: fatal: fsck error in packed object when pushing oh-my-zsh repo to new remote
+A: &lt;p&gt;&lt;a href="https://gitlab.com/gitlab-org/gitaly/issues/787" rel="nofollow noreferrer"&gt;In theory, this was already fixed at GitLab.&lt;/a&gt;  Why it is showing up for you, I have no idea.&lt;/p&gt;
+&lt;p&gt;The problem here is that &lt;code&gt;https://github.com/robbyrussell/oh-my-zsh&lt;/code&gt; itself is (somewhat) broken.  This has nothing to do with anything you did.  Meanwhile, your &lt;code&gt;gitlab.com&lt;/code&gt; service is configured to be ultra-strict.  This &lt;em&gt;also&lt;/em&gt; &lt;strong&gt;probably&lt;/strong&gt; has nothing to do with anything you did—but you'll need to change it, or else give up on the idea of sending &lt;em&gt;this&lt;/em&gt; repository to &lt;code&gt;gitlab.com&lt;/code&gt;.  (Or, perhaps your best bet, get them to note that their fix has un-fixed itself.)&lt;/p&gt;
+&lt;p&gt;If you clone the URL above and run &lt;code&gt;git fsck&lt;/code&gt; on your own clone, you'll see this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ git fsck
+Checking object directories: 100% (256/256), done.
+warning in tree 2b7227859263b6aabcc28355b0b994995b7148b6: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree a18c4d13c2a5fa2d4ecd5346c50e119b999b807d: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree 84df066176c8da3fd59b13731a86d90f4f1e5c9d: zeroPaddedFile
+[K2]
+Q: GIT 2nd PUSH is failing
+A: &lt;blockquote&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Git will not allow you to push changes if our branch is not up to date with the server&lt;/p&gt;
+&lt;p&gt;Once you try to &lt;code&gt;push&lt;/code&gt; your code to the remote repo git verify that your &amp;quot;local&amp;quot; branch has all the latest code from the remote branch. If it see that you are missing some commits it will not let you push the code to the remote.&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h3&gt;How to fix it?&lt;/h3&gt;
+&lt;p&gt;Its very simple - you simply need to pull the changes from the server in one of the following ways:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;# assuming you are on the desired branch
+# update your local server with all the latest code from the server
+# This is an optional command but its a good practice to always be 
+# synchronized with the server
+git fetch --all --prune
+# now pull (pull = fetch + merge) the changes from the server to your branch
+git pull origin &amp;lt;branch name&amp;gt;
+# now your local branch is up to date and contains all the &amp;quot;server&amp;quot; code as well
+# push your changes to the remote branch
+git push origin &amp;lt;branch name&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: "fatal: strange pathname '-im/somerepo.git' blocked
+A: &lt;p&gt;The leading &lt;code&gt;-&lt;/code&gt; character caused security issues in previous versions of git. It seems your Ubuntu installation contains the fixed Debian version that blocks your fetch attempt. You should rename the repository on BitBucket, and update your local configuration accordingly.&lt;/p&gt;
+&lt;p&gt;&lt;a href="http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2" rel="nofollow noreferrer"&gt;http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff" rel="nofollow noreferrer"&gt;https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: GitHub repository disabled when changing from private to public
+A: &lt;p&gt;Contacted GitHub support and they unlocked the repository. It may have happened because I changed the repo from private to public during their outage. Everything works fine now&lt;/p&gt;
+[K5]
+Q: merging local repo with github repo is resulting in a fatal error
+A: &lt;p&gt;Errors tell that your local branch is behind from master.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;1) Try &lt;code&gt;git pull origin master --rebase&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;if it does not work then local and remote branch, not in sync.
+you have to first sync your local master branch with remote master.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;follow following steps:&lt;/strong&gt;&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;copy your new commit hash which you recently commit.&lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git fetch origin&lt;/code&gt; &lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git reset --hard origin/master&lt;/code&gt; # to sync your
+local master with remoter master &lt;/li&gt;
+&lt;li&gt;cherry-pick your commit: &lt;code&gt;git cherry-pick your_commit_hash&lt;/code&gt;&lt;/li&gt;
+&lt;li&gt;&lt;code&gt;git push origin master&lt;/code&gt; # to push your commit
+Let me know if it still not resolved.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Thanks!&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5235,10 +8603,97 @@
 These steps leverage the information and tools suggested in various community discussions about installing Python packages on macOS, but the above process is structured for your specific situation regarding Python 3.3.</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: Why pypy is not recognizing my python 2.7/3.4 modules and packages?
+A: &lt;p&gt;PyPy 2.4 is a rather outdated version which contains no support for numpy (even if you tried to install it separately).&lt;/p&gt;
+&lt;p&gt;In any case it is very unlikely that even a brand-new version of PyPy would reduce the memory usage of a numpy-heavy program.&lt;/p&gt;
+&lt;p&gt;If you're hitting MemoryError at the scale of ~1-3GB of data in a single process, on a 32-bit OS, then it seems clear to me that you need a 64-bit OS.&lt;/p&gt;
+[K2]
+&lt;/strong&gt;: As discussed in the chat: The error was due to the conda env ignoring the CC variable. After installing python+pip via homebrew and the required python packages via pip, this answer's steps worked for the OP.&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;All in all, here's a setup.py that worked for me (macOS 10.5.7, gcc-10):&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;try:
+    from setuptools import setup
+except ImportError:
+    from distutils.core import setup
+from distutils.extension import Extension
+from Cython.Build import cythonize
+from torch.utils.cpp_extension import BuildExtension, CppExtension, CUDAExtension
+import numpy
+# Get the numpy include directory.
+numpy_include_dir = numpy.get_include()
+# Extensions
+# pykdtree (kd tree)
+pykdtree = Extension(
+    'im2mesh.utils.libkdtree.pykdtree.kdtree',
+    sources=[
+        'im2mesh/utils/libkdtree/pykdtree/kdtree.c',
+        'im2mesh/utils/libkdtree/pykdtree/_kdtree_core.c'
+    ],
+    language='c',
+    extra_compile_args=['-std=c99', '-O3', '-fopenmp'],
+    extra_link_args=['-lgomp'],
+    include_dirs=[numpy_include_dir]
+)
+# mcubes (marching cubes algorithm)
+mcubes_module = Extension(
+    'im2mesh.utils.libmcubes.mcubes',
+    sources=[
+        'im2mesh/utils/libmcubes/mcubes.pyx',
+        'im2mesh/utils/libmcubes/pywrapper.cpp',
+        'im2mesh/utils/libmcubes/marchingcubes.cpp'
+    ],
+    language='c++',
+    extra_compile_args=['-std=c++11'],
+    include_dirs=[numpy_include_dir]
+)
+# triangle hash (efficient mesh intersection)
+triangle_hash_module = Extension(
+[K3]
+Q: Google foo.bar Challenge Issue: Can't import libraries
+A: &lt;p&gt;Unfortunately numpy is not a standard library in python 2.7, and is not supported by foobar.  For a complete list of available modules, I suggest looking here: &lt;a href="https://docs.python.org/2/library/" rel="noreferrer"&gt;https://docs.python.org/2/library/&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: How is Anaconda related to Python?
+A: &lt;p&gt;Anaconda is a Python-based data processing and scientific computing platform. It has built in many very useful third-party libraries. Installing Anaconda is equivalent to automatically installing Python and some commonly used libraries such as Numpy, Pandas, Scrip, and Matplotlib, so it makes the installation so much easier than regular Python installation. If you don't install Anaconda, but instead only install Python from python.org, you also need to use pip to install various libraries one by one. It is painful and you need to consider compatibility, thus it is highly recommended to directly install Anaconda.&lt;/p&gt;
+[K5]
+Q: dpkg error: pycompile: not found
+A: &lt;p&gt;(EDIT: works in Python 3.11 down to 3.5)&lt;/p&gt;
+&lt;p&gt;Ahhhh, yes.  The venerable &amp;quot;Catch-22&amp;quot; situation of Debian package management.  It boils down to Debian depending on &lt;code&gt;py3compile&lt;/code&gt; as part of the &lt;code&gt;libpython3.x&lt;/code&gt; package when that package provides the &lt;code&gt;py3compile&lt;/code&gt; as well; it's a no-go, there.&lt;/p&gt;
+&lt;p&gt;I too was bitten by this unable to get &lt;code&gt;py3compile&lt;/code&gt; working again for I had too deleted the entire /usr/[/local]/lib/python3* directories.&lt;/p&gt;
+&lt;p&gt;Once done, nothing in Debian package management tool can help you get back to a working Python3 environment.  You must do meat-ball surgery.&lt;/p&gt;
+&lt;p&gt;Reconstruction of Python3 in Debian entails three critical things:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Restoring &lt;code&gt;py3compile&lt;/code&gt; script (for most of you, you already have this)&lt;/li&gt;
+&lt;li&gt;Restoring libpython3.7&lt;/li&gt;
+&lt;li&gt;Restoring python binary&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;One could do the RE-copying of /usr[/local]/lib directory from another working Debian host/system. But this time, I shall detail the steps from within the broken host in question (as if you do NOT have another working host).&lt;/p&gt;
+&lt;h1&gt;Step 1 - Download Packages&lt;/h1&gt;
+&lt;p&gt;Download the impacted Debian packages:&lt;/p&gt;
+&lt;pre class="lang-bash prettyprint-override"&gt;&lt;code&gt;cd /tmp
+apt-get download libpython3.7-minimal
+apt-get download python3.7-minimal
+apt-get download python3-minimal # (this is important)
+apt-get download libpython3.7-stdlib</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5328,14 +8783,129 @@
  ```
  Including this repository is necessary because many support libraries and Firebase libraries are hosted there ().
 3. **Sync Project with Gradle Files**: After making these changes, sync your project with the Gradle files in Android Studio to ensure that the new dependencies are resolved properly.
-Make sure to check the specific version numbers for compatibility with the Firebase libraries you are using. The retrieved context does indicate that FirebaseUI has specific dependencies on certain versions of Firebase libraries (), so ensure that all Firebase and support libraries are compatible.
-If you still face issues after trying these solutions, I recommend checking for any additional updates to both Android Studio and the Android SDK, as well as ensuring that your internet connection is stable during the sync process. The retrieved sources do not cover specific version numbers beyond the ones I've mentioned.</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
+Make sure to check the specific version numbers for compatibility with the Firebase libraries you are using. FirebaseUI has specific dependencies on certain versions of Firebase libraries (), so ensure that all Firebase and support libraries are compatible.
+If you still face issues after trying these solutions, I recommend checking for any additional updates to both Android Studio and the Android SDK, as well as ensuring that your internet connection is stable during the sync process. [catatan: informasi tidak tersedia] specific version numbers beyond the ones I've mentioned.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: "com.android.support:appcompat-v7:28.0.0" Error
+A: &lt;pre&gt;&lt;code&gt;implementation 'com.android.support:support-media-compat:28.0.0'
+implementation 'com.android.support:support-v4:28.0.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;add to dependencies and change &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:16.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;to &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:9.0.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This is working for me&lt;/p&gt;
+[K2]
+0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CONFIG_VERSION&amp;quot;: &amp;quot;21.2.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_VERSION&amp;quot;: &amp;quot;20.3.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_AUTH_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FIRESTORE_VERSION&amp;quot;: &amp;quot;24.4.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FUNCTIONS_VERSION&amp;quot;: &amp;quot;20.2.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_IID_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_INSTALLATIONS_VERSION&amp;quot;: &amp;quot;17.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_NDK_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_GSON_VERSION&amp;quot;: &amp;quot;2.9.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_GRADLE_PLUGIN_VERSION&amp;quot;: &amp;quot;1.4.2&amp;quot;,
+        &amp;quot;ANDROID_GRPC_OKHTTP&amp;quot;: &amp;quot;1.46.0&amp;quot;,
+        &amp;quot;IOS_USE_PRECOMPILED_FIRESTORE_POD&amp;quot;: &amp;quot;false&amp;quot;
+      },
+      &amp;quot;cordova-plugin-androidx-adapter&amp;quot;: {}
+    },
+    &amp;quot;platforms&amp;quot;: [
+      &amp;quot;browser&amp;quot;,
+      &amp;quot;ios&amp;quot;,
+      &amp;quot;android&amp;quot;
+    ]
+  }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;References:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://developer.apple.com
+[K3]
+Q: I keep receiving a gradle sync error when trying to add Firebase UI 2.3.0
+A: &lt;p&gt;Since you are using &lt;code&gt;com.android.support:customtabs:26.0.1&lt;/code&gt; you have to add in the &lt;code&gt;repositories&lt;/code&gt; the "&lt;a href="https://maven.google.com" rel="nofollow noreferrer"&gt;https://maven.google.com&lt;/a&gt;" endpoint.&lt;br&gt;
+All the support libraries since 25.4.0 are in the google maven repo as &lt;a href="https://developer.android.com/topic/libraries/support-library/revisions.html#25-4-0" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;In your case something like;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;allprojects {
+    repositories {
+        jcenter()
+        maven { url 'https://maven.fabric.io/public' }  // &amp;lt;= ADD THIS
+        maven {
+            url "https://maven.google.com"
+        }
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Also if you want to add the latest &lt;strong&gt;Firebase libraries v. 11.2.0&lt;/strong&gt; you have to add the same repo as &lt;a href="https://developers.google.com/android/guides/releases#august_2017_-_version_1120" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+[K4]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Error:Execution failed for task ':app:processDebugManifest'. &gt; Manifest merger failed
+A: &lt;p&gt;There are some mistakes:&lt;/p&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of Firebase and Google Play Services&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;Change:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:10.0.1'
+compile 'com.google.android.gms:play-services:10.0.1'
+compile 'com.google.firebase:firebase-storage:10.0.1'
+compile 'com.google.firebase:firebase-auth:11.0.1'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;using the latest version:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:11.4.2'
+compile 'com.google.android.gms:play-services:11.4.2'
+compile 'com.google.firebase:firebase-storage:11.4.2'
+compile 'com.google.firebase:firebase-auth:11.4.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of support libraries&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:appcompat-v7:26.1.0'
+compile 'com.android.support:support-v4:26.1.0'
+compile 'com.android.support:support-compat:26.1.0'
+compile 'com.android.support:cardview-v7:26.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FirebaseUI has dependency on a fixed version of firebase libraries.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Check &lt;a href="https://github.com/firebase/FirebaseUI-Android" rel="nofollow noreferrer"&gt;the table&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;For convenience, here are some examples:&lt;/p&gt;
+&lt;pre&gt;&lt;code</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5425,10 +8995,21 @@
 Both methods can be useful depending on your design needs. Understanding the context in which you're using them will help you decide which one to apply. For layouts where the element should always fill the visible space regardless of content, `100vh` is great. For content-driven layouts, `100%` might be better.</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5479,21 +9060,78 @@
 In summary, given the issues you are facing and the continuing trends in the .NET ecosystem, it would be beneficial to migrate your class libraries to .NET 6. This step will ensure compatibility with the latest versions of Entity Framework Core and leverage the latest features and performance improvements.</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: how to use EF6.0 in .netframework 4.6.2 class library project referenced inside ASPNET Core 2.0 project
+A: &lt;p&gt;The Microsoft article &lt;a href="https://learn.microsoft.com/en-us/aspnet/core/data/entity-framework-6" rel="nofollow noreferrer"&gt;Get Started with ASP.NET Core and Entity Framework 6&lt;/a&gt; has the steps necessary for using Entity Framework 6 from a ASP.NET Core project.&lt;/p&gt;
+&lt;p&gt;Regarding the &lt;code&gt;NotSupportedException&lt;/code&gt;, I would refer to the related question &lt;a href="https://stackoverflow.com/q/52185029/4387459"&gt;System.NotSupportedException: Unable to determine the provider name for provider factory of type 'System.Data.SqlClient.SqlClientFactory'&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;I ran into the same issue because I failed to change the Core &lt;code&gt;.csproj&lt;/code&gt; file from &lt;code&gt;&amp;lt;TargetFramework&amp;gt;netcoreapp2.2&amp;lt;/TargetFramework&amp;gt;&lt;/code&gt; to &lt;code&gt;&amp;lt;TargetFramework&amp;gt;net471&amp;lt;/TargetFramework&amp;gt;&lt;/code&gt; (which the article told me to do, but for some reason I thought wasn't necessary in Core 2.2). &lt;/p&gt;
+&lt;p&gt;I provided more explanation and details in the &lt;a href="https://stackoverflow.com/a/54116150/4387459"&gt;posted explanation/answer&lt;/a&gt; to the question I referenced above.&lt;/p&gt;
+[K2]
+Q: Is .Net 7 backwards compatible with .Net 6?
+A: &lt;p&gt;According to this post - &lt;a href="https://learn.microsoft.com/en-us/dotnet/core/compatibility/7.0" rel="noreferrer"&gt;https://learn.microsoft.com/en-us/dotnet/core/compatibility/7.0&lt;/a&gt; - it doesn't look like it, which makes sense since it's a major version change.&lt;/p&gt;
+&lt;p&gt;The fact that that .NET 7 will not be supported for as long as .NET 6 will be is a completely separate beast entirely as .NET 6 is a LTS (Long Term Support) release and will be supported with bug and security fixes for (has to look it up) 3 years.&lt;/p&gt;
+&lt;p&gt;.NET 7 however is a STS (Standard Term Support) release and will only be supported for 18 months (6 months beyond the release of .NET 8).&lt;/p&gt;
+&lt;p&gt;.NET 8 will be a LTS release and will again be supported for 3 years providing 1 year of overlap in support for .NET 6 and .NET 8.&lt;/p&gt;
+&lt;p&gt;More info on the support lifecycle of .NET and .NET Core versions can be found here: &lt;a href="https://dotnet.microsoft.com/en-us/platform/support/policy/dotnet-core" rel="noreferrer"&gt;https://dotnet.microsoft.com/en-us/platform/support/policy/dotnet-core&lt;/a&gt;&lt;/p&gt;
+[K3]
+Q: How to compile .NET Core 2.1 API project to target .NET Framework 4.7
+A: &lt;p&gt;&lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; indeed does not support .NET Framework 4.7 - so you &lt;strong&gt;cannot&lt;/strong&gt; trivially do this.&lt;/p&gt;
+&lt;p&gt;It &lt;em&gt;might&lt;/em&gt; be that you can use some manual sub-set of the things that &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; targets, and get it to work - but this will only help if you are just using &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; as a meta-package, and don't need something out of &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; itself. So: you could try dropping the &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; dependency, see what fails, and try adding packages back in. The list of things that &lt;code&gt;Microsoft.AspNetCore.App&lt;/code&gt; imports can be seen by expanding "Dependencies" on the &lt;a href="https://www.nuget.org/packages/Microsoft.AspNetCore.App/" rel="nofollow noreferrer"&gt;nuget page&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;But: it is entirely possible that it &lt;em&gt;just isn't possible&lt;/em&gt;.&lt;/p&gt;
+[K4]
+Q: Using ServiceStack with Full .NET Framework
+A: &lt;p&gt;If you want to run on &lt;strong&gt;classic ASP.NET&lt;/strong&gt; or HttpListener you should only reference the main &lt;code&gt;"ServiceStack.Admin"&lt;/code&gt; packages (i.e. without .Core suffix) which contain both .NET Standard 2.0 and .NET Framework v4.5 builds. In a .NET Framework Application it will use the &lt;strong&gt;.NET v4.5&lt;/strong&gt; Framework builds.&lt;/p&gt;
+&lt;p&gt;If you want to create new &lt;strong&gt;ASP.NET Core&lt;/strong&gt; Apps on the .NET Framework you should &lt;a href="http://docs.servicestack.net/templates-corefx#reference-core-packages" rel="nofollow noreferrer"&gt;reference .Core packages instead&lt;/a&gt; which only contains &lt;strong&gt;.NET Standard 2.0&lt;/strong&gt; builds to force .NET Framework Applications to use the .NET Standard builds that are required for running in ASP.NET Core Apps.&lt;/p&gt;
+&lt;p&gt;I strongly recommend starting with one of the &lt;a href="http://docs.servicestack.net/templates-corefx" rel="nofollow noreferrer"&gt;ASP.NET Core .NET Framework Templates&lt;/a&gt; to create a working project with the correct dependencies:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ npm install -g @servicestack/cli
+$ dotnet-new web-corefx AcmeNetFx
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You should &lt;strong&gt;never reference both&lt;/strong&gt;, also you can only use the same version number of all packages together, i.e. you can't use the deprecated &lt;code&gt;ServiceStack.Api.Swagger.Core&lt;/code&gt; package with v5.2.1 assemblies.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;ServiceStack.Api.Swagger&lt;/code&gt; contains the old &lt;a href="http://docs.servicestack.net/swagger-api" rel="nofollow noreferrer"&gt;v1.2 version of Swagger&lt;/a&gt;, you likely want to reference &lt;code
+[K5]
+ .net standard.  I target .net 4.6.1, .net standard 2.0, and .net core 2.1 since I have had issues resolving .net standard-only packages.  Perhaps that will change in future.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>annotator1</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="E2:E61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="G2:G61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+    <dataValidation sqref="H2:H61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: PENUH, SEBAGIAN" type="list">
+    <dataValidation sqref="I2:I61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: PENUH, SEBAGIAN" type="list">
       <formula1>"PENUH,SEBAGIAN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: all_supported, partly_supported, not_supported" type="list">
+      <formula1>"all_supported,partly_supported,not_supported"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: same, different_valid, different_unassessable" type="list">
+      <formula1>"same,different_valid,different_unassessable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: familiar, not_familiar" type="list">
+      <formula1>"familiar,not_familiar"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5506,7 +9144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -5522,35 +9160,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abstain: Y jika jawaban kandidat tidak mencoba menjawab; N jika mencoba menjawab.</t>
+          <t>Panduan singkat: docs/ANNOTATION_QUICKSTART.md.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hallucinated: isi HANYA jika abstain = N. Y jika ada &gt;= 1 klaim yang bertentangan dengan referensi atau fakta mapan, atau yang dikarang (API/fungsi/opsi tidak ada). N jika tidak ada.</t>
+          <t>annotator_id: sudah terisi; jangan diubah kecuali Anda annotator lain.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>severity: isi HANYA jika hallucinated = Y. PENUH jika kesalahan mengenai solusi utama; SEBAGIAN jika hanya detail sekunder.</t>
+          <t>abstain: Y jika jawaban kandidat tidak mencoba menjawab; N jika mencoba menjawab.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>notes: catatan bebas. Tulis 'referensi usang' bila memakai aturan referensi usang.</t>
+          <t>hallucinated: isi HANYA jika abstain = N. Y jika ada &gt;= 1 klaim yang bertentangan dengan referensi atau fakta mapan, atau yang dikarang (API/fungsi/opsi tidak ada). N jika tidak ada.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jangan mengubah kolom item_id, question, accepted_answer, candidate_answer.</t>
+          <t>severity: isi HANYA jika hallucinated = Y. PENUH jika kesalahan mengenai solusi utama; SEBAGIAN jika hanya detail sekunder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>wrong_claims: WAJIB jika hallucinated = Y, kosong jika tidak. Satu klaim salah per baris (Alt+Enter): jenis | klaim | bukti. jenis = contradicted atau fabricated. bukti = URL dokumentasi, atau kutipan dalam tanda petik dari thread/konteks (mis. "[K2] ... teks ...").</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>faithfulness_level: isi HANYA jika kolom context tidak kosong dan abstain = N: all_supported / partly_supported / not_supported (klaim jawaban didukung konteks?).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>approach_match: isi jika abstain = N: same / different_valid / different_unassessable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>domain_familiarity: selalu isi: familiar / not_familiar (keakraban Anda dengan topiknya).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>uncertain: selalu isi: Y jika Anda ragu pada label baris ini, N jika tidak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>notes: catatan bebas. Tulis 'referensi usang' bila memakai aturan referensi usang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jangan mengubah kolom item_id, question, accepted_answer, candidate_answer, context.</t>
         </is>
       </c>
     </row>
